--- a/docs/[13조]_400. 서비스_분석 설계서_434_테이블설계서_v0.1.filled.xlsx
+++ b/docs/[13조]_400. 서비스_분석 설계서_434_테이블설계서_v0.1.filled.xlsx
@@ -2926,7 +2926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K147"/>
+  <dimension ref="A1:K148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col width="18" customWidth="1" style="1" min="1" max="1"/>
@@ -3056,7 +3056,7 @@
       <c r="J3" s="92" t="inlineStr"/>
       <c r="K3" s="92" t="inlineStr">
         <is>
-          <t>Peer 식별자 (samsung_sds · lg_cns · hyundai_autoever · posco_dx)</t>
+          <t>Peer 식별자 (samsung_sds · lg_cns · hyundai_autoever · posco_dx · sk_ax)</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
       <c r="J4" s="92" t="inlineStr"/>
       <c r="K4" s="92" t="inlineStr">
         <is>
-          <t>한글 표기명 (삼성SDS · LG CNS · 현대오토에버 · 포스코DX)</t>
+          <t>한글 표기명 (삼성SDS · LG CNS · 현대오토에버 · 포스코DX · SK AX)</t>
         </is>
       </c>
     </row>
@@ -3139,35 +3139,39 @@
       <c r="B6" s="91" t="n"/>
       <c r="C6" s="92" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>role</t>
         </is>
       </c>
       <c r="D6" s="92" t="inlineStr">
         <is>
-          <t>활성 여부</t>
+          <t>역할</t>
         </is>
       </c>
       <c r="E6" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F6" s="92" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="G6" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G6" s="92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="H6" s="92" t="inlineStr"/>
       <c r="I6" s="92" t="inlineStr"/>
       <c r="J6" s="92" t="inlineStr">
         <is>
-          <t>Default TRUE</t>
+          <t>Default 'peer', CHECK (peer|self)</t>
         </is>
       </c>
       <c r="K6" s="92" t="inlineStr">
         <is>
-          <t>현재 모니터링 대상인지 여부</t>
+          <t>peer (경쟁사 4사) | self (SK AX 자사). V5 추가.</t>
         </is>
       </c>
     </row>
@@ -3176,12 +3180,12 @@
       <c r="B7" s="91" t="n"/>
       <c r="C7" s="92" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>is_active</t>
         </is>
       </c>
       <c r="D7" s="92" t="inlineStr">
         <is>
-          <t>생성 시각</t>
+          <t>활성 여부</t>
         </is>
       </c>
       <c r="E7" s="92" t="inlineStr">
@@ -3191,7 +3195,7 @@
       </c>
       <c r="F7" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="G7" s="92" t="inlineStr"/>
@@ -3199,102 +3203,98 @@
       <c r="I7" s="92" t="inlineStr"/>
       <c r="J7" s="92" t="inlineStr">
         <is>
-          <t>Default NOW()</t>
+          <t>Default TRUE</t>
         </is>
       </c>
       <c r="K7" s="92" t="inlineStr">
         <is>
-          <t>row 생성 시각</t>
+          <t>현재 모니터링 대상인지 여부</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="91" t="inlineStr">
-        <is>
-          <t>raw_articles</t>
-        </is>
-      </c>
-      <c r="B8" s="91" t="inlineStr">
-        <is>
-          <t>수집 기사 원문</t>
-        </is>
-      </c>
+      <c r="A8" s="91" t="n"/>
+      <c r="B8" s="91" t="n"/>
       <c r="C8" s="92" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D8" s="92" t="inlineStr">
         <is>
-          <t>기사 ID</t>
+          <t>생성 시각</t>
         </is>
       </c>
       <c r="E8" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F8" s="92" t="inlineStr">
         <is>
-          <t>BIGSERIAL</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="G8" s="92" t="inlineStr"/>
-      <c r="H8" s="92" t="inlineStr">
-        <is>
-          <t>PK1</t>
-        </is>
-      </c>
+      <c r="H8" s="92" t="inlineStr"/>
       <c r="I8" s="92" t="inlineStr"/>
       <c r="J8" s="92" t="inlineStr">
         <is>
+          <t>Default NOW()</t>
+        </is>
+      </c>
+      <c r="K8" s="92" t="inlineStr">
+        <is>
+          <t>row 생성 시각</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="91" t="inlineStr">
+        <is>
+          <t>raw_articles</t>
+        </is>
+      </c>
+      <c r="B9" s="91" t="inlineStr">
+        <is>
+          <t>수집 기사 원문</t>
+        </is>
+      </c>
+      <c r="C9" s="92" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D9" s="92" t="inlineStr">
+        <is>
+          <t>기사 ID</t>
+        </is>
+      </c>
+      <c r="E9" s="92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F9" s="92" t="inlineStr">
+        <is>
+          <t>BIGSERIAL</t>
+        </is>
+      </c>
+      <c r="G9" s="92" t="inlineStr"/>
+      <c r="H9" s="92" t="inlineStr">
+        <is>
+          <t>PK1</t>
+        </is>
+      </c>
+      <c r="I9" s="92" t="inlineStr"/>
+      <c r="J9" s="92" t="inlineStr">
+        <is>
           <t>AUTO_INCREMENT</t>
         </is>
       </c>
-      <c r="K8" s="92" t="inlineStr">
+      <c r="K9" s="92" t="inlineStr">
         <is>
           <t>row 자동 증가 PK</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="91" t="n"/>
-      <c r="B9" s="91" t="n"/>
-      <c r="C9" s="92" t="inlineStr">
-        <is>
-          <t>peer_id</t>
-        </is>
-      </c>
-      <c r="D9" s="92" t="inlineStr">
-        <is>
-          <t>Peer ID</t>
-        </is>
-      </c>
-      <c r="E9" s="92" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F9" s="92" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G9" s="92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H9" s="92" t="inlineStr"/>
-      <c r="I9" s="92" t="inlineStr">
-        <is>
-          <t>peer_companies.id</t>
-        </is>
-      </c>
-      <c r="J9" s="92" t="inlineStr"/>
-      <c r="K9" s="92" t="inlineStr">
-        <is>
-          <t>수집된 기사가 속한 Peer 회사</t>
         </is>
       </c>
     </row>
@@ -3303,12 +3303,12 @@
       <c r="B10" s="91" t="n"/>
       <c r="C10" s="92" t="inlineStr">
         <is>
-          <t>source_tier</t>
+          <t>peer_id</t>
         </is>
       </c>
       <c r="D10" s="92" t="inlineStr">
         <is>
-          <t>출처 등급</t>
+          <t>Peer ID</t>
         </is>
       </c>
       <c r="E10" s="92" t="inlineStr">
@@ -3318,20 +3318,24 @@
       </c>
       <c r="F10" s="92" t="inlineStr">
         <is>
-          <t>SMALLINT</t>
-        </is>
-      </c>
-      <c r="G10" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G10" s="92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="H10" s="92" t="inlineStr"/>
-      <c r="I10" s="92" t="inlineStr"/>
-      <c r="J10" s="92" t="inlineStr">
-        <is>
-          <t>1~5</t>
-        </is>
-      </c>
+      <c r="I10" s="92" t="inlineStr">
+        <is>
+          <t>peer_companies.id</t>
+        </is>
+      </c>
+      <c r="J10" s="92" t="inlineStr"/>
       <c r="K10" s="92" t="inlineStr">
         <is>
-          <t>출처 신뢰도 등급 (1=DART, 5=SNS)</t>
+          <t>수집된 기사가 속한 Peer 회사</t>
         </is>
       </c>
     </row>
@@ -3340,12 +3344,12 @@
       <c r="B11" s="91" t="n"/>
       <c r="C11" s="92" t="inlineStr">
         <is>
-          <t>source_name</t>
+          <t>source_tier</t>
         </is>
       </c>
       <c r="D11" s="92" t="inlineStr">
         <is>
-          <t>출처 명</t>
+          <t>출처 등급</t>
         </is>
       </c>
       <c r="E11" s="92" t="inlineStr">
@@ -3355,20 +3359,20 @@
       </c>
       <c r="F11" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G11" s="92" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>SMALLINT</t>
+        </is>
+      </c>
+      <c r="G11" s="92" t="inlineStr"/>
       <c r="H11" s="92" t="inlineStr"/>
       <c r="I11" s="92" t="inlineStr"/>
-      <c r="J11" s="92" t="inlineStr"/>
+      <c r="J11" s="92" t="inlineStr">
+        <is>
+          <t>1~5</t>
+        </is>
+      </c>
       <c r="K11" s="92" t="inlineStr">
         <is>
-          <t>수집 소스 이름 (DART · 한경 · Naver 등)</t>
+          <t>출처 신뢰도 등급 (1=DART, 5=SNS)</t>
         </is>
       </c>
     </row>
@@ -3377,12 +3381,12 @@
       <c r="B12" s="91" t="n"/>
       <c r="C12" s="92" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>source_name</t>
         </is>
       </c>
       <c r="D12" s="92" t="inlineStr">
         <is>
-          <t>제목</t>
+          <t>출처 명</t>
         </is>
       </c>
       <c r="E12" s="92" t="inlineStr">
@@ -3392,16 +3396,20 @@
       </c>
       <c r="F12" s="92" t="inlineStr">
         <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="G12" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G12" s="92" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="H12" s="92" t="inlineStr"/>
       <c r="I12" s="92" t="inlineStr"/>
       <c r="J12" s="92" t="inlineStr"/>
       <c r="K12" s="92" t="inlineStr">
         <is>
-          <t>기사 제목</t>
+          <t>수집 소스 이름 (DART · 한경 · Naver 등)</t>
         </is>
       </c>
     </row>
@@ -3410,17 +3418,17 @@
       <c r="B13" s="91" t="n"/>
       <c r="C13" s="92" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D13" s="92" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>제목</t>
         </is>
       </c>
       <c r="E13" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F13" s="92" t="inlineStr">
@@ -3431,14 +3439,10 @@
       <c r="G13" s="92" t="inlineStr"/>
       <c r="H13" s="92" t="inlineStr"/>
       <c r="I13" s="92" t="inlineStr"/>
-      <c r="J13" s="92" t="inlineStr">
-        <is>
-          <t>최대 10K자 잘라 저장</t>
-        </is>
-      </c>
+      <c r="J13" s="92" t="inlineStr"/>
       <c r="K13" s="92" t="inlineStr">
         <is>
-          <t>기사 본문 (요약 또는 full)</t>
+          <t>기사 제목</t>
         </is>
       </c>
     </row>
@@ -3447,17 +3451,17 @@
       <c r="B14" s="91" t="n"/>
       <c r="C14" s="92" t="inlineStr">
         <is>
-          <t>url</t>
+          <t>content</t>
         </is>
       </c>
       <c r="D14" s="92" t="inlineStr">
         <is>
-          <t>원문 URL</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="E14" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F14" s="92" t="inlineStr">
@@ -3470,12 +3474,12 @@
       <c r="I14" s="92" t="inlineStr"/>
       <c r="J14" s="92" t="inlineStr">
         <is>
-          <t>UNIQUE</t>
+          <t>최대 10K자 잘라 저장</t>
         </is>
       </c>
       <c r="K14" s="92" t="inlineStr">
         <is>
-          <t>원문 URL (멱등성 보장 키)</t>
+          <t>기사 본문 (요약 또는 full)</t>
         </is>
       </c>
     </row>
@@ -3484,12 +3488,12 @@
       <c r="B15" s="91" t="n"/>
       <c r="C15" s="92" t="inlineStr">
         <is>
-          <t>published_at</t>
+          <t>url</t>
         </is>
       </c>
       <c r="D15" s="92" t="inlineStr">
         <is>
-          <t>발행 시각</t>
+          <t>원문 URL</t>
         </is>
       </c>
       <c r="E15" s="92" t="inlineStr">
@@ -3499,16 +3503,20 @@
       </c>
       <c r="F15" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="G15" s="92" t="inlineStr"/>
       <c r="H15" s="92" t="inlineStr"/>
       <c r="I15" s="92" t="inlineStr"/>
-      <c r="J15" s="92" t="inlineStr"/>
+      <c r="J15" s="92" t="inlineStr">
+        <is>
+          <t>UNIQUE</t>
+        </is>
+      </c>
       <c r="K15" s="92" t="inlineStr">
         <is>
-          <t>원문 발행 시각</t>
+          <t>원문 URL (멱등성 보장 키)</t>
         </is>
       </c>
     </row>
@@ -3517,17 +3525,17 @@
       <c r="B16" s="91" t="n"/>
       <c r="C16" s="92" t="inlineStr">
         <is>
-          <t>collected_at</t>
+          <t>published_at</t>
         </is>
       </c>
       <c r="D16" s="92" t="inlineStr">
         <is>
-          <t>수집 시각</t>
+          <t>발행 시각</t>
         </is>
       </c>
       <c r="E16" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F16" s="92" t="inlineStr">
@@ -3538,14 +3546,10 @@
       <c r="G16" s="92" t="inlineStr"/>
       <c r="H16" s="92" t="inlineStr"/>
       <c r="I16" s="92" t="inlineStr"/>
-      <c r="J16" s="92" t="inlineStr">
-        <is>
-          <t>Default NOW()</t>
-        </is>
-      </c>
+      <c r="J16" s="92" t="inlineStr"/>
       <c r="K16" s="92" t="inlineStr">
         <is>
-          <t>AXIS 가 수집한 시각</t>
+          <t>원문 발행 시각</t>
         </is>
       </c>
     </row>
@@ -3554,12 +3558,12 @@
       <c r="B17" s="91" t="n"/>
       <c r="C17" s="92" t="inlineStr">
         <is>
-          <t>credibility_score</t>
+          <t>collected_at</t>
         </is>
       </c>
       <c r="D17" s="92" t="inlineStr">
         <is>
-          <t>신뢰도 점수</t>
+          <t>수집 시각</t>
         </is>
       </c>
       <c r="E17" s="92" t="inlineStr">
@@ -3569,7 +3573,7 @@
       </c>
       <c r="F17" s="92" t="inlineStr">
         <is>
-          <t>FLOAT</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="G17" s="92" t="inlineStr"/>
@@ -3577,12 +3581,12 @@
       <c r="I17" s="92" t="inlineStr"/>
       <c r="J17" s="92" t="inlineStr">
         <is>
-          <t>0.0~1.0</t>
+          <t>Default NOW()</t>
         </is>
       </c>
       <c r="K17" s="92" t="inlineStr">
         <is>
-          <t>CredibilityAgent 가 계산한 출처 신뢰도</t>
+          <t>AXIS 가 수집한 시각</t>
         </is>
       </c>
     </row>
@@ -3591,12 +3595,12 @@
       <c r="B18" s="91" t="n"/>
       <c r="C18" s="92" t="inlineStr">
         <is>
-          <t>credibility_grade</t>
+          <t>credibility_score</t>
         </is>
       </c>
       <c r="D18" s="92" t="inlineStr">
         <is>
-          <t>신뢰도 등급</t>
+          <t>신뢰도 점수</t>
         </is>
       </c>
       <c r="E18" s="92" t="inlineStr">
@@ -3606,24 +3610,20 @@
       </c>
       <c r="F18" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G18" s="92" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="G18" s="92" t="inlineStr"/>
       <c r="H18" s="92" t="inlineStr"/>
       <c r="I18" s="92" t="inlineStr"/>
       <c r="J18" s="92" t="inlineStr">
         <is>
-          <t>High|Medium|Low|Unverified</t>
+          <t>0.0~1.0</t>
         </is>
       </c>
       <c r="K18" s="92" t="inlineStr">
         <is>
-          <t>score 의 등급화 결과</t>
+          <t>CredibilityAgent 가 계산한 출처 신뢰도</t>
         </is>
       </c>
     </row>
@@ -3632,12 +3632,12 @@
       <c r="B19" s="91" t="n"/>
       <c r="C19" s="92" t="inlineStr">
         <is>
-          <t>cluster_id</t>
+          <t>credibility_grade</t>
         </is>
       </c>
       <c r="D19" s="92" t="inlineStr">
         <is>
-          <t>클러스터 ID</t>
+          <t>신뢰도 등급</t>
         </is>
       </c>
       <c r="E19" s="92" t="inlineStr">
@@ -3647,16 +3647,24 @@
       </c>
       <c r="F19" s="92" t="inlineStr">
         <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="G19" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G19" s="92" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="H19" s="92" t="inlineStr"/>
       <c r="I19" s="92" t="inlineStr"/>
-      <c r="J19" s="92" t="inlineStr"/>
+      <c r="J19" s="92" t="inlineStr">
+        <is>
+          <t>High|Medium|Low|Unverified</t>
+        </is>
+      </c>
       <c r="K19" s="92" t="inlineStr">
         <is>
-          <t>DedupAgent 가 부여한 동일 이슈 묶음 ID</t>
+          <t>score 의 등급화 결과</t>
         </is>
       </c>
     </row>
@@ -3665,12 +3673,12 @@
       <c r="B20" s="91" t="n"/>
       <c r="C20" s="92" t="inlineStr">
         <is>
-          <t>is_representative</t>
+          <t>cluster_id</t>
         </is>
       </c>
       <c r="D20" s="92" t="inlineStr">
         <is>
-          <t>대표 기사 여부</t>
+          <t>클러스터 ID</t>
         </is>
       </c>
       <c r="E20" s="92" t="inlineStr">
@@ -3680,20 +3688,16 @@
       </c>
       <c r="F20" s="92" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="G20" s="92" t="inlineStr"/>
       <c r="H20" s="92" t="inlineStr"/>
       <c r="I20" s="92" t="inlineStr"/>
-      <c r="J20" s="92" t="inlineStr">
-        <is>
-          <t>Default FALSE</t>
-        </is>
-      </c>
+      <c r="J20" s="92" t="inlineStr"/>
       <c r="K20" s="92" t="inlineStr">
         <is>
-          <t>클러스터 내 대표 기사 1건 표시</t>
+          <t>DedupAgent 가 부여한 동일 이슈 묶음 ID</t>
         </is>
       </c>
     </row>
@@ -3702,12 +3706,12 @@
       <c r="B21" s="91" t="n"/>
       <c r="C21" s="92" t="inlineStr">
         <is>
-          <t>processing_status</t>
+          <t>is_representative</t>
         </is>
       </c>
       <c r="D21" s="92" t="inlineStr">
         <is>
-          <t>처리 상태</t>
+          <t>대표 기사 여부</t>
         </is>
       </c>
       <c r="E21" s="92" t="inlineStr">
@@ -3717,24 +3721,20 @@
       </c>
       <c r="F21" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G21" s="92" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="G21" s="92" t="inlineStr"/>
       <c r="H21" s="92" t="inlineStr"/>
       <c r="I21" s="92" t="inlineStr"/>
       <c r="J21" s="92" t="inlineStr">
         <is>
-          <t>Default 'RAW'</t>
+          <t>Default FALSE</t>
         </is>
       </c>
       <c r="K21" s="92" t="inlineStr">
         <is>
-          <t>RAW · CLUSTERED_REP/DUPE · CLASSIFIED · SKIPPED_QUALITY/CREDIBILITY/ERROR</t>
+          <t>클러스터 내 대표 기사 1건 표시</t>
         </is>
       </c>
     </row>
@@ -3743,12 +3743,12 @@
       <c r="B22" s="91" t="n"/>
       <c r="C22" s="92" t="inlineStr">
         <is>
-          <t>importance_score</t>
+          <t>processing_status</t>
         </is>
       </c>
       <c r="D22" s="92" t="inlineStr">
         <is>
-          <t>중요도 점수</t>
+          <t>처리 상태</t>
         </is>
       </c>
       <c r="E22" s="92" t="inlineStr">
@@ -3758,20 +3758,24 @@
       </c>
       <c r="F22" s="92" t="inlineStr">
         <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="G22" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G22" s="92" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="H22" s="92" t="inlineStr"/>
       <c r="I22" s="92" t="inlineStr"/>
       <c r="J22" s="92" t="inlineStr">
         <is>
-          <t>0.0~1.0</t>
+          <t>Default 'RAW'</t>
         </is>
       </c>
       <c r="K22" s="92" t="inlineStr">
         <is>
-          <t>v3 exposure_score (결정적 산식)</t>
+          <t>RAW · CLUSTERED_REP/DUPE · CLASSIFIED · SKIPPED_QUALITY/CREDIBILITY/ERROR</t>
         </is>
       </c>
     </row>
@@ -3780,12 +3784,12 @@
       <c r="B23" s="91" t="n"/>
       <c r="C23" s="92" t="inlineStr">
         <is>
-          <t>metadata</t>
+          <t>importance_score</t>
         </is>
       </c>
       <c r="D23" s="92" t="inlineStr">
         <is>
-          <t>메타데이터</t>
+          <t>중요도 점수</t>
         </is>
       </c>
       <c r="E23" s="92" t="inlineStr">
@@ -3795,7 +3799,7 @@
       </c>
       <c r="F23" s="92" t="inlineStr">
         <is>
-          <t>JSONB</t>
+          <t>FLOAT</t>
         </is>
       </c>
       <c r="G23" s="92" t="inlineStr"/>
@@ -3803,12 +3807,12 @@
       <c r="I23" s="92" t="inlineStr"/>
       <c r="J23" s="92" t="inlineStr">
         <is>
-          <t>Default '{}'</t>
+          <t>0.0~1.0</t>
         </is>
       </c>
       <c r="K23" s="92" t="inlineStr">
         <is>
-          <t>url_hash · 크롤러별 부가 필드 · image_source_url 임시 보관</t>
+          <t>v3 exposure_score (결정적 산식)</t>
         </is>
       </c>
     </row>
@@ -3817,12 +3821,12 @@
       <c r="B24" s="91" t="n"/>
       <c r="C24" s="92" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>metadata</t>
         </is>
       </c>
       <c r="D24" s="92" t="inlineStr">
         <is>
-          <t>생성 시각</t>
+          <t>메타데이터</t>
         </is>
       </c>
       <c r="E24" s="92" t="inlineStr">
@@ -3832,7 +3836,7 @@
       </c>
       <c r="F24" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>JSONB</t>
         </is>
       </c>
       <c r="G24" s="92" t="inlineStr"/>
@@ -3840,102 +3844,98 @@
       <c r="I24" s="92" t="inlineStr"/>
       <c r="J24" s="92" t="inlineStr">
         <is>
-          <t>Default NOW()</t>
+          <t>Default '{}'</t>
         </is>
       </c>
       <c r="K24" s="92" t="inlineStr">
         <is>
-          <t>row 생성 시각</t>
+          <t>url_hash · 크롤러별 부가 필드 · image_source_url 임시 보관</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="91" t="inlineStr">
-        <is>
-          <t>job_postings</t>
-        </is>
-      </c>
-      <c r="B25" s="91" t="inlineStr">
-        <is>
-          <t>채용공고 스냅샷</t>
-        </is>
-      </c>
+      <c r="A25" s="91" t="n"/>
+      <c r="B25" s="91" t="n"/>
       <c r="C25" s="92" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D25" s="92" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>생성 시각</t>
         </is>
       </c>
       <c r="E25" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F25" s="92" t="inlineStr">
         <is>
-          <t>BIGSERIAL</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="G25" s="92" t="inlineStr"/>
-      <c r="H25" s="92" t="inlineStr">
-        <is>
-          <t>PK1</t>
-        </is>
-      </c>
+      <c r="H25" s="92" t="inlineStr"/>
       <c r="I25" s="92" t="inlineStr"/>
       <c r="J25" s="92" t="inlineStr">
         <is>
+          <t>Default NOW()</t>
+        </is>
+      </c>
+      <c r="K25" s="92" t="inlineStr">
+        <is>
+          <t>row 생성 시각</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="91" t="inlineStr">
+        <is>
+          <t>job_postings</t>
+        </is>
+      </c>
+      <c r="B26" s="91" t="inlineStr">
+        <is>
+          <t>채용공고 스냅샷</t>
+        </is>
+      </c>
+      <c r="C26" s="92" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D26" s="92" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="E26" s="92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F26" s="92" t="inlineStr">
+        <is>
+          <t>BIGSERIAL</t>
+        </is>
+      </c>
+      <c r="G26" s="92" t="inlineStr"/>
+      <c r="H26" s="92" t="inlineStr">
+        <is>
+          <t>PK1</t>
+        </is>
+      </c>
+      <c r="I26" s="92" t="inlineStr"/>
+      <c r="J26" s="92" t="inlineStr">
+        <is>
           <t>AUTO_INCREMENT</t>
         </is>
       </c>
-      <c r="K25" s="92" t="inlineStr">
+      <c r="K26" s="92" t="inlineStr">
         <is>
           <t>row PK</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="91" t="n"/>
-      <c r="B26" s="91" t="n"/>
-      <c r="C26" s="92" t="inlineStr">
-        <is>
-          <t>peer_id</t>
-        </is>
-      </c>
-      <c r="D26" s="92" t="inlineStr">
-        <is>
-          <t>Peer ID</t>
-        </is>
-      </c>
-      <c r="E26" s="92" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F26" s="92" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G26" s="92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H26" s="92" t="inlineStr"/>
-      <c r="I26" s="92" t="inlineStr">
-        <is>
-          <t>peer_companies.id</t>
-        </is>
-      </c>
-      <c r="J26" s="92" t="inlineStr"/>
-      <c r="K26" s="92" t="inlineStr">
-        <is>
-          <t>채용공고가 속한 Peer 회사</t>
         </is>
       </c>
     </row>
@@ -3944,12 +3944,12 @@
       <c r="B27" s="91" t="n"/>
       <c r="C27" s="92" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>peer_id</t>
         </is>
       </c>
       <c r="D27" s="92" t="inlineStr">
         <is>
-          <t>공고 제목</t>
+          <t>Peer ID</t>
         </is>
       </c>
       <c r="E27" s="92" t="inlineStr">
@@ -3959,16 +3959,24 @@
       </c>
       <c r="F27" s="92" t="inlineStr">
         <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="G27" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G27" s="92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="H27" s="92" t="inlineStr"/>
-      <c r="I27" s="92" t="inlineStr"/>
+      <c r="I27" s="92" t="inlineStr">
+        <is>
+          <t>peer_companies.id</t>
+        </is>
+      </c>
       <c r="J27" s="92" t="inlineStr"/>
       <c r="K27" s="92" t="inlineStr">
         <is>
-          <t>채용공고 제목</t>
+          <t>채용공고가 속한 Peer 회사</t>
         </is>
       </c>
     </row>
@@ -3977,35 +3985,31 @@
       <c r="B28" s="91" t="n"/>
       <c r="C28" s="92" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>job_title</t>
         </is>
       </c>
       <c r="D28" s="92" t="inlineStr">
         <is>
-          <t>부서</t>
+          <t>공고 제목</t>
         </is>
       </c>
       <c r="E28" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F28" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G28" s="92" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="G28" s="92" t="inlineStr"/>
       <c r="H28" s="92" t="inlineStr"/>
       <c r="I28" s="92" t="inlineStr"/>
       <c r="J28" s="92" t="inlineStr"/>
       <c r="K28" s="92" t="inlineStr">
         <is>
-          <t>공고된 부서 (옵션)</t>
+          <t>채용공고 제목</t>
         </is>
       </c>
     </row>
@@ -4014,12 +4018,12 @@
       <c r="B29" s="91" t="n"/>
       <c r="C29" s="92" t="inlineStr">
         <is>
-          <t>tech_stack</t>
+          <t>department</t>
         </is>
       </c>
       <c r="D29" s="92" t="inlineStr">
         <is>
-          <t>기술 스택</t>
+          <t>부서</t>
         </is>
       </c>
       <c r="E29" s="92" t="inlineStr">
@@ -4029,20 +4033,20 @@
       </c>
       <c r="F29" s="92" t="inlineStr">
         <is>
-          <t>TEXT[]</t>
-        </is>
-      </c>
-      <c r="G29" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G29" s="92" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="H29" s="92" t="inlineStr"/>
       <c r="I29" s="92" t="inlineStr"/>
-      <c r="J29" s="92" t="inlineStr">
-        <is>
-          <t>Default '{}'</t>
-        </is>
-      </c>
+      <c r="J29" s="92" t="inlineStr"/>
       <c r="K29" s="92" t="inlineStr">
         <is>
-          <t>추출한 기술 키워드 배열</t>
+          <t>공고된 부서 (옵션)</t>
         </is>
       </c>
     </row>
@@ -4051,22 +4055,22 @@
       <c r="B30" s="91" t="n"/>
       <c r="C30" s="92" t="inlineStr">
         <is>
-          <t>snapshot_week</t>
+          <t>tech_stack</t>
         </is>
       </c>
       <c r="D30" s="92" t="inlineStr">
         <is>
-          <t>스냅샷 주</t>
+          <t>기술 스택</t>
         </is>
       </c>
       <c r="E30" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F30" s="92" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>TEXT[]</t>
         </is>
       </c>
       <c r="G30" s="92" t="inlineStr"/>
@@ -4074,12 +4078,12 @@
       <c r="I30" s="92" t="inlineStr"/>
       <c r="J30" s="92" t="inlineStr">
         <is>
-          <t>월요일 기준</t>
+          <t>Default '{}'</t>
         </is>
       </c>
       <c r="K30" s="92" t="inlineStr">
         <is>
-          <t>주간 스냅샷 기준일 (월요일)</t>
+          <t>추출한 기술 키워드 배열</t>
         </is>
       </c>
     </row>
@@ -4088,22 +4092,22 @@
       <c r="B31" s="91" t="n"/>
       <c r="C31" s="92" t="inlineStr">
         <is>
-          <t>is_new</t>
+          <t>snapshot_week</t>
         </is>
       </c>
       <c r="D31" s="92" t="inlineStr">
         <is>
-          <t>신규 여부</t>
+          <t>스냅샷 주</t>
         </is>
       </c>
       <c r="E31" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F31" s="92" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="G31" s="92" t="inlineStr"/>
@@ -4111,12 +4115,12 @@
       <c r="I31" s="92" t="inlineStr"/>
       <c r="J31" s="92" t="inlineStr">
         <is>
-          <t>Default TRUE</t>
+          <t>월요일 기준</t>
         </is>
       </c>
       <c r="K31" s="92" t="inlineStr">
         <is>
-          <t>이전 주 대비 신규 등장 여부</t>
+          <t>주간 스냅샷 기준일 (월요일)</t>
         </is>
       </c>
     </row>
@@ -4125,12 +4129,12 @@
       <c r="B32" s="91" t="n"/>
       <c r="C32" s="92" t="inlineStr">
         <is>
-          <t>url</t>
+          <t>is_new</t>
         </is>
       </c>
       <c r="D32" s="92" t="inlineStr">
         <is>
-          <t>공고 URL</t>
+          <t>신규 여부</t>
         </is>
       </c>
       <c r="E32" s="92" t="inlineStr">
@@ -4140,16 +4144,20 @@
       </c>
       <c r="F32" s="92" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="G32" s="92" t="inlineStr"/>
       <c r="H32" s="92" t="inlineStr"/>
       <c r="I32" s="92" t="inlineStr"/>
-      <c r="J32" s="92" t="inlineStr"/>
+      <c r="J32" s="92" t="inlineStr">
+        <is>
+          <t>Default TRUE</t>
+        </is>
+      </c>
       <c r="K32" s="92" t="inlineStr">
         <is>
-          <t>원본 URL</t>
+          <t>이전 주 대비 신규 등장 여부</t>
         </is>
       </c>
     </row>
@@ -4158,12 +4166,12 @@
       <c r="B33" s="91" t="n"/>
       <c r="C33" s="92" t="inlineStr">
         <is>
-          <t>collected_at</t>
+          <t>url</t>
         </is>
       </c>
       <c r="D33" s="92" t="inlineStr">
         <is>
-          <t>수집 시각</t>
+          <t>공고 URL</t>
         </is>
       </c>
       <c r="E33" s="92" t="inlineStr">
@@ -4173,114 +4181,102 @@
       </c>
       <c r="F33" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="G33" s="92" t="inlineStr"/>
       <c r="H33" s="92" t="inlineStr"/>
       <c r="I33" s="92" t="inlineStr"/>
-      <c r="J33" s="92" t="inlineStr">
-        <is>
-          <t>Default NOW()</t>
-        </is>
-      </c>
+      <c r="J33" s="92" t="inlineStr"/>
       <c r="K33" s="92" t="inlineStr">
         <is>
+          <t>원본 URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="91" t="n"/>
+      <c r="B34" s="91" t="n"/>
+      <c r="C34" s="92" t="inlineStr">
+        <is>
+          <t>collected_at</t>
+        </is>
+      </c>
+      <c r="D34" s="92" t="inlineStr">
+        <is>
           <t>수집 시각</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="91" t="inlineStr">
-        <is>
-          <t>peer_financials</t>
-        </is>
-      </c>
-      <c r="B34" s="91" t="inlineStr">
-        <is>
-          <t>Peer 분기·연간 재무</t>
-        </is>
-      </c>
-      <c r="C34" s="92" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="D34" s="92" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
       <c r="E34" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F34" s="92" t="inlineStr">
         <is>
-          <t>BIGSERIAL</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="G34" s="92" t="inlineStr"/>
-      <c r="H34" s="92" t="inlineStr">
-        <is>
-          <t>PK1</t>
-        </is>
-      </c>
+      <c r="H34" s="92" t="inlineStr"/>
       <c r="I34" s="92" t="inlineStr"/>
       <c r="J34" s="92" t="inlineStr">
         <is>
+          <t>Default NOW()</t>
+        </is>
+      </c>
+      <c r="K34" s="92" t="inlineStr">
+        <is>
+          <t>수집 시각</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="91" t="inlineStr">
+        <is>
+          <t>peer_financials</t>
+        </is>
+      </c>
+      <c r="B35" s="91" t="inlineStr">
+        <is>
+          <t>Peer 분기·연간 재무</t>
+        </is>
+      </c>
+      <c r="C35" s="92" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D35" s="92" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="E35" s="92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F35" s="92" t="inlineStr">
+        <is>
+          <t>BIGSERIAL</t>
+        </is>
+      </c>
+      <c r="G35" s="92" t="inlineStr"/>
+      <c r="H35" s="92" t="inlineStr">
+        <is>
+          <t>PK1</t>
+        </is>
+      </c>
+      <c r="I35" s="92" t="inlineStr"/>
+      <c r="J35" s="92" t="inlineStr">
+        <is>
           <t>AUTO_INCREMENT</t>
         </is>
       </c>
-      <c r="K34" s="92" t="inlineStr">
+      <c r="K35" s="92" t="inlineStr">
         <is>
           <t>row PK</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="91" t="n"/>
-      <c r="B35" s="91" t="n"/>
-      <c r="C35" s="92" t="inlineStr">
-        <is>
-          <t>peer_id</t>
-        </is>
-      </c>
-      <c r="D35" s="92" t="inlineStr">
-        <is>
-          <t>Peer ID</t>
-        </is>
-      </c>
-      <c r="E35" s="92" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F35" s="92" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G35" s="92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H35" s="92" t="inlineStr"/>
-      <c r="I35" s="92" t="inlineStr">
-        <is>
-          <t>peer_companies.id</t>
-        </is>
-      </c>
-      <c r="J35" s="92" t="inlineStr">
-        <is>
-          <t>UNIQUE(peer_id, period)</t>
-        </is>
-      </c>
-      <c r="K35" s="92" t="inlineStr">
-        <is>
-          <t>재무 데이터 소속 Peer 회사</t>
         </is>
       </c>
     </row>
@@ -4289,12 +4285,12 @@
       <c r="B36" s="91" t="n"/>
       <c r="C36" s="92" t="inlineStr">
         <is>
-          <t>period</t>
+          <t>peer_id</t>
         </is>
       </c>
       <c r="D36" s="92" t="inlineStr">
         <is>
-          <t>보고 기간</t>
+          <t>Peer ID</t>
         </is>
       </c>
       <c r="E36" s="92" t="inlineStr">
@@ -4309,19 +4305,23 @@
       </c>
       <c r="G36" s="92" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H36" s="92" t="inlineStr"/>
-      <c r="I36" s="92" t="inlineStr"/>
+      <c r="I36" s="92" t="inlineStr">
+        <is>
+          <t>peer_companies.id</t>
+        </is>
+      </c>
       <c r="J36" s="92" t="inlineStr">
         <is>
-          <t>예: '2026Q1'</t>
+          <t>UNIQUE(peer_id, period)</t>
         </is>
       </c>
       <c r="K36" s="92" t="inlineStr">
         <is>
-          <t>분기·연간 식별 (YYYYQn 또는 YYYY)</t>
+          <t>재무 데이터 소속 Peer 회사</t>
         </is>
       </c>
     </row>
@@ -4330,31 +4330,39 @@
       <c r="B37" s="91" t="n"/>
       <c r="C37" s="92" t="inlineStr">
         <is>
-          <t>report_date</t>
+          <t>period</t>
         </is>
       </c>
       <c r="D37" s="92" t="inlineStr">
         <is>
-          <t>공시일</t>
+          <t>보고 기간</t>
         </is>
       </c>
       <c r="E37" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F37" s="92" t="inlineStr">
         <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="G37" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G37" s="92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="H37" s="92" t="inlineStr"/>
       <c r="I37" s="92" t="inlineStr"/>
-      <c r="J37" s="92" t="inlineStr"/>
+      <c r="J37" s="92" t="inlineStr">
+        <is>
+          <t>예: '2026Q1'</t>
+        </is>
+      </c>
       <c r="K37" s="92" t="inlineStr">
         <is>
-          <t>DART 공시·발표일</t>
+          <t>분기·연간 식별 (YYYYQn 또는 YYYY)</t>
         </is>
       </c>
     </row>
@@ -4363,12 +4371,12 @@
       <c r="B38" s="91" t="n"/>
       <c r="C38" s="92" t="inlineStr">
         <is>
-          <t>dart_rcept_no</t>
+          <t>report_date</t>
         </is>
       </c>
       <c r="D38" s="92" t="inlineStr">
         <is>
-          <t>DART 공시번호</t>
+          <t>공시일</t>
         </is>
       </c>
       <c r="E38" s="92" t="inlineStr">
@@ -4378,20 +4386,16 @@
       </c>
       <c r="F38" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G38" s="92" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="G38" s="92" t="inlineStr"/>
       <c r="H38" s="92" t="inlineStr"/>
       <c r="I38" s="92" t="inlineStr"/>
       <c r="J38" s="92" t="inlineStr"/>
       <c r="K38" s="92" t="inlineStr">
         <is>
-          <t>DART 접수번호 (검증 추적)</t>
+          <t>DART 공시·발표일</t>
         </is>
       </c>
     </row>
@@ -4400,12 +4404,12 @@
       <c r="B39" s="91" t="n"/>
       <c r="C39" s="92" t="inlineStr">
         <is>
-          <t>ir_page</t>
+          <t>dart_rcept_no</t>
         </is>
       </c>
       <c r="D39" s="92" t="inlineStr">
         <is>
-          <t>IR 페이지</t>
+          <t>DART 공시번호</t>
         </is>
       </c>
       <c r="E39" s="92" t="inlineStr">
@@ -4415,16 +4419,20 @@
       </c>
       <c r="F39" s="92" t="inlineStr">
         <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="G39" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G39" s="92" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="H39" s="92" t="inlineStr"/>
       <c r="I39" s="92" t="inlineStr"/>
       <c r="J39" s="92" t="inlineStr"/>
       <c r="K39" s="92" t="inlineStr">
         <is>
-          <t>IR PDF 의 페이지 번호</t>
+          <t>DART 접수번호 (검증 추적)</t>
         </is>
       </c>
     </row>
@@ -4433,12 +4441,12 @@
       <c r="B40" s="91" t="n"/>
       <c r="C40" s="92" t="inlineStr">
         <is>
-          <t>revenue_total_krwbn</t>
+          <t>ir_page</t>
         </is>
       </c>
       <c r="D40" s="92" t="inlineStr">
         <is>
-          <t>총 매출 (억원)</t>
+          <t>IR 페이지</t>
         </is>
       </c>
       <c r="E40" s="92" t="inlineStr">
@@ -4448,20 +4456,16 @@
       </c>
       <c r="F40" s="92" t="inlineStr">
         <is>
-          <t>FLOAT</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="G40" s="92" t="inlineStr"/>
       <c r="H40" s="92" t="inlineStr"/>
       <c r="I40" s="92" t="inlineStr"/>
-      <c r="J40" s="92" t="inlineStr">
-        <is>
-          <t>단위: 억원</t>
-        </is>
-      </c>
+      <c r="J40" s="92" t="inlineStr"/>
       <c r="K40" s="92" t="inlineStr">
         <is>
-          <t>분기·연간 전체 매출</t>
+          <t>IR PDF 의 페이지 번호</t>
         </is>
       </c>
     </row>
@@ -4470,12 +4474,12 @@
       <c r="B41" s="91" t="n"/>
       <c r="C41" s="92" t="inlineStr">
         <is>
-          <t>operating_profit_krwbn</t>
+          <t>revenue_total_krwbn</t>
         </is>
       </c>
       <c r="D41" s="92" t="inlineStr">
         <is>
-          <t>영업이익 (억원)</t>
+          <t>총 매출 (억원)</t>
         </is>
       </c>
       <c r="E41" s="92" t="inlineStr">
@@ -4498,7 +4502,7 @@
       </c>
       <c r="K41" s="92" t="inlineStr">
         <is>
-          <t>영업이익</t>
+          <t>분기·연간 전체 매출</t>
         </is>
       </c>
     </row>
@@ -4507,12 +4511,12 @@
       <c r="B42" s="91" t="n"/>
       <c r="C42" s="92" t="inlineStr">
         <is>
-          <t>segment_revenue</t>
+          <t>operating_profit_krwbn</t>
         </is>
       </c>
       <c r="D42" s="92" t="inlineStr">
         <is>
-          <t>사업부 매출</t>
+          <t>영업이익 (억원)</t>
         </is>
       </c>
       <c r="E42" s="92" t="inlineStr">
@@ -4522,7 +4526,7 @@
       </c>
       <c r="F42" s="92" t="inlineStr">
         <is>
-          <t>JSONB</t>
+          <t>FLOAT</t>
         </is>
       </c>
       <c r="G42" s="92" t="inlineStr"/>
@@ -4530,12 +4534,12 @@
       <c r="I42" s="92" t="inlineStr"/>
       <c r="J42" s="92" t="inlineStr">
         <is>
-          <t>Default '{}'</t>
+          <t>단위: 억원</t>
         </is>
       </c>
       <c r="K42" s="92" t="inlineStr">
         <is>
-          <t>{segment_id: 매출_억원}</t>
+          <t>영업이익</t>
         </is>
       </c>
     </row>
@@ -4544,12 +4548,12 @@
       <c r="B43" s="91" t="n"/>
       <c r="C43" s="92" t="inlineStr">
         <is>
-          <t>ai_revenue_share_pct</t>
+          <t>segment_revenue</t>
         </is>
       </c>
       <c r="D43" s="92" t="inlineStr">
         <is>
-          <t>AI 매출 비중 (%)</t>
+          <t>사업부 매출</t>
         </is>
       </c>
       <c r="E43" s="92" t="inlineStr">
@@ -4559,7 +4563,7 @@
       </c>
       <c r="F43" s="92" t="inlineStr">
         <is>
-          <t>FLOAT</t>
+          <t>JSONB</t>
         </is>
       </c>
       <c r="G43" s="92" t="inlineStr"/>
@@ -4567,12 +4571,12 @@
       <c r="I43" s="92" t="inlineStr"/>
       <c r="J43" s="92" t="inlineStr">
         <is>
-          <t>0~100</t>
+          <t>Default '{}'</t>
         </is>
       </c>
       <c r="K43" s="92" t="inlineStr">
         <is>
-          <t>AI 사업 매출 비중</t>
+          <t>{segment_id: 매출_억원}</t>
         </is>
       </c>
     </row>
@@ -4581,12 +4585,12 @@
       <c r="B44" s="91" t="n"/>
       <c r="C44" s="92" t="inlineStr">
         <is>
-          <t>headcount</t>
+          <t>ai_revenue_share_pct</t>
         </is>
       </c>
       <c r="D44" s="92" t="inlineStr">
         <is>
-          <t>인력 현황</t>
+          <t>AI 매출 비중 (%)</t>
         </is>
       </c>
       <c r="E44" s="92" t="inlineStr">
@@ -4596,7 +4600,7 @@
       </c>
       <c r="F44" s="92" t="inlineStr">
         <is>
-          <t>JSONB</t>
+          <t>FLOAT</t>
         </is>
       </c>
       <c r="G44" s="92" t="inlineStr"/>
@@ -4604,12 +4608,12 @@
       <c r="I44" s="92" t="inlineStr"/>
       <c r="J44" s="92" t="inlineStr">
         <is>
-          <t>Default '{}'</t>
+          <t>0~100</t>
         </is>
       </c>
       <c r="K44" s="92" t="inlineStr">
         <is>
-          <t>{total, rd, ai_engineers_est}</t>
+          <t>AI 사업 매출 비중</t>
         </is>
       </c>
     </row>
@@ -4618,12 +4622,12 @@
       <c r="B45" s="91" t="n"/>
       <c r="C45" s="92" t="inlineStr">
         <is>
-          <t>raw_payload</t>
+          <t>headcount</t>
         </is>
       </c>
       <c r="D45" s="92" t="inlineStr">
         <is>
-          <t>원본 페이로드</t>
+          <t>인력 현황</t>
         </is>
       </c>
       <c r="E45" s="92" t="inlineStr">
@@ -4639,10 +4643,14 @@
       <c r="G45" s="92" t="inlineStr"/>
       <c r="H45" s="92" t="inlineStr"/>
       <c r="I45" s="92" t="inlineStr"/>
-      <c r="J45" s="92" t="inlineStr"/>
+      <c r="J45" s="92" t="inlineStr">
+        <is>
+          <t>Default '{}'</t>
+        </is>
+      </c>
       <c r="K45" s="92" t="inlineStr">
         <is>
-          <t>IRParserAgent 후처리 결과</t>
+          <t>{total, rd, ai_engineers_est}</t>
         </is>
       </c>
     </row>
@@ -4651,12 +4659,12 @@
       <c r="B46" s="91" t="n"/>
       <c r="C46" s="92" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>raw_payload</t>
         </is>
       </c>
       <c r="D46" s="92" t="inlineStr">
         <is>
-          <t>데이터 출처</t>
+          <t>원본 페이로드</t>
         </is>
       </c>
       <c r="E46" s="92" t="inlineStr">
@@ -4666,24 +4674,16 @@
       </c>
       <c r="F46" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G46" s="92" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>JSONB</t>
+        </is>
+      </c>
+      <c r="G46" s="92" t="inlineStr"/>
       <c r="H46" s="92" t="inlineStr"/>
       <c r="I46" s="92" t="inlineStr"/>
-      <c r="J46" s="92" t="inlineStr">
-        <is>
-          <t>Default 'stub_v0'</t>
-        </is>
-      </c>
+      <c r="J46" s="92" t="inlineStr"/>
       <c r="K46" s="92" t="inlineStr">
         <is>
-          <t>stub_v0 | dart | ir_pdf | manual</t>
+          <t>IRParserAgent 후처리 결과</t>
         </is>
       </c>
     </row>
@@ -4692,12 +4692,12 @@
       <c r="B47" s="91" t="n"/>
       <c r="C47" s="92" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>source</t>
         </is>
       </c>
       <c r="D47" s="92" t="inlineStr">
         <is>
-          <t>생성 시각</t>
+          <t>데이터 출처</t>
         </is>
       </c>
       <c r="E47" s="92" t="inlineStr">
@@ -4707,83 +4707,83 @@
       </c>
       <c r="F47" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
-        </is>
-      </c>
-      <c r="G47" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G47" s="92" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="H47" s="92" t="inlineStr"/>
       <c r="I47" s="92" t="inlineStr"/>
       <c r="J47" s="92" t="inlineStr">
         <is>
-          <t>Default NOW()</t>
+          <t>Default 'stub_v0'</t>
         </is>
       </c>
       <c r="K47" s="92" t="inlineStr">
         <is>
-          <t>row 생성 시각</t>
+          <t>stub_v0 | dart | ir_pdf | manual</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="91" t="inlineStr">
-        <is>
-          <t>mbb_baseline</t>
-        </is>
-      </c>
-      <c r="B48" s="91" t="inlineStr">
-        <is>
-          <t>컨설팅 보고서 baseline</t>
-        </is>
-      </c>
+      <c r="A48" s="91" t="n"/>
+      <c r="B48" s="91" t="n"/>
       <c r="C48" s="92" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D48" s="92" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>생성 시각</t>
         </is>
       </c>
       <c r="E48" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F48" s="92" t="inlineStr">
         <is>
-          <t>BIGSERIAL</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="G48" s="92" t="inlineStr"/>
-      <c r="H48" s="92" t="inlineStr">
-        <is>
-          <t>PK1</t>
-        </is>
-      </c>
+      <c r="H48" s="92" t="inlineStr"/>
       <c r="I48" s="92" t="inlineStr"/>
       <c r="J48" s="92" t="inlineStr">
         <is>
-          <t>AUTO_INCREMENT</t>
+          <t>Default NOW()</t>
         </is>
       </c>
       <c r="K48" s="92" t="inlineStr">
         <is>
-          <t>row PK</t>
+          <t>row 생성 시각</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="91" t="n"/>
-      <c r="B49" s="91" t="n"/>
+      <c r="A49" s="91" t="inlineStr">
+        <is>
+          <t>mbb_baseline</t>
+        </is>
+      </c>
+      <c r="B49" s="91" t="inlineStr">
+        <is>
+          <t>컨설팅 보고서 baseline</t>
+        </is>
+      </c>
       <c r="C49" s="92" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D49" s="92" t="inlineStr">
         <is>
-          <t>발행처</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E49" s="92" t="inlineStr">
@@ -4793,24 +4793,24 @@
       </c>
       <c r="F49" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G49" s="92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H49" s="92" t="inlineStr"/>
+          <t>BIGSERIAL</t>
+        </is>
+      </c>
+      <c r="G49" s="92" t="inlineStr"/>
+      <c r="H49" s="92" t="inlineStr">
+        <is>
+          <t>PK1</t>
+        </is>
+      </c>
       <c r="I49" s="92" t="inlineStr"/>
       <c r="J49" s="92" t="inlineStr">
         <is>
-          <t>McKinsey|BCG|Bain|Kearney|...</t>
+          <t>AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="K49" s="92" t="inlineStr">
         <is>
-          <t>컨설팅사 이름</t>
+          <t>row PK</t>
         </is>
       </c>
     </row>
@@ -4819,17 +4819,17 @@
       <c r="B50" s="91" t="n"/>
       <c r="C50" s="92" t="inlineStr">
         <is>
-          <t>report_id</t>
+          <t>source</t>
         </is>
       </c>
       <c r="D50" s="92" t="inlineStr">
         <is>
-          <t>보고서 ID</t>
+          <t>발행처</t>
         </is>
       </c>
       <c r="E50" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F50" s="92" t="inlineStr">
@@ -4839,15 +4839,19 @@
       </c>
       <c r="G50" s="92" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H50" s="92" t="inlineStr"/>
       <c r="I50" s="92" t="inlineStr"/>
-      <c r="J50" s="92" t="inlineStr"/>
+      <c r="J50" s="92" t="inlineStr">
+        <is>
+          <t>McKinsey|BCG|Bain|Kearney|...</t>
+        </is>
+      </c>
       <c r="K50" s="92" t="inlineStr">
         <is>
-          <t>발행처 내부 식별자</t>
+          <t>컨설팅사 이름</t>
         </is>
       </c>
     </row>
@@ -4856,31 +4860,35 @@
       <c r="B51" s="91" t="n"/>
       <c r="C51" s="92" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>report_id</t>
         </is>
       </c>
       <c r="D51" s="92" t="inlineStr">
         <is>
-          <t>제목</t>
+          <t>보고서 ID</t>
         </is>
       </c>
       <c r="E51" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F51" s="92" t="inlineStr">
         <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="G51" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G51" s="92" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="H51" s="92" t="inlineStr"/>
       <c r="I51" s="92" t="inlineStr"/>
       <c r="J51" s="92" t="inlineStr"/>
       <c r="K51" s="92" t="inlineStr">
         <is>
-          <t>보고서 제목</t>
+          <t>발행처 내부 식별자</t>
         </is>
       </c>
     </row>
@@ -4889,22 +4897,22 @@
       <c r="B52" s="91" t="n"/>
       <c r="C52" s="92" t="inlineStr">
         <is>
-          <t>published_date</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D52" s="92" t="inlineStr">
         <is>
-          <t>발행일</t>
+          <t>제목</t>
         </is>
       </c>
       <c r="E52" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F52" s="92" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="G52" s="92" t="inlineStr"/>
@@ -4913,7 +4921,7 @@
       <c r="J52" s="92" t="inlineStr"/>
       <c r="K52" s="92" t="inlineStr">
         <is>
-          <t>원문 발행일</t>
+          <t>보고서 제목</t>
         </is>
       </c>
     </row>
@@ -4922,12 +4930,12 @@
       <c r="B53" s="91" t="n"/>
       <c r="C53" s="92" t="inlineStr">
         <is>
-          <t>url</t>
+          <t>published_date</t>
         </is>
       </c>
       <c r="D53" s="92" t="inlineStr">
         <is>
-          <t>원문 URL</t>
+          <t>발행일</t>
         </is>
       </c>
       <c r="E53" s="92" t="inlineStr">
@@ -4937,7 +4945,7 @@
       </c>
       <c r="F53" s="92" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="G53" s="92" t="inlineStr"/>
@@ -4946,7 +4954,7 @@
       <c r="J53" s="92" t="inlineStr"/>
       <c r="K53" s="92" t="inlineStr">
         <is>
-          <t>원문 URL (PDF · 웹 페이지)</t>
+          <t>원문 발행일</t>
         </is>
       </c>
     </row>
@@ -4955,12 +4963,12 @@
       <c r="B54" s="91" t="n"/>
       <c r="C54" s="92" t="inlineStr">
         <is>
-          <t>summary</t>
+          <t>url</t>
         </is>
       </c>
       <c r="D54" s="92" t="inlineStr">
         <is>
-          <t>요약</t>
+          <t>원문 URL</t>
         </is>
       </c>
       <c r="E54" s="92" t="inlineStr">
@@ -4979,7 +4987,7 @@
       <c r="J54" s="92" t="inlineStr"/>
       <c r="K54" s="92" t="inlineStr">
         <is>
-          <t>보고서 핵심 요약 (운영자 입력 또는 AI 생성)</t>
+          <t>원문 URL (PDF · 웹 페이지)</t>
         </is>
       </c>
     </row>
@@ -4988,12 +4996,12 @@
       <c r="B55" s="91" t="n"/>
       <c r="C55" s="92" t="inlineStr">
         <is>
-          <t>sectors</t>
+          <t>summary</t>
         </is>
       </c>
       <c r="D55" s="92" t="inlineStr">
         <is>
-          <t>섹터 배열</t>
+          <t>요약</t>
         </is>
       </c>
       <c r="E55" s="92" t="inlineStr">
@@ -5003,20 +5011,16 @@
       </c>
       <c r="F55" s="92" t="inlineStr">
         <is>
-          <t>TEXT[]</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="G55" s="92" t="inlineStr"/>
       <c r="H55" s="92" t="inlineStr"/>
       <c r="I55" s="92" t="inlineStr"/>
-      <c r="J55" s="92" t="inlineStr">
-        <is>
-          <t>Default '{}'</t>
-        </is>
-      </c>
+      <c r="J55" s="92" t="inlineStr"/>
       <c r="K55" s="92" t="inlineStr">
         <is>
-          <t>['ai_tech', 'security'] 등</t>
+          <t>보고서 핵심 요약 (운영자 입력 또는 AI 생성)</t>
         </is>
       </c>
     </row>
@@ -5025,12 +5029,12 @@
       <c r="B56" s="91" t="n"/>
       <c r="C56" s="92" t="inlineStr">
         <is>
-          <t>keywords</t>
+          <t>sectors</t>
         </is>
       </c>
       <c r="D56" s="92" t="inlineStr">
         <is>
-          <t>키워드 배열</t>
+          <t>섹터 배열</t>
         </is>
       </c>
       <c r="E56" s="92" t="inlineStr">
@@ -5053,7 +5057,7 @@
       </c>
       <c r="K56" s="92" t="inlineStr">
         <is>
-          <t>EvidenceAgent 매칭용 키워드</t>
+          <t>['ai_tech', 'security'] 등</t>
         </is>
       </c>
     </row>
@@ -5062,12 +5066,12 @@
       <c r="B57" s="91" t="n"/>
       <c r="C57" s="92" t="inlineStr">
         <is>
-          <t>raw_payload</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="D57" s="92" t="inlineStr">
         <is>
-          <t>원본 페이로드</t>
+          <t>키워드 배열</t>
         </is>
       </c>
       <c r="E57" s="92" t="inlineStr">
@@ -5077,7 +5081,7 @@
       </c>
       <c r="F57" s="92" t="inlineStr">
         <is>
-          <t>JSONB</t>
+          <t>TEXT[]</t>
         </is>
       </c>
       <c r="G57" s="92" t="inlineStr"/>
@@ -5090,7 +5094,7 @@
       </c>
       <c r="K57" s="92" t="inlineStr">
         <is>
-          <t>추가 메타 (저자 · 페이지 수 등)</t>
+          <t>EvidenceAgent 매칭용 키워드</t>
         </is>
       </c>
     </row>
@@ -5099,12 +5103,12 @@
       <c r="B58" s="91" t="n"/>
       <c r="C58" s="92" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>raw_payload</t>
         </is>
       </c>
       <c r="D58" s="92" t="inlineStr">
         <is>
-          <t>활성 여부</t>
+          <t>원본 페이로드</t>
         </is>
       </c>
       <c r="E58" s="92" t="inlineStr">
@@ -5114,7 +5118,7 @@
       </c>
       <c r="F58" s="92" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>JSONB</t>
         </is>
       </c>
       <c r="G58" s="92" t="inlineStr"/>
@@ -5122,12 +5126,12 @@
       <c r="I58" s="92" t="inlineStr"/>
       <c r="J58" s="92" t="inlineStr">
         <is>
-          <t>Default TRUE</t>
+          <t>Default '{}'</t>
         </is>
       </c>
       <c r="K58" s="92" t="inlineStr">
         <is>
-          <t>현재 매칭 대상 여부</t>
+          <t>추가 메타 (저자 · 페이지 수 등)</t>
         </is>
       </c>
     </row>
@@ -5136,12 +5140,12 @@
       <c r="B59" s="91" t="n"/>
       <c r="C59" s="92" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>is_active</t>
         </is>
       </c>
       <c r="D59" s="92" t="inlineStr">
         <is>
-          <t>생성 시각</t>
+          <t>활성 여부</t>
         </is>
       </c>
       <c r="E59" s="92" t="inlineStr">
@@ -5151,7 +5155,7 @@
       </c>
       <c r="F59" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="G59" s="92" t="inlineStr"/>
@@ -5159,106 +5163,102 @@
       <c r="I59" s="92" t="inlineStr"/>
       <c r="J59" s="92" t="inlineStr">
         <is>
-          <t>Default NOW()</t>
+          <t>Default TRUE</t>
         </is>
       </c>
       <c r="K59" s="92" t="inlineStr">
         <is>
-          <t>row 생성 시각</t>
+          <t>현재 매칭 대상 여부</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="91" t="inlineStr">
-        <is>
-          <t>issue_cards</t>
-        </is>
-      </c>
-      <c r="B60" s="91" t="inlineStr">
-        <is>
-          <t>동향 카드</t>
-        </is>
-      </c>
+      <c r="A60" s="91" t="n"/>
+      <c r="B60" s="91" t="n"/>
       <c r="C60" s="92" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D60" s="92" t="inlineStr">
         <is>
-          <t>카드 ID</t>
+          <t>생성 시각</t>
         </is>
       </c>
       <c r="E60" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F60" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G60" s="92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H60" s="92" t="inlineStr">
-        <is>
-          <t>PK1</t>
-        </is>
-      </c>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="G60" s="92" t="inlineStr"/>
+      <c r="H60" s="92" t="inlineStr"/>
       <c r="I60" s="92" t="inlineStr"/>
       <c r="J60" s="92" t="inlineStr">
         <is>
+          <t>Default NOW()</t>
+        </is>
+      </c>
+      <c r="K60" s="92" t="inlineStr">
+        <is>
+          <t>row 생성 시각</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="91" t="inlineStr">
+        <is>
+          <t>issue_cards</t>
+        </is>
+      </c>
+      <c r="B61" s="91" t="inlineStr">
+        <is>
+          <t>동향 카드</t>
+        </is>
+      </c>
+      <c r="C61" s="92" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D61" s="92" t="inlineStr">
+        <is>
+          <t>카드 ID</t>
+        </is>
+      </c>
+      <c r="E61" s="92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F61" s="92" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G61" s="92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H61" s="92" t="inlineStr">
+        <is>
+          <t>PK1</t>
+        </is>
+      </c>
+      <c r="I61" s="92" t="inlineStr"/>
+      <c r="J61" s="92" t="inlineStr">
+        <is>
           <t>IC-YYYYMMDD-NNN</t>
         </is>
       </c>
-      <c r="K60" s="92" t="inlineStr">
+      <c r="K61" s="92" t="inlineStr">
         <is>
           <t>카드 식별자 (날짜+순번)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="91" t="n"/>
-      <c r="B61" s="91" t="n"/>
-      <c r="C61" s="92" t="inlineStr">
-        <is>
-          <t>peer_id</t>
-        </is>
-      </c>
-      <c r="D61" s="92" t="inlineStr">
-        <is>
-          <t>Peer ID</t>
-        </is>
-      </c>
-      <c r="E61" s="92" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F61" s="92" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G61" s="92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H61" s="92" t="inlineStr"/>
-      <c r="I61" s="92" t="inlineStr">
-        <is>
-          <t>peer_companies.id</t>
-        </is>
-      </c>
-      <c r="J61" s="92" t="inlineStr"/>
-      <c r="K61" s="92" t="inlineStr">
-        <is>
-          <t>카드가 속한 Peer 회사</t>
         </is>
       </c>
     </row>
@@ -5267,31 +5267,39 @@
       <c r="B62" s="91" t="n"/>
       <c r="C62" s="92" t="inlineStr">
         <is>
-          <t>cluster_id</t>
+          <t>peer_id</t>
         </is>
       </c>
       <c r="D62" s="92" t="inlineStr">
         <is>
-          <t>클러스터 ID</t>
+          <t>Peer ID</t>
         </is>
       </c>
       <c r="E62" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F62" s="92" t="inlineStr">
         <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="G62" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G62" s="92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="H62" s="92" t="inlineStr"/>
-      <c r="I62" s="92" t="inlineStr"/>
+      <c r="I62" s="92" t="inlineStr">
+        <is>
+          <t>peer_companies.id</t>
+        </is>
+      </c>
       <c r="J62" s="92" t="inlineStr"/>
       <c r="K62" s="92" t="inlineStr">
         <is>
-          <t>raw_articles 의 cluster_id 와 매칭</t>
+          <t>카드가 속한 Peer 회사</t>
         </is>
       </c>
     </row>
@@ -5300,35 +5308,31 @@
       <c r="B63" s="91" t="n"/>
       <c r="C63" s="92" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>cluster_id</t>
         </is>
       </c>
       <c r="D63" s="92" t="inlineStr">
         <is>
-          <t>카드 제목</t>
+          <t>클러스터 ID</t>
         </is>
       </c>
       <c r="E63" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F63" s="92" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="G63" s="92" t="inlineStr"/>
       <c r="H63" s="92" t="inlineStr"/>
       <c r="I63" s="92" t="inlineStr"/>
-      <c r="J63" s="92" t="inlineStr">
-        <is>
-          <t>≤500자</t>
-        </is>
-      </c>
+      <c r="J63" s="92" t="inlineStr"/>
       <c r="K63" s="92" t="inlineStr">
         <is>
-          <t>AI 가 생성한 카드 제목</t>
+          <t>raw_articles 의 cluster_id 와 매칭</t>
         </is>
       </c>
     </row>
@@ -5337,22 +5341,22 @@
       <c r="B64" s="91" t="n"/>
       <c r="C64" s="92" t="inlineStr">
         <is>
-          <t>summary_lines</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D64" s="92" t="inlineStr">
         <is>
-          <t>3줄 요약</t>
+          <t>카드 제목</t>
         </is>
       </c>
       <c r="E64" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F64" s="92" t="inlineStr">
         <is>
-          <t>TEXT[]</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="G64" s="92" t="inlineStr"/>
@@ -5360,12 +5364,12 @@
       <c r="I64" s="92" t="inlineStr"/>
       <c r="J64" s="92" t="inlineStr">
         <is>
-          <t>Default '{}', 정확히 3줄</t>
+          <t>≤500자</t>
         </is>
       </c>
       <c r="K64" s="92" t="inlineStr">
         <is>
-          <t>IssueCardAgent 가 생성한 3줄 요약 배열</t>
+          <t>AI 가 생성한 카드 제목</t>
         </is>
       </c>
     </row>
@@ -5374,12 +5378,12 @@
       <c r="B65" s="91" t="n"/>
       <c r="C65" s="92" t="inlineStr">
         <is>
-          <t>event_type</t>
+          <t>summary_lines</t>
         </is>
       </c>
       <c r="D65" s="92" t="inlineStr">
         <is>
-          <t>이벤트 타입</t>
+          <t>3줄 요약</t>
         </is>
       </c>
       <c r="E65" s="92" t="inlineStr">
@@ -5389,24 +5393,20 @@
       </c>
       <c r="F65" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G65" s="92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>TEXT[]</t>
+        </is>
+      </c>
+      <c r="G65" s="92" t="inlineStr"/>
       <c r="H65" s="92" t="inlineStr"/>
       <c r="I65" s="92" t="inlineStr"/>
       <c r="J65" s="92" t="inlineStr">
         <is>
-          <t>partnership|ma|personnel|tech|regulation|new_biz</t>
+          <t>Default '{}', 정확히 3줄</t>
         </is>
       </c>
       <c r="K65" s="92" t="inlineStr">
         <is>
-          <t>v3 이벤트 6 분류</t>
+          <t>IssueCardAgent 가 생성한 3줄 요약 배열</t>
         </is>
       </c>
     </row>
@@ -5415,12 +5415,12 @@
       <c r="B66" s="91" t="n"/>
       <c r="C66" s="92" t="inlineStr">
         <is>
-          <t>importance</t>
+          <t>event_type</t>
         </is>
       </c>
       <c r="D66" s="92" t="inlineStr">
         <is>
-          <t>중요도 (band)</t>
+          <t>이벤트 타입</t>
         </is>
       </c>
       <c r="E66" s="92" t="inlineStr">
@@ -5435,19 +5435,19 @@
       </c>
       <c r="G66" s="92" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H66" s="92" t="inlineStr"/>
       <c r="I66" s="92" t="inlineStr"/>
       <c r="J66" s="92" t="inlineStr">
         <is>
-          <t>v3: high|medium|low</t>
+          <t>partnership|ma|personnel|tech|regulation|new_biz</t>
         </is>
       </c>
       <c r="K66" s="92" t="inlineStr">
         <is>
-          <t>v3 exposure_band (구 urgent/notable/reference)</t>
+          <t>v3 이벤트 6 분류</t>
         </is>
       </c>
     </row>
@@ -5456,12 +5456,12 @@
       <c r="B67" s="91" t="n"/>
       <c r="C67" s="92" t="inlineStr">
         <is>
-          <t>importance_score</t>
+          <t>importance</t>
         </is>
       </c>
       <c r="D67" s="92" t="inlineStr">
         <is>
-          <t>중요도 점수</t>
+          <t>중요도 (band)</t>
         </is>
       </c>
       <c r="E67" s="92" t="inlineStr">
@@ -5471,20 +5471,24 @@
       </c>
       <c r="F67" s="92" t="inlineStr">
         <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="G67" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G67" s="92" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="H67" s="92" t="inlineStr"/>
       <c r="I67" s="92" t="inlineStr"/>
       <c r="J67" s="92" t="inlineStr">
         <is>
-          <t>0.0~1.0</t>
+          <t>v3: high|medium|low</t>
         </is>
       </c>
       <c r="K67" s="92" t="inlineStr">
         <is>
-          <t>v3 exposure_score (결정적 산식)</t>
+          <t>v3 exposure_band (구 urgent/notable/reference)</t>
         </is>
       </c>
     </row>
@@ -5493,12 +5497,12 @@
       <c r="B68" s="91" t="n"/>
       <c r="C68" s="92" t="inlineStr">
         <is>
-          <t>implication</t>
+          <t>importance_score</t>
         </is>
       </c>
       <c r="D68" s="92" t="inlineStr">
         <is>
-          <t>시사점 + 통합 메타</t>
+          <t>중요도 점수</t>
         </is>
       </c>
       <c r="E68" s="92" t="inlineStr">
@@ -5508,16 +5512,20 @@
       </c>
       <c r="F68" s="92" t="inlineStr">
         <is>
-          <t>JSONB</t>
+          <t>FLOAT</t>
         </is>
       </c>
       <c r="G68" s="92" t="inlineStr"/>
       <c r="H68" s="92" t="inlineStr"/>
       <c r="I68" s="92" t="inlineStr"/>
-      <c r="J68" s="92" t="inlineStr"/>
+      <c r="J68" s="92" t="inlineStr">
+        <is>
+          <t>0.0~1.0</t>
+        </is>
+      </c>
       <c r="K68" s="92" t="inlineStr">
         <is>
-          <t>{sector, sectors, exposure_score, exposure_band, signals, evidence_chain}</t>
+          <t>v3 exposure_score (결정적 산식)</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5534,12 @@
       <c r="B69" s="91" t="n"/>
       <c r="C69" s="92" t="inlineStr">
         <is>
-          <t>sources</t>
+          <t>implication</t>
         </is>
       </c>
       <c r="D69" s="92" t="inlineStr">
         <is>
-          <t>출처 목록</t>
+          <t>시사점 + 통합 메타</t>
         </is>
       </c>
       <c r="E69" s="92" t="inlineStr">
@@ -5547,14 +5555,10 @@
       <c r="G69" s="92" t="inlineStr"/>
       <c r="H69" s="92" t="inlineStr"/>
       <c r="I69" s="92" t="inlineStr"/>
-      <c r="J69" s="92" t="inlineStr">
-        <is>
-          <t>JSONB array</t>
-        </is>
-      </c>
+      <c r="J69" s="92" t="inlineStr"/>
       <c r="K69" s="92" t="inlineStr">
         <is>
-          <t>원문 출처 (제목 · URL · source_name · credibility_score)</t>
+          <t>{sector, sectors, exposure_score, exposure_band, signals, evidence_chain}</t>
         </is>
       </c>
     </row>
@@ -5563,12 +5567,12 @@
       <c r="B70" s="91" t="n"/>
       <c r="C70" s="92" t="inlineStr">
         <is>
-          <t>validation_pass</t>
+          <t>sources</t>
         </is>
       </c>
       <c r="D70" s="92" t="inlineStr">
         <is>
-          <t>검증 통과 여부</t>
+          <t>출처 목록</t>
         </is>
       </c>
       <c r="E70" s="92" t="inlineStr">
@@ -5578,16 +5582,20 @@
       </c>
       <c r="F70" s="92" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>JSONB</t>
         </is>
       </c>
       <c r="G70" s="92" t="inlineStr"/>
       <c r="H70" s="92" t="inlineStr"/>
       <c r="I70" s="92" t="inlineStr"/>
-      <c r="J70" s="92" t="inlineStr"/>
+      <c r="J70" s="92" t="inlineStr">
+        <is>
+          <t>JSONB array</t>
+        </is>
+      </c>
       <c r="K70" s="92" t="inlineStr">
         <is>
-          <t>EvidenceAgent 의 4종 chain 첨부 통과 여부</t>
+          <t>원문 출처 (제목 · URL · source_name · credibility_score)</t>
         </is>
       </c>
     </row>
@@ -5596,12 +5604,12 @@
       <c r="B71" s="91" t="n"/>
       <c r="C71" s="92" t="inlineStr">
         <is>
-          <t>validation_sc_score</t>
+          <t>validation_pass</t>
         </is>
       </c>
       <c r="D71" s="92" t="inlineStr">
         <is>
-          <t>SC 점수</t>
+          <t>검증 통과 여부</t>
         </is>
       </c>
       <c r="E71" s="92" t="inlineStr">
@@ -5611,20 +5619,16 @@
       </c>
       <c r="F71" s="92" t="inlineStr">
         <is>
-          <t>FLOAT</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="G71" s="92" t="inlineStr"/>
       <c r="H71" s="92" t="inlineStr"/>
       <c r="I71" s="92" t="inlineStr"/>
-      <c r="J71" s="92" t="inlineStr">
-        <is>
-          <t>1.0(pass) | 0.0(fail)</t>
-        </is>
-      </c>
+      <c r="J71" s="92" t="inlineStr"/>
       <c r="K71" s="92" t="inlineStr">
         <is>
-          <t>v3 에서 의미 축소 — pass 의 binary flag</t>
+          <t>EvidenceAgent 의 4종 chain 첨부 통과 여부</t>
         </is>
       </c>
     </row>
@@ -5633,12 +5637,12 @@
       <c r="B72" s="91" t="n"/>
       <c r="C72" s="92" t="inlineStr">
         <is>
-          <t>is_human_reviewed</t>
+          <t>validation_sc_score</t>
         </is>
       </c>
       <c r="D72" s="92" t="inlineStr">
         <is>
-          <t>사람 검토 여부</t>
+          <t>SC 점수</t>
         </is>
       </c>
       <c r="E72" s="92" t="inlineStr">
@@ -5648,7 +5652,7 @@
       </c>
       <c r="F72" s="92" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>FLOAT</t>
         </is>
       </c>
       <c r="G72" s="92" t="inlineStr"/>
@@ -5656,12 +5660,12 @@
       <c r="I72" s="92" t="inlineStr"/>
       <c r="J72" s="92" t="inlineStr">
         <is>
-          <t>Default FALSE</t>
+          <t>1.0(pass) | 0.0(fail)</t>
         </is>
       </c>
       <c r="K72" s="92" t="inlineStr">
         <is>
-          <t>운영자 수동 검토 플래그</t>
+          <t>v3 에서 의미 축소 — pass 의 binary flag</t>
         </is>
       </c>
     </row>
@@ -5670,12 +5674,12 @@
       <c r="B73" s="91" t="n"/>
       <c r="C73" s="92" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>is_human_reviewed</t>
         </is>
       </c>
       <c r="D73" s="92" t="inlineStr">
         <is>
-          <t>생성 시각</t>
+          <t>사람 검토 여부</t>
         </is>
       </c>
       <c r="E73" s="92" t="inlineStr">
@@ -5685,7 +5689,7 @@
       </c>
       <c r="F73" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="G73" s="92" t="inlineStr"/>
@@ -5693,106 +5697,98 @@
       <c r="I73" s="92" t="inlineStr"/>
       <c r="J73" s="92" t="inlineStr">
         <is>
-          <t>Default NOW()</t>
+          <t>Default FALSE</t>
         </is>
       </c>
       <c r="K73" s="92" t="inlineStr">
         <is>
-          <t>row 생성 시각</t>
+          <t>운영자 수동 검토 플래그</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="91" t="inlineStr">
-        <is>
-          <t>evidence_chain</t>
-        </is>
-      </c>
-      <c r="B74" s="91" t="inlineStr">
-        <is>
-          <t>검증 체인 4종</t>
-        </is>
-      </c>
+      <c r="A74" s="91" t="n"/>
+      <c r="B74" s="91" t="n"/>
       <c r="C74" s="92" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D74" s="92" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>생성 시각</t>
         </is>
       </c>
       <c r="E74" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F74" s="92" t="inlineStr">
         <is>
-          <t>BIGSERIAL</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="G74" s="92" t="inlineStr"/>
-      <c r="H74" s="92" t="inlineStr">
-        <is>
-          <t>PK1</t>
-        </is>
-      </c>
+      <c r="H74" s="92" t="inlineStr"/>
       <c r="I74" s="92" t="inlineStr"/>
       <c r="J74" s="92" t="inlineStr">
         <is>
+          <t>Default NOW()</t>
+        </is>
+      </c>
+      <c r="K74" s="92" t="inlineStr">
+        <is>
+          <t>row 생성 시각</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="91" t="inlineStr">
+        <is>
+          <t>evidence_chain</t>
+        </is>
+      </c>
+      <c r="B75" s="91" t="inlineStr">
+        <is>
+          <t>검증 체인 4종</t>
+        </is>
+      </c>
+      <c r="C75" s="92" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D75" s="92" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="E75" s="92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F75" s="92" t="inlineStr">
+        <is>
+          <t>BIGSERIAL</t>
+        </is>
+      </c>
+      <c r="G75" s="92" t="inlineStr"/>
+      <c r="H75" s="92" t="inlineStr">
+        <is>
+          <t>PK1</t>
+        </is>
+      </c>
+      <c r="I75" s="92" t="inlineStr"/>
+      <c r="J75" s="92" t="inlineStr">
+        <is>
           <t>AUTO_INCREMENT</t>
         </is>
       </c>
-      <c r="K74" s="92" t="inlineStr">
+      <c r="K75" s="92" t="inlineStr">
         <is>
           <t>row PK</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="91" t="n"/>
-      <c r="B75" s="91" t="n"/>
-      <c r="C75" s="92" t="inlineStr">
-        <is>
-          <t>issue_card_id</t>
-        </is>
-      </c>
-      <c r="D75" s="92" t="inlineStr">
-        <is>
-          <t>카드 ID</t>
-        </is>
-      </c>
-      <c r="E75" s="92" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F75" s="92" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G75" s="92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H75" s="92" t="inlineStr"/>
-      <c r="I75" s="92" t="inlineStr">
-        <is>
-          <t>issue_cards.id</t>
-        </is>
-      </c>
-      <c r="J75" s="92" t="inlineStr">
-        <is>
-          <t>UNIQUE · ON DELETE CASCADE</t>
-        </is>
-      </c>
-      <c r="K75" s="92" t="inlineStr">
-        <is>
-          <t>1:1 매핑되는 동향 카드</t>
         </is>
       </c>
     </row>
@@ -5801,35 +5797,43 @@
       <c r="B76" s="91" t="n"/>
       <c r="C76" s="92" t="inlineStr">
         <is>
-          <t>source_links</t>
+          <t>issue_card_id</t>
         </is>
       </c>
       <c r="D76" s="92" t="inlineStr">
         <is>
-          <t>출처 링크</t>
+          <t>카드 ID</t>
         </is>
       </c>
       <c r="E76" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F76" s="92" t="inlineStr">
         <is>
-          <t>JSONB</t>
-        </is>
-      </c>
-      <c r="G76" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G76" s="92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="H76" s="92" t="inlineStr"/>
-      <c r="I76" s="92" t="inlineStr"/>
+      <c r="I76" s="92" t="inlineStr">
+        <is>
+          <t>issue_cards.id</t>
+        </is>
+      </c>
       <c r="J76" s="92" t="inlineStr">
         <is>
-          <t>Default '[]'</t>
+          <t>UNIQUE · ON DELETE CASCADE</t>
         </is>
       </c>
       <c r="K76" s="92" t="inlineStr">
         <is>
-          <t>[{title, url, source_name, credibility_score}]</t>
+          <t>1:1 매핑되는 동향 카드</t>
         </is>
       </c>
     </row>
@@ -5838,12 +5842,12 @@
       <c r="B77" s="91" t="n"/>
       <c r="C77" s="92" t="inlineStr">
         <is>
-          <t>provenance</t>
+          <t>source_links</t>
         </is>
       </c>
       <c r="D77" s="92" t="inlineStr">
         <is>
-          <t>프로비넌스</t>
+          <t>출처 링크</t>
         </is>
       </c>
       <c r="E77" s="92" t="inlineStr">
@@ -5861,12 +5865,12 @@
       <c r="I77" s="92" t="inlineStr"/>
       <c r="J77" s="92" t="inlineStr">
         <is>
-          <t>Default '{}'</t>
+          <t>Default '[]'</t>
         </is>
       </c>
       <c r="K77" s="92" t="inlineStr">
         <is>
-          <t>{raw_article_ids, cluster_id, llm_model, prompt_version, evidence_version, run_at}</t>
+          <t>[{title, url, source_name, credibility_score}]</t>
         </is>
       </c>
     </row>
@@ -5875,12 +5879,12 @@
       <c r="B78" s="91" t="n"/>
       <c r="C78" s="92" t="inlineStr">
         <is>
-          <t>financial_refs</t>
+          <t>provenance</t>
         </is>
       </c>
       <c r="D78" s="92" t="inlineStr">
         <is>
-          <t>재무 참조</t>
+          <t>프로비넌스</t>
         </is>
       </c>
       <c r="E78" s="92" t="inlineStr">
@@ -5898,12 +5902,12 @@
       <c r="I78" s="92" t="inlineStr"/>
       <c r="J78" s="92" t="inlineStr">
         <is>
-          <t>Default '[]'</t>
+          <t>Default '{}'</t>
         </is>
       </c>
       <c r="K78" s="92" t="inlineStr">
         <is>
-          <t>[{period, metric, value, delta_qoq, delta_yoy, dart_rcept_no, ir_page}]</t>
+          <t>{raw_article_ids, cluster_id, llm_model, prompt_version, evidence_version, run_at}</t>
         </is>
       </c>
     </row>
@@ -5912,12 +5916,12 @@
       <c r="B79" s="91" t="n"/>
       <c r="C79" s="92" t="inlineStr">
         <is>
-          <t>mbb_refs</t>
+          <t>financial_refs</t>
         </is>
       </c>
       <c r="D79" s="92" t="inlineStr">
         <is>
-          <t>컨설팅 참조</t>
+          <t>재무 참조</t>
         </is>
       </c>
       <c r="E79" s="92" t="inlineStr">
@@ -5935,12 +5939,12 @@
       <c r="I79" s="92" t="inlineStr"/>
       <c r="J79" s="92" t="inlineStr">
         <is>
-          <t>Default '[]', W5 활성</t>
+          <t>Default '[]'</t>
         </is>
       </c>
       <c r="K79" s="92" t="inlineStr">
         <is>
-          <t>MBB·커니 보고서 자동 매칭 결과</t>
+          <t>[{period, metric, value, delta_qoq, delta_yoy, dart_rcept_no, ir_page}]</t>
         </is>
       </c>
     </row>
@@ -5949,12 +5953,12 @@
       <c r="B80" s="91" t="n"/>
       <c r="C80" s="92" t="inlineStr">
         <is>
-          <t>financial_link</t>
+          <t>mbb_refs</t>
         </is>
       </c>
       <c r="D80" s="92" t="inlineStr">
         <is>
-          <t>재무 링크 정보</t>
+          <t>컨설팅 참조</t>
         </is>
       </c>
       <c r="E80" s="92" t="inlineStr">
@@ -5970,10 +5974,14 @@
       <c r="G80" s="92" t="inlineStr"/>
       <c r="H80" s="92" t="inlineStr"/>
       <c r="I80" s="92" t="inlineStr"/>
-      <c r="J80" s="92" t="inlineStr"/>
+      <c r="J80" s="92" t="inlineStr">
+        <is>
+          <t>Default '[]', W5 활성</t>
+        </is>
+      </c>
       <c r="K80" s="92" t="inlineStr">
         <is>
-          <t>{linked, segment, highlights, headcount_delta, reason}</t>
+          <t>MBB·커니 보고서 자동 매칭 결과</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5990,12 @@
       <c r="B81" s="91" t="n"/>
       <c r="C81" s="92" t="inlineStr">
         <is>
-          <t>evidence_version</t>
+          <t>financial_link</t>
         </is>
       </c>
       <c r="D81" s="92" t="inlineStr">
         <is>
-          <t>버전</t>
+          <t>재무 링크 정보</t>
         </is>
       </c>
       <c r="E81" s="92" t="inlineStr">
@@ -5997,24 +6005,16 @@
       </c>
       <c r="F81" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G81" s="92" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>JSONB</t>
+        </is>
+      </c>
+      <c r="G81" s="92" t="inlineStr"/>
       <c r="H81" s="92" t="inlineStr"/>
       <c r="I81" s="92" t="inlineStr"/>
-      <c r="J81" s="92" t="inlineStr">
-        <is>
-          <t>Default 'v3.0'</t>
-        </is>
-      </c>
+      <c r="J81" s="92" t="inlineStr"/>
       <c r="K81" s="92" t="inlineStr">
         <is>
-          <t>Evidence chain 스키마 버전</t>
+          <t>{linked, segment, highlights, headcount_delta, reason}</t>
         </is>
       </c>
     </row>
@@ -6023,12 +6023,12 @@
       <c r="B82" s="91" t="n"/>
       <c r="C82" s="92" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>evidence_version</t>
         </is>
       </c>
       <c r="D82" s="92" t="inlineStr">
         <is>
-          <t>검증 통과</t>
+          <t>버전</t>
         </is>
       </c>
       <c r="E82" s="92" t="inlineStr">
@@ -6038,20 +6038,24 @@
       </c>
       <c r="F82" s="92" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="G82" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G82" s="92" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="H82" s="92" t="inlineStr"/>
       <c r="I82" s="92" t="inlineStr"/>
       <c r="J82" s="92" t="inlineStr">
         <is>
-          <t>Default FALSE</t>
+          <t>Default 'v3.0'</t>
         </is>
       </c>
       <c r="K82" s="92" t="inlineStr">
         <is>
-          <t>4종 모두 첨부됐는지</t>
+          <t>Evidence chain 스키마 버전</t>
         </is>
       </c>
     </row>
@@ -6060,12 +6064,12 @@
       <c r="B83" s="91" t="n"/>
       <c r="C83" s="92" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="D83" s="92" t="inlineStr">
         <is>
-          <t>누락 항목</t>
+          <t>검증 통과</t>
         </is>
       </c>
       <c r="E83" s="92" t="inlineStr">
@@ -6075,7 +6079,7 @@
       </c>
       <c r="F83" s="92" t="inlineStr">
         <is>
-          <t>TEXT[]</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="G83" s="92" t="inlineStr"/>
@@ -6083,12 +6087,12 @@
       <c r="I83" s="92" t="inlineStr"/>
       <c r="J83" s="92" t="inlineStr">
         <is>
-          <t>Default '{}'</t>
+          <t>Default FALSE</t>
         </is>
       </c>
       <c r="K83" s="92" t="inlineStr">
         <is>
-          <t>pass=false 시 누락된 chain 종류</t>
+          <t>4종 모두 첨부됐는지</t>
         </is>
       </c>
     </row>
@@ -6097,12 +6101,12 @@
       <c r="B84" s="91" t="n"/>
       <c r="C84" s="92" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D84" s="92" t="inlineStr">
         <is>
-          <t>생성 시각</t>
+          <t>누락 항목</t>
         </is>
       </c>
       <c r="E84" s="92" t="inlineStr">
@@ -6112,7 +6116,7 @@
       </c>
       <c r="F84" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>TEXT[]</t>
         </is>
       </c>
       <c r="G84" s="92" t="inlineStr"/>
@@ -6120,102 +6124,98 @@
       <c r="I84" s="92" t="inlineStr"/>
       <c r="J84" s="92" t="inlineStr">
         <is>
-          <t>Default NOW()</t>
+          <t>Default '{}'</t>
         </is>
       </c>
       <c r="K84" s="92" t="inlineStr">
         <is>
-          <t>row 생성 시각</t>
+          <t>pass=false 시 누락된 chain 종류</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="91" t="inlineStr">
-        <is>
-          <t>article_images</t>
-        </is>
-      </c>
-      <c r="B85" s="91" t="inlineStr">
-        <is>
-          <t>카드 뉴스 이미지 메타</t>
-        </is>
-      </c>
+      <c r="A85" s="91" t="n"/>
+      <c r="B85" s="91" t="n"/>
       <c r="C85" s="92" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D85" s="92" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>생성 시각</t>
         </is>
       </c>
       <c r="E85" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F85" s="92" t="inlineStr">
         <is>
-          <t>BIGSERIAL</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="G85" s="92" t="inlineStr"/>
-      <c r="H85" s="92" t="inlineStr">
-        <is>
-          <t>PK1</t>
-        </is>
-      </c>
+      <c r="H85" s="92" t="inlineStr"/>
       <c r="I85" s="92" t="inlineStr"/>
       <c r="J85" s="92" t="inlineStr">
         <is>
+          <t>Default NOW()</t>
+        </is>
+      </c>
+      <c r="K85" s="92" t="inlineStr">
+        <is>
+          <t>row 생성 시각</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="91" t="inlineStr">
+        <is>
+          <t>article_images</t>
+        </is>
+      </c>
+      <c r="B86" s="91" t="inlineStr">
+        <is>
+          <t>카드 뉴스 이미지 메타</t>
+        </is>
+      </c>
+      <c r="C86" s="92" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D86" s="92" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="E86" s="92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F86" s="92" t="inlineStr">
+        <is>
+          <t>BIGSERIAL</t>
+        </is>
+      </c>
+      <c r="G86" s="92" t="inlineStr"/>
+      <c r="H86" s="92" t="inlineStr">
+        <is>
+          <t>PK1</t>
+        </is>
+      </c>
+      <c r="I86" s="92" t="inlineStr"/>
+      <c r="J86" s="92" t="inlineStr">
+        <is>
           <t>AUTO_INCREMENT</t>
         </is>
       </c>
-      <c r="K85" s="92" t="inlineStr">
+      <c r="K86" s="92" t="inlineStr">
         <is>
           <t>row PK</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="91" t="n"/>
-      <c r="B86" s="91" t="n"/>
-      <c r="C86" s="92" t="inlineStr">
-        <is>
-          <t>article_id</t>
-        </is>
-      </c>
-      <c r="D86" s="92" t="inlineStr">
-        <is>
-          <t>기사 ID</t>
-        </is>
-      </c>
-      <c r="E86" s="92" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F86" s="92" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="G86" s="92" t="inlineStr"/>
-      <c r="H86" s="92" t="inlineStr"/>
-      <c r="I86" s="92" t="inlineStr">
-        <is>
-          <t>raw_articles.id</t>
-        </is>
-      </c>
-      <c r="J86" s="92" t="inlineStr">
-        <is>
-          <t>ON DELETE SET NULL</t>
-        </is>
-      </c>
-      <c r="K86" s="92" t="inlineStr">
-        <is>
-          <t>원본 기사 (출처)</t>
         </is>
       </c>
     </row>
@@ -6224,12 +6224,12 @@
       <c r="B87" s="91" t="n"/>
       <c r="C87" s="92" t="inlineStr">
         <is>
-          <t>cluster_id</t>
+          <t>article_id</t>
         </is>
       </c>
       <c r="D87" s="92" t="inlineStr">
         <is>
-          <t>클러스터 ID</t>
+          <t>기사 ID</t>
         </is>
       </c>
       <c r="E87" s="92" t="inlineStr">
@@ -6244,11 +6244,19 @@
       </c>
       <c r="G87" s="92" t="inlineStr"/>
       <c r="H87" s="92" t="inlineStr"/>
-      <c r="I87" s="92" t="inlineStr"/>
-      <c r="J87" s="92" t="inlineStr"/>
+      <c r="I87" s="92" t="inlineStr">
+        <is>
+          <t>raw_articles.id</t>
+        </is>
+      </c>
+      <c r="J87" s="92" t="inlineStr">
+        <is>
+          <t>ON DELETE SET NULL</t>
+        </is>
+      </c>
       <c r="K87" s="92" t="inlineStr">
         <is>
-          <t>이미지가 속한 클러스터</t>
+          <t>원본 기사 (출처)</t>
         </is>
       </c>
     </row>
@@ -6257,12 +6265,12 @@
       <c r="B88" s="91" t="n"/>
       <c r="C88" s="92" t="inlineStr">
         <is>
-          <t>issue_card_id</t>
+          <t>cluster_id</t>
         </is>
       </c>
       <c r="D88" s="92" t="inlineStr">
         <is>
-          <t>카드 ID</t>
+          <t>클러스터 ID</t>
         </is>
       </c>
       <c r="E88" s="92" t="inlineStr">
@@ -6272,28 +6280,16 @@
       </c>
       <c r="F88" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G88" s="92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="G88" s="92" t="inlineStr"/>
       <c r="H88" s="92" t="inlineStr"/>
-      <c r="I88" s="92" t="inlineStr">
-        <is>
-          <t>issue_cards.id</t>
-        </is>
-      </c>
-      <c r="J88" s="92" t="inlineStr">
-        <is>
-          <t>ON DELETE SET NULL</t>
-        </is>
-      </c>
+      <c r="I88" s="92" t="inlineStr"/>
+      <c r="J88" s="92" t="inlineStr"/>
       <c r="K88" s="92" t="inlineStr">
         <is>
-          <t>backend lookup 키 — 카드별 대표 이미지</t>
+          <t>이미지가 속한 클러스터</t>
         </is>
       </c>
     </row>
@@ -6302,31 +6298,43 @@
       <c r="B89" s="91" t="n"/>
       <c r="C89" s="92" t="inlineStr">
         <is>
-          <t>source_url</t>
+          <t>issue_card_id</t>
         </is>
       </c>
       <c r="D89" s="92" t="inlineStr">
         <is>
-          <t>원본 URL</t>
+          <t>카드 ID</t>
         </is>
       </c>
       <c r="E89" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F89" s="92" t="inlineStr">
         <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="G89" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G89" s="92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="H89" s="92" t="inlineStr"/>
-      <c r="I89" s="92" t="inlineStr"/>
-      <c r="J89" s="92" t="inlineStr"/>
+      <c r="I89" s="92" t="inlineStr">
+        <is>
+          <t>issue_cards.id</t>
+        </is>
+      </c>
+      <c r="J89" s="92" t="inlineStr">
+        <is>
+          <t>ON DELETE SET NULL</t>
+        </is>
+      </c>
       <c r="K89" s="92" t="inlineStr">
         <is>
-          <t>og:image / twitter:image / 본문 첫 &lt;img&gt;</t>
+          <t>backend lookup 키 — 카드별 대표 이미지</t>
         </is>
       </c>
     </row>
@@ -6335,12 +6343,12 @@
       <c r="B90" s="91" t="n"/>
       <c r="C90" s="92" t="inlineStr">
         <is>
-          <t>source_url_hash</t>
+          <t>source_url</t>
         </is>
       </c>
       <c r="D90" s="92" t="inlineStr">
         <is>
-          <t>URL 해시</t>
+          <t>원본 URL</t>
         </is>
       </c>
       <c r="E90" s="92" t="inlineStr">
@@ -6350,24 +6358,16 @@
       </c>
       <c r="F90" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G90" s="92" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="G90" s="92" t="inlineStr"/>
       <c r="H90" s="92" t="inlineStr"/>
       <c r="I90" s="92" t="inlineStr"/>
-      <c r="J90" s="92" t="inlineStr">
-        <is>
-          <t>UNIQUE</t>
-        </is>
-      </c>
+      <c r="J90" s="92" t="inlineStr"/>
       <c r="K90" s="92" t="inlineStr">
         <is>
-          <t>SHA-256(source_url) — 중복 다운로드 차단</t>
+          <t>og:image / twitter:image / 본문 첫 &lt;img&gt;</t>
         </is>
       </c>
     </row>
@@ -6376,12 +6376,12 @@
       <c r="B91" s="91" t="n"/>
       <c r="C91" s="92" t="inlineStr">
         <is>
-          <t>storage_path</t>
+          <t>source_url_hash</t>
         </is>
       </c>
       <c r="D91" s="92" t="inlineStr">
         <is>
-          <t>저장 경로</t>
+          <t>URL 해시</t>
         </is>
       </c>
       <c r="E91" s="92" t="inlineStr">
@@ -6391,20 +6391,24 @@
       </c>
       <c r="F91" s="92" t="inlineStr">
         <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="G91" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G91" s="92" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="H91" s="92" t="inlineStr"/>
       <c r="I91" s="92" t="inlineStr"/>
       <c r="J91" s="92" t="inlineStr">
         <is>
-          <t>상대 경로</t>
+          <t>UNIQUE</t>
         </is>
       </c>
       <c r="K91" s="92" t="inlineStr">
         <is>
-          <t>IMAGE_STORAGE_PATH 기준 (예: lg_cns/2026-04/&lt;hash&gt;.jpg)</t>
+          <t>SHA-256(source_url) — 중복 다운로드 차단</t>
         </is>
       </c>
     </row>
@@ -6413,39 +6417,35 @@
       <c r="B92" s="91" t="n"/>
       <c r="C92" s="92" t="inlineStr">
         <is>
-          <t>content_type</t>
+          <t>storage_path</t>
         </is>
       </c>
       <c r="D92" s="92" t="inlineStr">
         <is>
-          <t>MIME 타입</t>
+          <t>저장 경로</t>
         </is>
       </c>
       <c r="E92" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F92" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G92" s="92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="G92" s="92" t="inlineStr"/>
       <c r="H92" s="92" t="inlineStr"/>
       <c r="I92" s="92" t="inlineStr"/>
       <c r="J92" s="92" t="inlineStr">
         <is>
-          <t>image/jpeg|png|webp</t>
+          <t>상대 경로</t>
         </is>
       </c>
       <c r="K92" s="92" t="inlineStr">
         <is>
-          <t>이미지 MIME</t>
+          <t>IMAGE_STORAGE_PATH 기준 (예: lg_cns/2026-04/&lt;hash&gt;.jpg)</t>
         </is>
       </c>
     </row>
@@ -6454,12 +6454,12 @@
       <c r="B93" s="91" t="n"/>
       <c r="C93" s="92" t="inlineStr">
         <is>
-          <t>width</t>
+          <t>content_type</t>
         </is>
       </c>
       <c r="D93" s="92" t="inlineStr">
         <is>
-          <t>너비</t>
+          <t>MIME 타입</t>
         </is>
       </c>
       <c r="E93" s="92" t="inlineStr">
@@ -6469,20 +6469,24 @@
       </c>
       <c r="F93" s="92" t="inlineStr">
         <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="G93" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G93" s="92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="H93" s="92" t="inlineStr"/>
       <c r="I93" s="92" t="inlineStr"/>
       <c r="J93" s="92" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>image/jpeg|png|webp</t>
         </is>
       </c>
       <c r="K93" s="92" t="inlineStr">
         <is>
-          <t>이미지 너비</t>
+          <t>이미지 MIME</t>
         </is>
       </c>
     </row>
@@ -6491,12 +6495,12 @@
       <c r="B94" s="91" t="n"/>
       <c r="C94" s="92" t="inlineStr">
         <is>
-          <t>height</t>
+          <t>width</t>
         </is>
       </c>
       <c r="D94" s="92" t="inlineStr">
         <is>
-          <t>높이</t>
+          <t>너비</t>
         </is>
       </c>
       <c r="E94" s="92" t="inlineStr">
@@ -6519,7 +6523,7 @@
       </c>
       <c r="K94" s="92" t="inlineStr">
         <is>
-          <t>이미지 높이</t>
+          <t>이미지 너비</t>
         </is>
       </c>
     </row>
@@ -6528,12 +6532,12 @@
       <c r="B95" s="91" t="n"/>
       <c r="C95" s="92" t="inlineStr">
         <is>
-          <t>file_size_bytes</t>
+          <t>height</t>
         </is>
       </c>
       <c r="D95" s="92" t="inlineStr">
         <is>
-          <t>파일 크기</t>
+          <t>높이</t>
         </is>
       </c>
       <c r="E95" s="92" t="inlineStr">
@@ -6551,12 +6555,12 @@
       <c r="I95" s="92" t="inlineStr"/>
       <c r="J95" s="92" t="inlineStr">
         <is>
-          <t>≤5MB</t>
+          <t>px</t>
         </is>
       </c>
       <c r="K95" s="92" t="inlineStr">
         <is>
-          <t>파일 바이트 (5MB 상한)</t>
+          <t>이미지 높이</t>
         </is>
       </c>
     </row>
@@ -6565,12 +6569,12 @@
       <c r="B96" s="91" t="n"/>
       <c r="C96" s="92" t="inlineStr">
         <is>
-          <t>alt_text</t>
+          <t>file_size_bytes</t>
         </is>
       </c>
       <c r="D96" s="92" t="inlineStr">
         <is>
-          <t>alt 텍스트</t>
+          <t>파일 크기</t>
         </is>
       </c>
       <c r="E96" s="92" t="inlineStr">
@@ -6580,16 +6584,20 @@
       </c>
       <c r="F96" s="92" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="G96" s="92" t="inlineStr"/>
       <c r="H96" s="92" t="inlineStr"/>
       <c r="I96" s="92" t="inlineStr"/>
-      <c r="J96" s="92" t="inlineStr"/>
+      <c r="J96" s="92" t="inlineStr">
+        <is>
+          <t>≤5MB</t>
+        </is>
+      </c>
       <c r="K96" s="92" t="inlineStr">
         <is>
-          <t>접근성 + 이메일 차단 시 노출</t>
+          <t>파일 바이트 (5MB 상한)</t>
         </is>
       </c>
     </row>
@@ -6598,12 +6606,12 @@
       <c r="B97" s="91" t="n"/>
       <c r="C97" s="92" t="inlineStr">
         <is>
-          <t>attribution</t>
+          <t>alt_text</t>
         </is>
       </c>
       <c r="D97" s="92" t="inlineStr">
         <is>
-          <t>출처 표기</t>
+          <t>alt 텍스트</t>
         </is>
       </c>
       <c r="E97" s="92" t="inlineStr">
@@ -6622,7 +6630,7 @@
       <c r="J97" s="92" t="inlineStr"/>
       <c r="K97" s="92" t="inlineStr">
         <is>
-          <t>예: '제공: 한경'</t>
+          <t>접근성 + 이메일 차단 시 노출</t>
         </is>
       </c>
     </row>
@@ -6631,12 +6639,12 @@
       <c r="B98" s="91" t="n"/>
       <c r="C98" s="92" t="inlineStr">
         <is>
-          <t>fetched_at</t>
+          <t>attribution</t>
         </is>
       </c>
       <c r="D98" s="92" t="inlineStr">
         <is>
-          <t>다운로드 시각</t>
+          <t>출처 표기</t>
         </is>
       </c>
       <c r="E98" s="92" t="inlineStr">
@@ -6646,7 +6654,7 @@
       </c>
       <c r="F98" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="G98" s="92" t="inlineStr"/>
@@ -6655,7 +6663,7 @@
       <c r="J98" s="92" t="inlineStr"/>
       <c r="K98" s="92" t="inlineStr">
         <is>
-          <t>이미지 다운로드 완료 시각</t>
+          <t>예: '제공: 한경'</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6672,12 @@
       <c r="B99" s="91" t="n"/>
       <c r="C99" s="92" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>fetched_at</t>
         </is>
       </c>
       <c r="D99" s="92" t="inlineStr">
         <is>
-          <t>생성 시각</t>
+          <t>다운로드 시각</t>
         </is>
       </c>
       <c r="E99" s="92" t="inlineStr">
@@ -6685,77 +6693,69 @@
       <c r="G99" s="92" t="inlineStr"/>
       <c r="H99" s="92" t="inlineStr"/>
       <c r="I99" s="92" t="inlineStr"/>
-      <c r="J99" s="92" t="inlineStr">
-        <is>
-          <t>Default NOW()</t>
-        </is>
-      </c>
+      <c r="J99" s="92" t="inlineStr"/>
       <c r="K99" s="92" t="inlineStr">
         <is>
-          <t>row 생성 시각</t>
+          <t>이미지 다운로드 완료 시각</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="91" t="inlineStr">
-        <is>
-          <t>recipients</t>
-        </is>
-      </c>
-      <c r="B100" s="91" t="inlineStr">
-        <is>
-          <t>메일 수신자</t>
-        </is>
-      </c>
+      <c r="A100" s="91" t="n"/>
+      <c r="B100" s="91" t="n"/>
       <c r="C100" s="92" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D100" s="92" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>생성 시각</t>
         </is>
       </c>
       <c r="E100" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F100" s="92" t="inlineStr">
         <is>
-          <t>BIGSERIAL</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="G100" s="92" t="inlineStr"/>
-      <c r="H100" s="92" t="inlineStr">
-        <is>
-          <t>PK1</t>
-        </is>
-      </c>
+      <c r="H100" s="92" t="inlineStr"/>
       <c r="I100" s="92" t="inlineStr"/>
       <c r="J100" s="92" t="inlineStr">
         <is>
-          <t>AUTO_INCREMENT</t>
+          <t>Default NOW()</t>
         </is>
       </c>
       <c r="K100" s="92" t="inlineStr">
         <is>
-          <t>row PK</t>
+          <t>row 생성 시각</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="91" t="n"/>
-      <c r="B101" s="91" t="n"/>
+      <c r="A101" s="91" t="inlineStr">
+        <is>
+          <t>recipients</t>
+        </is>
+      </c>
+      <c r="B101" s="91" t="inlineStr">
+        <is>
+          <t>메일 수신자</t>
+        </is>
+      </c>
       <c r="C101" s="92" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D101" s="92" t="inlineStr">
         <is>
-          <t>이메일</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E101" s="92" t="inlineStr">
@@ -6765,24 +6765,24 @@
       </c>
       <c r="F101" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G101" s="92" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="H101" s="92" t="inlineStr"/>
+          <t>BIGSERIAL</t>
+        </is>
+      </c>
+      <c r="G101" s="92" t="inlineStr"/>
+      <c r="H101" s="92" t="inlineStr">
+        <is>
+          <t>PK1</t>
+        </is>
+      </c>
       <c r="I101" s="92" t="inlineStr"/>
       <c r="J101" s="92" t="inlineStr">
         <is>
-          <t>UNIQUE</t>
+          <t>AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="K101" s="92" t="inlineStr">
         <is>
-          <t>수신자 이메일 (중복 차단 키)</t>
+          <t>row PK</t>
         </is>
       </c>
     </row>
@@ -6791,17 +6791,17 @@
       <c r="B102" s="91" t="n"/>
       <c r="C102" s="92" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>email</t>
         </is>
       </c>
       <c r="D102" s="92" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>이메일</t>
         </is>
       </c>
       <c r="E102" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F102" s="92" t="inlineStr">
@@ -6811,15 +6811,19 @@
       </c>
       <c r="G102" s="92" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>255</t>
         </is>
       </c>
       <c r="H102" s="92" t="inlineStr"/>
       <c r="I102" s="92" t="inlineStr"/>
-      <c r="J102" s="92" t="inlineStr"/>
+      <c r="J102" s="92" t="inlineStr">
+        <is>
+          <t>UNIQUE</t>
+        </is>
+      </c>
       <c r="K102" s="92" t="inlineStr">
         <is>
-          <t>수신자 이름</t>
+          <t>수신자 이메일 (중복 차단 키)</t>
         </is>
       </c>
     </row>
@@ -6828,17 +6832,17 @@
       <c r="B103" s="91" t="n"/>
       <c r="C103" s="92" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>name</t>
         </is>
       </c>
       <c r="D103" s="92" t="inlineStr">
         <is>
-          <t>역할</t>
+          <t>이름</t>
         </is>
       </c>
       <c r="E103" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F103" s="92" t="inlineStr">
@@ -6848,19 +6852,15 @@
       </c>
       <c r="G103" s="92" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H103" s="92" t="inlineStr"/>
       <c r="I103" s="92" t="inlineStr"/>
-      <c r="J103" s="92" t="inlineStr">
-        <is>
-          <t>pm|executive|admin</t>
-        </is>
-      </c>
+      <c r="J103" s="92" t="inlineStr"/>
       <c r="K103" s="92" t="inlineStr">
         <is>
-          <t>PM=전체 / executive=핵심 / admin=관리자</t>
+          <t>수신자 이름</t>
         </is>
       </c>
     </row>
@@ -6869,12 +6869,12 @@
       <c r="B104" s="91" t="n"/>
       <c r="C104" s="92" t="inlineStr">
         <is>
-          <t>impact_threshold</t>
+          <t>role</t>
         </is>
       </c>
       <c r="D104" s="92" t="inlineStr">
         <is>
-          <t>임팩트 임계치</t>
+          <t>역할</t>
         </is>
       </c>
       <c r="E104" s="92" t="inlineStr">
@@ -6884,20 +6884,24 @@
       </c>
       <c r="F104" s="92" t="inlineStr">
         <is>
-          <t>SMALLINT</t>
-        </is>
-      </c>
-      <c r="G104" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G104" s="92" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="H104" s="92" t="inlineStr"/>
       <c r="I104" s="92" t="inlineStr"/>
       <c r="J104" s="92" t="inlineStr">
         <is>
-          <t>Default 3, 1~5</t>
+          <t>pm|executive|admin</t>
         </is>
       </c>
       <c r="K104" s="92" t="inlineStr">
         <is>
-          <t>포함될 카드 최소 importance_score (PM=3, 임원=4)</t>
+          <t>PM=전체 / executive=핵심 / admin=관리자</t>
         </is>
       </c>
     </row>
@@ -6906,39 +6910,35 @@
       <c r="B105" s="91" t="n"/>
       <c r="C105" s="92" t="inlineStr">
         <is>
-          <t>locale</t>
+          <t>impact_threshold</t>
         </is>
       </c>
       <c r="D105" s="92" t="inlineStr">
         <is>
-          <t>로케일</t>
+          <t>임팩트 임계치</t>
         </is>
       </c>
       <c r="E105" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F105" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G105" s="92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>SMALLINT</t>
+        </is>
+      </c>
+      <c r="G105" s="92" t="inlineStr"/>
       <c r="H105" s="92" t="inlineStr"/>
       <c r="I105" s="92" t="inlineStr"/>
       <c r="J105" s="92" t="inlineStr">
         <is>
-          <t>Default 'ko-KR'</t>
+          <t>Default 3, 1~5</t>
         </is>
       </c>
       <c r="K105" s="92" t="inlineStr">
         <is>
-          <t>메일 언어 (ko-KR 등)</t>
+          <t>포함될 카드 최소 importance_score (PM=3, 임원=4)</t>
         </is>
       </c>
     </row>
@@ -6947,12 +6947,12 @@
       <c r="B106" s="91" t="n"/>
       <c r="C106" s="92" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>locale</t>
         </is>
       </c>
       <c r="D106" s="92" t="inlineStr">
         <is>
-          <t>활성 여부</t>
+          <t>로케일</t>
         </is>
       </c>
       <c r="E106" s="92" t="inlineStr">
@@ -6962,20 +6962,24 @@
       </c>
       <c r="F106" s="92" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="G106" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G106" s="92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="H106" s="92" t="inlineStr"/>
       <c r="I106" s="92" t="inlineStr"/>
       <c r="J106" s="92" t="inlineStr">
         <is>
-          <t>Default TRUE</t>
+          <t>Default 'ko-KR'</t>
         </is>
       </c>
       <c r="K106" s="92" t="inlineStr">
         <is>
-          <t>현재 발송 대상 여부</t>
+          <t>메일 언어 (ko-KR 등)</t>
         </is>
       </c>
     </row>
@@ -6984,12 +6988,12 @@
       <c r="B107" s="91" t="n"/>
       <c r="C107" s="92" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>is_active</t>
         </is>
       </c>
       <c r="D107" s="92" t="inlineStr">
         <is>
-          <t>생성 시각</t>
+          <t>활성 여부</t>
         </is>
       </c>
       <c r="E107" s="92" t="inlineStr">
@@ -6999,7 +7003,7 @@
       </c>
       <c r="F107" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="G107" s="92" t="inlineStr"/>
@@ -7007,12 +7011,12 @@
       <c r="I107" s="92" t="inlineStr"/>
       <c r="J107" s="92" t="inlineStr">
         <is>
-          <t>Default NOW()</t>
+          <t>Default TRUE</t>
         </is>
       </c>
       <c r="K107" s="92" t="inlineStr">
         <is>
-          <t>row 생성 시각</t>
+          <t>현재 발송 대상 여부</t>
         </is>
       </c>
     </row>
@@ -7021,12 +7025,12 @@
       <c r="B108" s="91" t="n"/>
       <c r="C108" s="92" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D108" s="92" t="inlineStr">
         <is>
-          <t>수정 시각</t>
+          <t>생성 시각</t>
         </is>
       </c>
       <c r="E108" s="92" t="inlineStr">
@@ -7049,97 +7053,93 @@
       </c>
       <c r="K108" s="92" t="inlineStr">
         <is>
-          <t>row 수정 시각</t>
+          <t>row 생성 시각</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="91" t="inlineStr">
-        <is>
-          <t>briefing_history</t>
-        </is>
-      </c>
-      <c r="B109" s="91" t="inlineStr">
-        <is>
-          <t>메일 발송 이력</t>
-        </is>
-      </c>
+      <c r="A109" s="91" t="n"/>
+      <c r="B109" s="91" t="n"/>
       <c r="C109" s="92" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="D109" s="92" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>수정 시각</t>
         </is>
       </c>
       <c r="E109" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F109" s="92" t="inlineStr">
         <is>
-          <t>BIGSERIAL</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="G109" s="92" t="inlineStr"/>
-      <c r="H109" s="92" t="inlineStr">
-        <is>
-          <t>PK1</t>
-        </is>
-      </c>
+      <c r="H109" s="92" t="inlineStr"/>
       <c r="I109" s="92" t="inlineStr"/>
       <c r="J109" s="92" t="inlineStr">
         <is>
+          <t>Default NOW()</t>
+        </is>
+      </c>
+      <c r="K109" s="92" t="inlineStr">
+        <is>
+          <t>row 수정 시각</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="91" t="inlineStr">
+        <is>
+          <t>briefing_history</t>
+        </is>
+      </c>
+      <c r="B110" s="91" t="inlineStr">
+        <is>
+          <t>메일 발송 이력</t>
+        </is>
+      </c>
+      <c r="C110" s="92" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D110" s="92" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="E110" s="92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F110" s="92" t="inlineStr">
+        <is>
+          <t>BIGSERIAL</t>
+        </is>
+      </c>
+      <c r="G110" s="92" t="inlineStr"/>
+      <c r="H110" s="92" t="inlineStr">
+        <is>
+          <t>PK1</t>
+        </is>
+      </c>
+      <c r="I110" s="92" t="inlineStr"/>
+      <c r="J110" s="92" t="inlineStr">
+        <is>
           <t>AUTO_INCREMENT</t>
         </is>
       </c>
-      <c r="K109" s="92" t="inlineStr">
+      <c r="K110" s="92" t="inlineStr">
         <is>
           <t>row PK</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="91" t="n"/>
-      <c r="B110" s="91" t="n"/>
-      <c r="C110" s="92" t="inlineStr">
-        <is>
-          <t>recipient_id</t>
-        </is>
-      </c>
-      <c r="D110" s="92" t="inlineStr">
-        <is>
-          <t>수신자 ID</t>
-        </is>
-      </c>
-      <c r="E110" s="92" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F110" s="92" t="inlineStr">
-        <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="G110" s="92" t="inlineStr"/>
-      <c r="H110" s="92" t="inlineStr"/>
-      <c r="I110" s="92" t="inlineStr">
-        <is>
-          <t>recipients.id</t>
-        </is>
-      </c>
-      <c r="J110" s="92" t="inlineStr">
-        <is>
-          <t>ON DELETE RESTRICT</t>
-        </is>
-      </c>
-      <c r="K110" s="92" t="inlineStr">
-        <is>
-          <t>발송 대상 수신자</t>
         </is>
       </c>
     </row>
@@ -7148,12 +7148,12 @@
       <c r="B111" s="91" t="n"/>
       <c r="C111" s="92" t="inlineStr">
         <is>
-          <t>briefing_date</t>
+          <t>recipient_id</t>
         </is>
       </c>
       <c r="D111" s="92" t="inlineStr">
         <is>
-          <t>브리핑 날짜</t>
+          <t>수신자 ID</t>
         </is>
       </c>
       <c r="E111" s="92" t="inlineStr">
@@ -7163,16 +7163,24 @@
       </c>
       <c r="F111" s="92" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="G111" s="92" t="inlineStr"/>
       <c r="H111" s="92" t="inlineStr"/>
-      <c r="I111" s="92" t="inlineStr"/>
-      <c r="J111" s="92" t="inlineStr"/>
+      <c r="I111" s="92" t="inlineStr">
+        <is>
+          <t>recipients.id</t>
+        </is>
+      </c>
+      <c r="J111" s="92" t="inlineStr">
+        <is>
+          <t>ON DELETE RESTRICT</t>
+        </is>
+      </c>
       <c r="K111" s="92" t="inlineStr">
         <is>
-          <t>어느 영업일의 브리핑인지</t>
+          <t>발송 대상 수신자</t>
         </is>
       </c>
     </row>
@@ -7181,35 +7189,31 @@
       <c r="B112" s="91" t="n"/>
       <c r="C112" s="92" t="inlineStr">
         <is>
-          <t>run_id</t>
+          <t>briefing_date</t>
         </is>
       </c>
       <c r="D112" s="92" t="inlineStr">
         <is>
-          <t>실행 ID</t>
+          <t>브리핑 날짜</t>
         </is>
       </c>
       <c r="E112" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F112" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G112" s="92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="G112" s="92" t="inlineStr"/>
       <c r="H112" s="92" t="inlineStr"/>
       <c r="I112" s="92" t="inlineStr"/>
       <c r="J112" s="92" t="inlineStr"/>
       <c r="K112" s="92" t="inlineStr">
         <is>
-          <t>한 cycle 식별자 (재시도 추적)</t>
+          <t>어느 영업일의 브리핑인지</t>
         </is>
       </c>
     </row>
@@ -7218,35 +7222,35 @@
       <c r="B113" s="91" t="n"/>
       <c r="C113" s="92" t="inlineStr">
         <is>
-          <t>card_count</t>
+          <t>run_id</t>
         </is>
       </c>
       <c r="D113" s="92" t="inlineStr">
         <is>
-          <t>카드 수</t>
+          <t>실행 ID</t>
         </is>
       </c>
       <c r="E113" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F113" s="92" t="inlineStr">
         <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="G113" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G113" s="92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="H113" s="92" t="inlineStr"/>
       <c r="I113" s="92" t="inlineStr"/>
-      <c r="J113" s="92" t="inlineStr">
-        <is>
-          <t>Default 0</t>
-        </is>
-      </c>
+      <c r="J113" s="92" t="inlineStr"/>
       <c r="K113" s="92" t="inlineStr">
         <is>
-          <t>발송된 카드 개수</t>
+          <t>한 cycle 식별자 (재시도 추적)</t>
         </is>
       </c>
     </row>
@@ -7255,22 +7259,22 @@
       <c r="B114" s="91" t="n"/>
       <c r="C114" s="92" t="inlineStr">
         <is>
-          <t>card_ids</t>
+          <t>card_count</t>
         </is>
       </c>
       <c r="D114" s="92" t="inlineStr">
         <is>
-          <t>카드 ID 배열</t>
+          <t>카드 수</t>
         </is>
       </c>
       <c r="E114" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F114" s="92" t="inlineStr">
         <is>
-          <t>TEXT[]</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="G114" s="92" t="inlineStr"/>
@@ -7278,12 +7282,12 @@
       <c r="I114" s="92" t="inlineStr"/>
       <c r="J114" s="92" t="inlineStr">
         <is>
-          <t>Default '{}'</t>
+          <t>Default 0</t>
         </is>
       </c>
       <c r="K114" s="92" t="inlineStr">
         <is>
-          <t>포함된 issue_cards.id 배열</t>
+          <t>발송된 카드 개수</t>
         </is>
       </c>
     </row>
@@ -7292,12 +7296,12 @@
       <c r="B115" s="91" t="n"/>
       <c r="C115" s="92" t="inlineStr">
         <is>
-          <t>subject</t>
+          <t>card_ids</t>
         </is>
       </c>
       <c r="D115" s="92" t="inlineStr">
         <is>
-          <t>메일 제목</t>
+          <t>카드 ID 배열</t>
         </is>
       </c>
       <c r="E115" s="92" t="inlineStr">
@@ -7307,16 +7311,20 @@
       </c>
       <c r="F115" s="92" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>TEXT[]</t>
         </is>
       </c>
       <c r="G115" s="92" t="inlineStr"/>
       <c r="H115" s="92" t="inlineStr"/>
       <c r="I115" s="92" t="inlineStr"/>
-      <c r="J115" s="92" t="inlineStr"/>
+      <c r="J115" s="92" t="inlineStr">
+        <is>
+          <t>Default '{}'</t>
+        </is>
+      </c>
       <c r="K115" s="92" t="inlineStr">
         <is>
-          <t>메일 제목 (저장 옵션)</t>
+          <t>포함된 issue_cards.id 배열</t>
         </is>
       </c>
     </row>
@@ -7325,12 +7333,12 @@
       <c r="B116" s="91" t="n"/>
       <c r="C116" s="92" t="inlineStr">
         <is>
-          <t>body_preview</t>
+          <t>subject</t>
         </is>
       </c>
       <c r="D116" s="92" t="inlineStr">
         <is>
-          <t>본문 미리보기</t>
+          <t>메일 제목</t>
         </is>
       </c>
       <c r="E116" s="92" t="inlineStr">
@@ -7346,14 +7354,10 @@
       <c r="G116" s="92" t="inlineStr"/>
       <c r="H116" s="92" t="inlineStr"/>
       <c r="I116" s="92" t="inlineStr"/>
-      <c r="J116" s="92" t="inlineStr">
-        <is>
-          <t>첫 200자</t>
-        </is>
-      </c>
+      <c r="J116" s="92" t="inlineStr"/>
       <c r="K116" s="92" t="inlineStr">
         <is>
-          <t>본문 첫 200자 (감사 + 디버깅)</t>
+          <t>메일 제목 (저장 옵션)</t>
         </is>
       </c>
     </row>
@@ -7362,39 +7366,35 @@
       <c r="B117" s="91" t="n"/>
       <c r="C117" s="92" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>body_preview</t>
         </is>
       </c>
       <c r="D117" s="92" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>본문 미리보기</t>
         </is>
       </c>
       <c r="E117" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F117" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G117" s="92" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="G117" s="92" t="inlineStr"/>
       <c r="H117" s="92" t="inlineStr"/>
       <c r="I117" s="92" t="inlineStr"/>
       <c r="J117" s="92" t="inlineStr">
         <is>
-          <t>sent|failed|skipped</t>
+          <t>첫 200자</t>
         </is>
       </c>
       <c r="K117" s="92" t="inlineStr">
         <is>
-          <t>발송 결과</t>
+          <t>본문 첫 200자 (감사 + 디버깅)</t>
         </is>
       </c>
     </row>
@@ -7403,31 +7403,39 @@
       <c r="B118" s="91" t="n"/>
       <c r="C118" s="92" t="inlineStr">
         <is>
-          <t>smtp_response</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D118" s="92" t="inlineStr">
         <is>
-          <t>SMTP 응답</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="E118" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F118" s="92" t="inlineStr">
         <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="G118" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G118" s="92" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="H118" s="92" t="inlineStr"/>
       <c r="I118" s="92" t="inlineStr"/>
-      <c r="J118" s="92" t="inlineStr"/>
+      <c r="J118" s="92" t="inlineStr">
+        <is>
+          <t>sent|failed|skipped</t>
+        </is>
+      </c>
       <c r="K118" s="92" t="inlineStr">
         <is>
-          <t>SendGrid/SMTP 응답 코드 + 메시지</t>
+          <t>발송 결과</t>
         </is>
       </c>
     </row>
@@ -7436,12 +7444,12 @@
       <c r="B119" s="91" t="n"/>
       <c r="C119" s="92" t="inlineStr">
         <is>
-          <t>error_msg</t>
+          <t>smtp_response</t>
         </is>
       </c>
       <c r="D119" s="92" t="inlineStr">
         <is>
-          <t>에러 메시지</t>
+          <t>SMTP 응답</t>
         </is>
       </c>
       <c r="E119" s="92" t="inlineStr">
@@ -7460,7 +7468,7 @@
       <c r="J119" s="92" t="inlineStr"/>
       <c r="K119" s="92" t="inlineStr">
         <is>
-          <t>status=failed 시 상세</t>
+          <t>SendGrid/SMTP 응답 코드 + 메시지</t>
         </is>
       </c>
     </row>
@@ -7469,12 +7477,12 @@
       <c r="B120" s="91" t="n"/>
       <c r="C120" s="92" t="inlineStr">
         <is>
-          <t>retry_count</t>
+          <t>error_msg</t>
         </is>
       </c>
       <c r="D120" s="92" t="inlineStr">
         <is>
-          <t>재시도 횟수</t>
+          <t>에러 메시지</t>
         </is>
       </c>
       <c r="E120" s="92" t="inlineStr">
@@ -7484,20 +7492,16 @@
       </c>
       <c r="F120" s="92" t="inlineStr">
         <is>
-          <t>SMALLINT</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="G120" s="92" t="inlineStr"/>
       <c r="H120" s="92" t="inlineStr"/>
       <c r="I120" s="92" t="inlineStr"/>
-      <c r="J120" s="92" t="inlineStr">
-        <is>
-          <t>Default 0</t>
-        </is>
-      </c>
+      <c r="J120" s="92" t="inlineStr"/>
       <c r="K120" s="92" t="inlineStr">
         <is>
-          <t>EmailAgent retry ×3 횟수</t>
+          <t>status=failed 시 상세</t>
         </is>
       </c>
     </row>
@@ -7506,12 +7510,12 @@
       <c r="B121" s="91" t="n"/>
       <c r="C121" s="92" t="inlineStr">
         <is>
-          <t>sent_at</t>
+          <t>retry_count</t>
         </is>
       </c>
       <c r="D121" s="92" t="inlineStr">
         <is>
-          <t>발송 시각</t>
+          <t>재시도 횟수</t>
         </is>
       </c>
       <c r="E121" s="92" t="inlineStr">
@@ -7521,7 +7525,7 @@
       </c>
       <c r="F121" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>SMALLINT</t>
         </is>
       </c>
       <c r="G121" s="92" t="inlineStr"/>
@@ -7529,12 +7533,12 @@
       <c r="I121" s="92" t="inlineStr"/>
       <c r="J121" s="92" t="inlineStr">
         <is>
-          <t>Default NOW()</t>
+          <t>Default 0</t>
         </is>
       </c>
       <c r="K121" s="92" t="inlineStr">
         <is>
-          <t>메일 발송 완료 시각</t>
+          <t>EmailAgent retry ×3 횟수</t>
         </is>
       </c>
     </row>
@@ -7543,12 +7547,12 @@
       <c r="B122" s="91" t="n"/>
       <c r="C122" s="92" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>sent_at</t>
         </is>
       </c>
       <c r="D122" s="92" t="inlineStr">
         <is>
-          <t>생성 시각</t>
+          <t>발송 시각</t>
         </is>
       </c>
       <c r="E122" s="92" t="inlineStr">
@@ -7571,93 +7575,93 @@
       </c>
       <c r="K122" s="92" t="inlineStr">
         <is>
-          <t>row 생성 시각</t>
+          <t>메일 발송 완료 시각</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="91" t="inlineStr">
-        <is>
-          <t>pipeline_logs</t>
-        </is>
-      </c>
-      <c r="B123" s="91" t="inlineStr">
-        <is>
-          <t>파이프라인 실행 로그</t>
-        </is>
-      </c>
+      <c r="A123" s="91" t="n"/>
+      <c r="B123" s="91" t="n"/>
       <c r="C123" s="92" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D123" s="92" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>생성 시각</t>
         </is>
       </c>
       <c r="E123" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F123" s="92" t="inlineStr">
         <is>
-          <t>BIGSERIAL</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="G123" s="92" t="inlineStr"/>
-      <c r="H123" s="92" t="inlineStr">
-        <is>
-          <t>PK1</t>
-        </is>
-      </c>
+      <c r="H123" s="92" t="inlineStr"/>
       <c r="I123" s="92" t="inlineStr"/>
       <c r="J123" s="92" t="inlineStr">
         <is>
+          <t>Default NOW()</t>
+        </is>
+      </c>
+      <c r="K123" s="92" t="inlineStr">
+        <is>
+          <t>row 생성 시각</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="91" t="inlineStr">
+        <is>
+          <t>pipeline_logs</t>
+        </is>
+      </c>
+      <c r="B124" s="91" t="inlineStr">
+        <is>
+          <t>파이프라인 실행 로그</t>
+        </is>
+      </c>
+      <c r="C124" s="92" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D124" s="92" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="E124" s="92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F124" s="92" t="inlineStr">
+        <is>
+          <t>BIGSERIAL</t>
+        </is>
+      </c>
+      <c r="G124" s="92" t="inlineStr"/>
+      <c r="H124" s="92" t="inlineStr">
+        <is>
+          <t>PK1</t>
+        </is>
+      </c>
+      <c r="I124" s="92" t="inlineStr"/>
+      <c r="J124" s="92" t="inlineStr">
+        <is>
           <t>AUTO_INCREMENT</t>
         </is>
       </c>
-      <c r="K123" s="92" t="inlineStr">
+      <c r="K124" s="92" t="inlineStr">
         <is>
           <t>row PK</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="91" t="n"/>
-      <c r="B124" s="91" t="n"/>
-      <c r="C124" s="92" t="inlineStr">
-        <is>
-          <t>pipeline_step</t>
-        </is>
-      </c>
-      <c r="D124" s="92" t="inlineStr">
-        <is>
-          <t>파이프라인 단계</t>
-        </is>
-      </c>
-      <c r="E124" s="92" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F124" s="92" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G124" s="92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H124" s="92" t="inlineStr"/>
-      <c r="I124" s="92" t="inlineStr"/>
-      <c r="J124" s="92" t="inlineStr"/>
-      <c r="K124" s="92" t="inlineStr">
-        <is>
-          <t>단계 식별자 (crawl · credibility · dedup 등)</t>
         </is>
       </c>
     </row>
@@ -7666,17 +7670,17 @@
       <c r="B125" s="91" t="n"/>
       <c r="C125" s="92" t="inlineStr">
         <is>
-          <t>peer_id</t>
+          <t>pipeline_step</t>
         </is>
       </c>
       <c r="D125" s="92" t="inlineStr">
         <is>
-          <t>Peer ID</t>
+          <t>파이프라인 단계</t>
         </is>
       </c>
       <c r="E125" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F125" s="92" t="inlineStr">
@@ -7694,7 +7698,7 @@
       <c r="J125" s="92" t="inlineStr"/>
       <c r="K125" s="92" t="inlineStr">
         <is>
-          <t>처리한 Peer (전체 단계면 NULL)</t>
+          <t>단계 식별자 (crawl · credibility · dedup 등)</t>
         </is>
       </c>
     </row>
@@ -7703,12 +7707,12 @@
       <c r="B126" s="91" t="n"/>
       <c r="C126" s="92" t="inlineStr">
         <is>
-          <t>input_count</t>
+          <t>peer_id</t>
         </is>
       </c>
       <c r="D126" s="92" t="inlineStr">
         <is>
-          <t>입력 건수</t>
+          <t>Peer ID</t>
         </is>
       </c>
       <c r="E126" s="92" t="inlineStr">
@@ -7718,16 +7722,20 @@
       </c>
       <c r="F126" s="92" t="inlineStr">
         <is>
-          <t>INT</t>
-        </is>
-      </c>
-      <c r="G126" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G126" s="92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="H126" s="92" t="inlineStr"/>
       <c r="I126" s="92" t="inlineStr"/>
       <c r="J126" s="92" t="inlineStr"/>
       <c r="K126" s="92" t="inlineStr">
         <is>
-          <t>단계 입력 article 또는 cluster 수</t>
+          <t>처리한 Peer (전체 단계면 NULL)</t>
         </is>
       </c>
     </row>
@@ -7736,12 +7744,12 @@
       <c r="B127" s="91" t="n"/>
       <c r="C127" s="92" t="inlineStr">
         <is>
-          <t>output_count</t>
+          <t>input_count</t>
         </is>
       </c>
       <c r="D127" s="92" t="inlineStr">
         <is>
-          <t>출력 건수</t>
+          <t>입력 건수</t>
         </is>
       </c>
       <c r="E127" s="92" t="inlineStr">
@@ -7760,7 +7768,7 @@
       <c r="J127" s="92" t="inlineStr"/>
       <c r="K127" s="92" t="inlineStr">
         <is>
-          <t>단계 출력 건수</t>
+          <t>단계 입력 article 또는 cluster 수</t>
         </is>
       </c>
     </row>
@@ -7769,12 +7777,12 @@
       <c r="B128" s="91" t="n"/>
       <c r="C128" s="92" t="inlineStr">
         <is>
-          <t>elapsed_ms</t>
+          <t>output_count</t>
         </is>
       </c>
       <c r="D128" s="92" t="inlineStr">
         <is>
-          <t>소요 시간</t>
+          <t>출력 건수</t>
         </is>
       </c>
       <c r="E128" s="92" t="inlineStr">
@@ -7790,14 +7798,10 @@
       <c r="G128" s="92" t="inlineStr"/>
       <c r="H128" s="92" t="inlineStr"/>
       <c r="I128" s="92" t="inlineStr"/>
-      <c r="J128" s="92" t="inlineStr">
-        <is>
-          <t>단위: ms</t>
-        </is>
-      </c>
+      <c r="J128" s="92" t="inlineStr"/>
       <c r="K128" s="92" t="inlineStr">
         <is>
-          <t>단계 실행 소요 ms</t>
+          <t>단계 출력 건수</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7810,12 @@
       <c r="B129" s="91" t="n"/>
       <c r="C129" s="92" t="inlineStr">
         <is>
-          <t>llm_tokens_used</t>
+          <t>elapsed_ms</t>
         </is>
       </c>
       <c r="D129" s="92" t="inlineStr">
         <is>
-          <t>LLM 토큰</t>
+          <t>소요 시간</t>
         </is>
       </c>
       <c r="E129" s="92" t="inlineStr">
@@ -7826,19 +7830,15 @@
       </c>
       <c r="G129" s="92" t="inlineStr"/>
       <c r="H129" s="92" t="inlineStr"/>
-      <c r="I129" s="92" t="inlineStr">
-        <is>
-          <t>Default 0</t>
-        </is>
-      </c>
+      <c r="I129" s="92" t="inlineStr"/>
       <c r="J129" s="92" t="inlineStr">
         <is>
-          <t>단계 별 OpenAI 토큰 사용량 합계</t>
+          <t>단위: ms</t>
         </is>
       </c>
       <c r="K129" s="92" t="inlineStr">
         <is>
-          <t>비용 추적</t>
+          <t>단계 실행 소요 ms</t>
         </is>
       </c>
     </row>
@@ -7847,12 +7847,12 @@
       <c r="B130" s="91" t="n"/>
       <c r="C130" s="92" t="inlineStr">
         <is>
-          <t>error_msg</t>
+          <t>llm_tokens_used</t>
         </is>
       </c>
       <c r="D130" s="92" t="inlineStr">
         <is>
-          <t>에러 메시지</t>
+          <t>LLM 토큰</t>
         </is>
       </c>
       <c r="E130" s="92" t="inlineStr">
@@ -7862,16 +7862,24 @@
       </c>
       <c r="F130" s="92" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="G130" s="92" t="inlineStr"/>
       <c r="H130" s="92" t="inlineStr"/>
-      <c r="I130" s="92" t="inlineStr"/>
-      <c r="J130" s="92" t="inlineStr"/>
+      <c r="I130" s="92" t="inlineStr">
+        <is>
+          <t>Default 0</t>
+        </is>
+      </c>
+      <c r="J130" s="92" t="inlineStr">
+        <is>
+          <t>단계 별 OpenAI 토큰 사용량 합계</t>
+        </is>
+      </c>
       <c r="K130" s="92" t="inlineStr">
         <is>
-          <t>에러 시 메시지 (정상 시 NULL)</t>
+          <t>비용 추적</t>
         </is>
       </c>
     </row>
@@ -7880,12 +7888,12 @@
       <c r="B131" s="91" t="n"/>
       <c r="C131" s="92" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>error_msg</t>
         </is>
       </c>
       <c r="D131" s="92" t="inlineStr">
         <is>
-          <t>기록 시각</t>
+          <t>에러 메시지</t>
         </is>
       </c>
       <c r="E131" s="92" t="inlineStr">
@@ -7895,106 +7903,102 @@
       </c>
       <c r="F131" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="G131" s="92" t="inlineStr"/>
       <c r="H131" s="92" t="inlineStr"/>
       <c r="I131" s="92" t="inlineStr"/>
-      <c r="J131" s="92" t="inlineStr">
-        <is>
-          <t>Default NOW()</t>
-        </is>
-      </c>
+      <c r="J131" s="92" t="inlineStr"/>
       <c r="K131" s="92" t="inlineStr">
         <is>
-          <t>로그 기록 시각</t>
+          <t>에러 시 메시지 (정상 시 NULL)</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="91" t="inlineStr">
-        <is>
-          <t>crawl_logs</t>
-        </is>
-      </c>
-      <c r="B132" s="91" t="inlineStr">
-        <is>
-          <t>크롤러 실행 로그</t>
-        </is>
-      </c>
+      <c r="A132" s="91" t="n"/>
+      <c r="B132" s="91" t="n"/>
       <c r="C132" s="92" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D132" s="92" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>기록 시각</t>
         </is>
       </c>
       <c r="E132" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F132" s="92" t="inlineStr">
         <is>
-          <t>BIGSERIAL</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="G132" s="92" t="inlineStr"/>
-      <c r="H132" s="92" t="inlineStr">
-        <is>
-          <t>PK1</t>
-        </is>
-      </c>
+      <c r="H132" s="92" t="inlineStr"/>
       <c r="I132" s="92" t="inlineStr"/>
       <c r="J132" s="92" t="inlineStr">
         <is>
+          <t>Default NOW()</t>
+        </is>
+      </c>
+      <c r="K132" s="92" t="inlineStr">
+        <is>
+          <t>로그 기록 시각</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="91" t="inlineStr">
+        <is>
+          <t>crawl_logs</t>
+        </is>
+      </c>
+      <c r="B133" s="91" t="inlineStr">
+        <is>
+          <t>크롤러 실행 로그</t>
+        </is>
+      </c>
+      <c r="C133" s="92" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D133" s="92" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="E133" s="92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F133" s="92" t="inlineStr">
+        <is>
+          <t>BIGSERIAL</t>
+        </is>
+      </c>
+      <c r="G133" s="92" t="inlineStr"/>
+      <c r="H133" s="92" t="inlineStr">
+        <is>
+          <t>PK1</t>
+        </is>
+      </c>
+      <c r="I133" s="92" t="inlineStr"/>
+      <c r="J133" s="92" t="inlineStr">
+        <is>
           <t>AUTO_INCREMENT</t>
         </is>
       </c>
-      <c r="K132" s="92" t="inlineStr">
+      <c r="K133" s="92" t="inlineStr">
         <is>
           <t>row PK</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="91" t="n"/>
-      <c r="B133" s="91" t="n"/>
-      <c r="C133" s="92" t="inlineStr">
-        <is>
-          <t>peer_id</t>
-        </is>
-      </c>
-      <c r="D133" s="92" t="inlineStr">
-        <is>
-          <t>Peer ID</t>
-        </is>
-      </c>
-      <c r="E133" s="92" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F133" s="92" t="inlineStr">
-        <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G133" s="92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H133" s="92" t="inlineStr"/>
-      <c r="I133" s="92" t="inlineStr"/>
-      <c r="J133" s="92" t="inlineStr"/>
-      <c r="K133" s="92" t="inlineStr">
-        <is>
-          <t>크롤링 대상 Peer</t>
         </is>
       </c>
     </row>
@@ -8003,12 +8007,12 @@
       <c r="B134" s="91" t="n"/>
       <c r="C134" s="92" t="inlineStr">
         <is>
-          <t>source_name</t>
+          <t>peer_id</t>
         </is>
       </c>
       <c r="D134" s="92" t="inlineStr">
         <is>
-          <t>출처 이름</t>
+          <t>Peer ID</t>
         </is>
       </c>
       <c r="E134" s="92" t="inlineStr">
@@ -8023,7 +8027,7 @@
       </c>
       <c r="G134" s="92" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H134" s="92" t="inlineStr"/>
@@ -8031,7 +8035,7 @@
       <c r="J134" s="92" t="inlineStr"/>
       <c r="K134" s="92" t="inlineStr">
         <is>
-          <t>크롤링 소스 (DART · 한경 등)</t>
+          <t>크롤링 대상 Peer</t>
         </is>
       </c>
     </row>
@@ -8040,12 +8044,12 @@
       <c r="B135" s="91" t="n"/>
       <c r="C135" s="92" t="inlineStr">
         <is>
-          <t>started_at</t>
+          <t>source_name</t>
         </is>
       </c>
       <c r="D135" s="92" t="inlineStr">
         <is>
-          <t>시작 시각</t>
+          <t>출처 이름</t>
         </is>
       </c>
       <c r="E135" s="92" t="inlineStr">
@@ -8055,16 +8059,20 @@
       </c>
       <c r="F135" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
-        </is>
-      </c>
-      <c r="G135" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G135" s="92" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="H135" s="92" t="inlineStr"/>
       <c r="I135" s="92" t="inlineStr"/>
       <c r="J135" s="92" t="inlineStr"/>
       <c r="K135" s="92" t="inlineStr">
         <is>
-          <t>크롤링 시작 시각</t>
+          <t>크롤링 소스 (DART · 한경 등)</t>
         </is>
       </c>
     </row>
@@ -8073,17 +8081,17 @@
       <c r="B136" s="91" t="n"/>
       <c r="C136" s="92" t="inlineStr">
         <is>
-          <t>finished_at</t>
+          <t>started_at</t>
         </is>
       </c>
       <c r="D136" s="92" t="inlineStr">
         <is>
-          <t>완료 시각</t>
+          <t>시작 시각</t>
         </is>
       </c>
       <c r="E136" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F136" s="92" t="inlineStr">
@@ -8097,7 +8105,7 @@
       <c r="J136" s="92" t="inlineStr"/>
       <c r="K136" s="92" t="inlineStr">
         <is>
-          <t>크롤링 완료 시각 (실패 시 NULL)</t>
+          <t>크롤링 시작 시각</t>
         </is>
       </c>
     </row>
@@ -8106,12 +8114,12 @@
       <c r="B137" s="91" t="n"/>
       <c r="C137" s="92" t="inlineStr">
         <is>
-          <t>total_count</t>
+          <t>finished_at</t>
         </is>
       </c>
       <c r="D137" s="92" t="inlineStr">
         <is>
-          <t>전체 건수</t>
+          <t>완료 시각</t>
         </is>
       </c>
       <c r="E137" s="92" t="inlineStr">
@@ -8121,20 +8129,16 @@
       </c>
       <c r="F137" s="92" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="G137" s="92" t="inlineStr"/>
       <c r="H137" s="92" t="inlineStr"/>
       <c r="I137" s="92" t="inlineStr"/>
-      <c r="J137" s="92" t="inlineStr">
-        <is>
-          <t>Default 0</t>
-        </is>
-      </c>
+      <c r="J137" s="92" t="inlineStr"/>
       <c r="K137" s="92" t="inlineStr">
         <is>
-          <t>수집 시도 총 건수</t>
+          <t>크롤링 완료 시각 (실패 시 NULL)</t>
         </is>
       </c>
     </row>
@@ -8143,12 +8147,12 @@
       <c r="B138" s="91" t="n"/>
       <c r="C138" s="92" t="inlineStr">
         <is>
-          <t>success_count</t>
+          <t>total_count</t>
         </is>
       </c>
       <c r="D138" s="92" t="inlineStr">
         <is>
-          <t>성공 건수</t>
+          <t>전체 건수</t>
         </is>
       </c>
       <c r="E138" s="92" t="inlineStr">
@@ -8171,7 +8175,7 @@
       </c>
       <c r="K138" s="92" t="inlineStr">
         <is>
-          <t>INSERT 성공 건수</t>
+          <t>수집 시도 총 건수</t>
         </is>
       </c>
     </row>
@@ -8180,12 +8184,12 @@
       <c r="B139" s="91" t="n"/>
       <c r="C139" s="92" t="inlineStr">
         <is>
-          <t>skipped_count</t>
+          <t>success_count</t>
         </is>
       </c>
       <c r="D139" s="92" t="inlineStr">
         <is>
-          <t>스킵 건수</t>
+          <t>성공 건수</t>
         </is>
       </c>
       <c r="E139" s="92" t="inlineStr">
@@ -8208,7 +8212,7 @@
       </c>
       <c r="K139" s="92" t="inlineStr">
         <is>
-          <t>중복/품질 미달로 스킵된 건수</t>
+          <t>INSERT 성공 건수</t>
         </is>
       </c>
     </row>
@@ -8217,12 +8221,12 @@
       <c r="B140" s="91" t="n"/>
       <c r="C140" s="92" t="inlineStr">
         <is>
-          <t>error_msg</t>
+          <t>skipped_count</t>
         </is>
       </c>
       <c r="D140" s="92" t="inlineStr">
         <is>
-          <t>에러 메시지</t>
+          <t>스킵 건수</t>
         </is>
       </c>
       <c r="E140" s="92" t="inlineStr">
@@ -8232,16 +8236,20 @@
       </c>
       <c r="F140" s="92" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="G140" s="92" t="inlineStr"/>
       <c r="H140" s="92" t="inlineStr"/>
       <c r="I140" s="92" t="inlineStr"/>
-      <c r="J140" s="92" t="inlineStr"/>
+      <c r="J140" s="92" t="inlineStr">
+        <is>
+          <t>Default 0</t>
+        </is>
+      </c>
       <c r="K140" s="92" t="inlineStr">
         <is>
-          <t>전체 작업 실패 시 에러</t>
+          <t>중복/품질 미달로 스킵된 건수</t>
         </is>
       </c>
     </row>
@@ -8250,12 +8258,12 @@
       <c r="B141" s="91" t="n"/>
       <c r="C141" s="92" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>error_msg</t>
         </is>
       </c>
       <c r="D141" s="92" t="inlineStr">
         <is>
-          <t>기록 시각</t>
+          <t>에러 메시지</t>
         </is>
       </c>
       <c r="E141" s="92" t="inlineStr">
@@ -8265,102 +8273,102 @@
       </c>
       <c r="F141" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="G141" s="92" t="inlineStr"/>
       <c r="H141" s="92" t="inlineStr"/>
       <c r="I141" s="92" t="inlineStr"/>
-      <c r="J141" s="92" t="inlineStr">
-        <is>
-          <t>Default NOW()</t>
-        </is>
-      </c>
+      <c r="J141" s="92" t="inlineStr"/>
       <c r="K141" s="92" t="inlineStr">
         <is>
-          <t>로그 기록 시각</t>
+          <t>전체 작업 실패 시 에러</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="91" t="inlineStr">
-        <is>
-          <t>golden_set</t>
-        </is>
-      </c>
-      <c r="B142" s="91" t="inlineStr">
-        <is>
-          <t>RAG 평가용 골든셋</t>
-        </is>
-      </c>
+      <c r="A142" s="91" t="n"/>
+      <c r="B142" s="91" t="n"/>
       <c r="C142" s="92" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D142" s="92" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>기록 시각</t>
         </is>
       </c>
       <c r="E142" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F142" s="92" t="inlineStr">
         <is>
-          <t>BIGSERIAL</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="G142" s="92" t="inlineStr"/>
-      <c r="H142" s="92" t="inlineStr">
-        <is>
-          <t>PK1</t>
-        </is>
-      </c>
+      <c r="H142" s="92" t="inlineStr"/>
       <c r="I142" s="92" t="inlineStr"/>
       <c r="J142" s="92" t="inlineStr">
         <is>
+          <t>Default NOW()</t>
+        </is>
+      </c>
+      <c r="K142" s="92" t="inlineStr">
+        <is>
+          <t>로그 기록 시각</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="91" t="inlineStr">
+        <is>
+          <t>golden_set</t>
+        </is>
+      </c>
+      <c r="B143" s="91" t="inlineStr">
+        <is>
+          <t>RAG 평가용 골든셋</t>
+        </is>
+      </c>
+      <c r="C143" s="92" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="D143" s="92" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="E143" s="92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F143" s="92" t="inlineStr">
+        <is>
+          <t>BIGSERIAL</t>
+        </is>
+      </c>
+      <c r="G143" s="92" t="inlineStr"/>
+      <c r="H143" s="92" t="inlineStr">
+        <is>
+          <t>PK1</t>
+        </is>
+      </c>
+      <c r="I143" s="92" t="inlineStr"/>
+      <c r="J143" s="92" t="inlineStr">
+        <is>
           <t>AUTO_INCREMENT</t>
         </is>
       </c>
-      <c r="K142" s="92" t="inlineStr">
+      <c r="K143" s="92" t="inlineStr">
         <is>
           <t>row PK</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="91" t="n"/>
-      <c r="B143" s="91" t="n"/>
-      <c r="C143" s="92" t="inlineStr">
-        <is>
-          <t>query</t>
-        </is>
-      </c>
-      <c r="D143" s="92" t="inlineStr">
-        <is>
-          <t>쿼리</t>
-        </is>
-      </c>
-      <c r="E143" s="92" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F143" s="92" t="inlineStr">
-        <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="G143" s="92" t="inlineStr"/>
-      <c r="H143" s="92" t="inlineStr"/>
-      <c r="I143" s="92" t="inlineStr"/>
-      <c r="J143" s="92" t="inlineStr"/>
-      <c r="K143" s="92" t="inlineStr">
-        <is>
-          <t>RAG 평가용 자연어 query</t>
         </is>
       </c>
     </row>
@@ -8369,35 +8377,31 @@
       <c r="B144" s="91" t="n"/>
       <c r="C144" s="92" t="inlineStr">
         <is>
-          <t>expected_card_ids</t>
+          <t>query</t>
         </is>
       </c>
       <c r="D144" s="92" t="inlineStr">
         <is>
-          <t>기대 카드 ID</t>
+          <t>쿼리</t>
         </is>
       </c>
       <c r="E144" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F144" s="92" t="inlineStr">
         <is>
-          <t>TEXT[]</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="G144" s="92" t="inlineStr"/>
       <c r="H144" s="92" t="inlineStr"/>
       <c r="I144" s="92" t="inlineStr"/>
-      <c r="J144" s="92" t="inlineStr">
-        <is>
-          <t>Default '{}'</t>
-        </is>
-      </c>
+      <c r="J144" s="92" t="inlineStr"/>
       <c r="K144" s="92" t="inlineStr">
         <is>
-          <t>정답 카드 ID 배열</t>
+          <t>RAG 평가용 자연어 query</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8410,12 @@
       <c r="B145" s="91" t="n"/>
       <c r="C145" s="92" t="inlineStr">
         <is>
-          <t>annotator</t>
+          <t>expected_card_ids</t>
         </is>
       </c>
       <c r="D145" s="92" t="inlineStr">
         <is>
-          <t>라벨러</t>
+          <t>기대 카드 ID</t>
         </is>
       </c>
       <c r="E145" s="92" t="inlineStr">
@@ -8421,20 +8425,20 @@
       </c>
       <c r="F145" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G145" s="92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>TEXT[]</t>
+        </is>
+      </c>
+      <c r="G145" s="92" t="inlineStr"/>
       <c r="H145" s="92" t="inlineStr"/>
       <c r="I145" s="92" t="inlineStr"/>
-      <c r="J145" s="92" t="inlineStr"/>
+      <c r="J145" s="92" t="inlineStr">
+        <is>
+          <t>Default '{}'</t>
+        </is>
+      </c>
       <c r="K145" s="92" t="inlineStr">
         <is>
-          <t>라벨링 담당자 이름</t>
+          <t>정답 카드 ID 배열</t>
         </is>
       </c>
     </row>
@@ -8443,12 +8447,12 @@
       <c r="B146" s="91" t="n"/>
       <c r="C146" s="92" t="inlineStr">
         <is>
-          <t>difficulty</t>
+          <t>annotator</t>
         </is>
       </c>
       <c r="D146" s="92" t="inlineStr">
         <is>
-          <t>난이도</t>
+          <t>라벨러</t>
         </is>
       </c>
       <c r="E146" s="92" t="inlineStr">
@@ -8463,19 +8467,15 @@
       </c>
       <c r="G146" s="92" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="H146" s="92" t="inlineStr"/>
       <c r="I146" s="92" t="inlineStr"/>
-      <c r="J146" s="92" t="inlineStr">
-        <is>
-          <t>easy | hard</t>
-        </is>
-      </c>
+      <c r="J146" s="92" t="inlineStr"/>
       <c r="K146" s="92" t="inlineStr">
         <is>
-          <t>평가 난이도 분류</t>
+          <t>라벨링 담당자 이름</t>
         </is>
       </c>
     </row>
@@ -8484,12 +8484,12 @@
       <c r="B147" s="91" t="n"/>
       <c r="C147" s="92" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>difficulty</t>
         </is>
       </c>
       <c r="D147" s="92" t="inlineStr">
         <is>
-          <t>생성 시각</t>
+          <t>난이도</t>
         </is>
       </c>
       <c r="E147" s="92" t="inlineStr">
@@ -8499,18 +8499,59 @@
       </c>
       <c r="F147" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
-        </is>
-      </c>
-      <c r="G147" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G147" s="92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="H147" s="92" t="inlineStr"/>
       <c r="I147" s="92" t="inlineStr"/>
       <c r="J147" s="92" t="inlineStr">
         <is>
+          <t>easy | hard</t>
+        </is>
+      </c>
+      <c r="K147" s="92" t="inlineStr">
+        <is>
+          <t>평가 난이도 분류</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="91" t="n"/>
+      <c r="B148" s="91" t="n"/>
+      <c r="C148" s="92" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="D148" s="92" t="inlineStr">
+        <is>
+          <t>생성 시각</t>
+        </is>
+      </c>
+      <c r="E148" s="92" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F148" s="92" t="inlineStr">
+        <is>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="G148" s="92" t="inlineStr"/>
+      <c r="H148" s="92" t="inlineStr"/>
+      <c r="I148" s="92" t="inlineStr"/>
+      <c r="J148" s="92" t="inlineStr">
+        <is>
           <t>Default NOW()</t>
         </is>
       </c>
-      <c r="K147" s="92" t="inlineStr">
+      <c r="K148" s="92" t="inlineStr">
         <is>
           <t>row 생성 시각</t>
         </is>

--- a/docs/[13조]_400. 서비스_분석 설계서_434_테이블설계서_v0.1.filled.xlsx
+++ b/docs/[13조]_400. 서비스_분석 설계서_434_테이블설계서_v0.1.filled.xlsx
@@ -2926,7 +2926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K148"/>
+  <dimension ref="A1:K147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5" customHeight="1"/>
   <cols>
     <col width="18" customWidth="1" style="1" min="1" max="1"/>
@@ -3139,39 +3139,35 @@
       <c r="B6" s="91" t="n"/>
       <c r="C6" s="92" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>is_active</t>
         </is>
       </c>
       <c r="D6" s="92" t="inlineStr">
         <is>
-          <t>역할</t>
+          <t>활성 여부</t>
         </is>
       </c>
       <c r="E6" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F6" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G6" s="92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="G6" s="92" t="inlineStr"/>
       <c r="H6" s="92" t="inlineStr"/>
       <c r="I6" s="92" t="inlineStr"/>
       <c r="J6" s="92" t="inlineStr">
         <is>
-          <t>Default 'peer', CHECK (peer|self)</t>
+          <t>Default TRUE</t>
         </is>
       </c>
       <c r="K6" s="92" t="inlineStr">
         <is>
-          <t>peer (경쟁사 4사) | self (SK AX 자사). V5 추가.</t>
+          <t>현재 모니터링 대상인지 여부</t>
         </is>
       </c>
     </row>
@@ -3180,12 +3176,12 @@
       <c r="B7" s="91" t="n"/>
       <c r="C7" s="92" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D7" s="92" t="inlineStr">
         <is>
-          <t>활성 여부</t>
+          <t>생성 시각</t>
         </is>
       </c>
       <c r="E7" s="92" t="inlineStr">
@@ -3195,7 +3191,7 @@
       </c>
       <c r="F7" s="92" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="G7" s="92" t="inlineStr"/>
@@ -3203,71 +3199,75 @@
       <c r="I7" s="92" t="inlineStr"/>
       <c r="J7" s="92" t="inlineStr">
         <is>
-          <t>Default TRUE</t>
+          <t>Default NOW()</t>
         </is>
       </c>
       <c r="K7" s="92" t="inlineStr">
         <is>
-          <t>현재 모니터링 대상인지 여부</t>
+          <t>row 생성 시각</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="91" t="n"/>
-      <c r="B8" s="91" t="n"/>
+      <c r="A8" s="91" t="inlineStr">
+        <is>
+          <t>raw_articles</t>
+        </is>
+      </c>
+      <c r="B8" s="91" t="inlineStr">
+        <is>
+          <t>수집 기사 원문</t>
+        </is>
+      </c>
       <c r="C8" s="92" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D8" s="92" t="inlineStr">
         <is>
-          <t>생성 시각</t>
+          <t>기사 ID</t>
         </is>
       </c>
       <c r="E8" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F8" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>BIGSERIAL</t>
         </is>
       </c>
       <c r="G8" s="92" t="inlineStr"/>
-      <c r="H8" s="92" t="inlineStr"/>
+      <c r="H8" s="92" t="inlineStr">
+        <is>
+          <t>PK1</t>
+        </is>
+      </c>
       <c r="I8" s="92" t="inlineStr"/>
       <c r="J8" s="92" t="inlineStr">
         <is>
-          <t>Default NOW()</t>
+          <t>AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="K8" s="92" t="inlineStr">
         <is>
-          <t>row 생성 시각</t>
+          <t>row 자동 증가 PK</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="91" t="inlineStr">
-        <is>
-          <t>raw_articles</t>
-        </is>
-      </c>
-      <c r="B9" s="91" t="inlineStr">
-        <is>
-          <t>수집 기사 원문</t>
-        </is>
-      </c>
+      <c r="A9" s="91" t="n"/>
+      <c r="B9" s="91" t="n"/>
       <c r="C9" s="92" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>peer_id</t>
         </is>
       </c>
       <c r="D9" s="92" t="inlineStr">
         <is>
-          <t>기사 ID</t>
+          <t>Peer ID</t>
         </is>
       </c>
       <c r="E9" s="92" t="inlineStr">
@@ -3277,24 +3277,24 @@
       </c>
       <c r="F9" s="92" t="inlineStr">
         <is>
-          <t>BIGSERIAL</t>
-        </is>
-      </c>
-      <c r="G9" s="92" t="inlineStr"/>
-      <c r="H9" s="92" t="inlineStr">
-        <is>
-          <t>PK1</t>
-        </is>
-      </c>
-      <c r="I9" s="92" t="inlineStr"/>
-      <c r="J9" s="92" t="inlineStr">
-        <is>
-          <t>AUTO_INCREMENT</t>
-        </is>
-      </c>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G9" s="92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H9" s="92" t="inlineStr"/>
+      <c r="I9" s="92" t="inlineStr">
+        <is>
+          <t>peer_companies.id</t>
+        </is>
+      </c>
+      <c r="J9" s="92" t="inlineStr"/>
       <c r="K9" s="92" t="inlineStr">
         <is>
-          <t>row 자동 증가 PK</t>
+          <t>수집된 기사가 속한 Peer 회사</t>
         </is>
       </c>
     </row>
@@ -3303,12 +3303,12 @@
       <c r="B10" s="91" t="n"/>
       <c r="C10" s="92" t="inlineStr">
         <is>
-          <t>peer_id</t>
+          <t>source_tier</t>
         </is>
       </c>
       <c r="D10" s="92" t="inlineStr">
         <is>
-          <t>Peer ID</t>
+          <t>출처 등급</t>
         </is>
       </c>
       <c r="E10" s="92" t="inlineStr">
@@ -3318,24 +3318,20 @@
       </c>
       <c r="F10" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G10" s="92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>SMALLINT</t>
+        </is>
+      </c>
+      <c r="G10" s="92" t="inlineStr"/>
       <c r="H10" s="92" t="inlineStr"/>
-      <c r="I10" s="92" t="inlineStr">
-        <is>
-          <t>peer_companies.id</t>
-        </is>
-      </c>
-      <c r="J10" s="92" t="inlineStr"/>
+      <c r="I10" s="92" t="inlineStr"/>
+      <c r="J10" s="92" t="inlineStr">
+        <is>
+          <t>1~5</t>
+        </is>
+      </c>
       <c r="K10" s="92" t="inlineStr">
         <is>
-          <t>수집된 기사가 속한 Peer 회사</t>
+          <t>출처 신뢰도 등급 (1=DART, 5=SNS)</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3340,12 @@
       <c r="B11" s="91" t="n"/>
       <c r="C11" s="92" t="inlineStr">
         <is>
-          <t>source_tier</t>
+          <t>source_name</t>
         </is>
       </c>
       <c r="D11" s="92" t="inlineStr">
         <is>
-          <t>출처 등급</t>
+          <t>출처 명</t>
         </is>
       </c>
       <c r="E11" s="92" t="inlineStr">
@@ -3359,20 +3355,20 @@
       </c>
       <c r="F11" s="92" t="inlineStr">
         <is>
-          <t>SMALLINT</t>
-        </is>
-      </c>
-      <c r="G11" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G11" s="92" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="H11" s="92" t="inlineStr"/>
       <c r="I11" s="92" t="inlineStr"/>
-      <c r="J11" s="92" t="inlineStr">
-        <is>
-          <t>1~5</t>
-        </is>
-      </c>
+      <c r="J11" s="92" t="inlineStr"/>
       <c r="K11" s="92" t="inlineStr">
         <is>
-          <t>출처 신뢰도 등급 (1=DART, 5=SNS)</t>
+          <t>수집 소스 이름 (DART · 한경 · Naver 등)</t>
         </is>
       </c>
     </row>
@@ -3381,12 +3377,12 @@
       <c r="B12" s="91" t="n"/>
       <c r="C12" s="92" t="inlineStr">
         <is>
-          <t>source_name</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D12" s="92" t="inlineStr">
         <is>
-          <t>출처 명</t>
+          <t>제목</t>
         </is>
       </c>
       <c r="E12" s="92" t="inlineStr">
@@ -3396,20 +3392,16 @@
       </c>
       <c r="F12" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G12" s="92" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="G12" s="92" t="inlineStr"/>
       <c r="H12" s="92" t="inlineStr"/>
       <c r="I12" s="92" t="inlineStr"/>
       <c r="J12" s="92" t="inlineStr"/>
       <c r="K12" s="92" t="inlineStr">
         <is>
-          <t>수집 소스 이름 (DART · 한경 · Naver 등)</t>
+          <t>기사 제목</t>
         </is>
       </c>
     </row>
@@ -3418,17 +3410,17 @@
       <c r="B13" s="91" t="n"/>
       <c r="C13" s="92" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>content</t>
         </is>
       </c>
       <c r="D13" s="92" t="inlineStr">
         <is>
-          <t>제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="E13" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F13" s="92" t="inlineStr">
@@ -3439,10 +3431,14 @@
       <c r="G13" s="92" t="inlineStr"/>
       <c r="H13" s="92" t="inlineStr"/>
       <c r="I13" s="92" t="inlineStr"/>
-      <c r="J13" s="92" t="inlineStr"/>
+      <c r="J13" s="92" t="inlineStr">
+        <is>
+          <t>최대 10K자 잘라 저장</t>
+        </is>
+      </c>
       <c r="K13" s="92" t="inlineStr">
         <is>
-          <t>기사 제목</t>
+          <t>기사 본문 (요약 또는 full)</t>
         </is>
       </c>
     </row>
@@ -3451,17 +3447,17 @@
       <c r="B14" s="91" t="n"/>
       <c r="C14" s="92" t="inlineStr">
         <is>
-          <t>content</t>
+          <t>url</t>
         </is>
       </c>
       <c r="D14" s="92" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>원문 URL</t>
         </is>
       </c>
       <c r="E14" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F14" s="92" t="inlineStr">
@@ -3474,12 +3470,12 @@
       <c r="I14" s="92" t="inlineStr"/>
       <c r="J14" s="92" t="inlineStr">
         <is>
-          <t>최대 10K자 잘라 저장</t>
+          <t>UNIQUE</t>
         </is>
       </c>
       <c r="K14" s="92" t="inlineStr">
         <is>
-          <t>기사 본문 (요약 또는 full)</t>
+          <t>원문 URL (멱등성 보장 키)</t>
         </is>
       </c>
     </row>
@@ -3488,12 +3484,12 @@
       <c r="B15" s="91" t="n"/>
       <c r="C15" s="92" t="inlineStr">
         <is>
-          <t>url</t>
+          <t>published_at</t>
         </is>
       </c>
       <c r="D15" s="92" t="inlineStr">
         <is>
-          <t>원문 URL</t>
+          <t>발행 시각</t>
         </is>
       </c>
       <c r="E15" s="92" t="inlineStr">
@@ -3503,20 +3499,16 @@
       </c>
       <c r="F15" s="92" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="G15" s="92" t="inlineStr"/>
       <c r="H15" s="92" t="inlineStr"/>
       <c r="I15" s="92" t="inlineStr"/>
-      <c r="J15" s="92" t="inlineStr">
-        <is>
-          <t>UNIQUE</t>
-        </is>
-      </c>
+      <c r="J15" s="92" t="inlineStr"/>
       <c r="K15" s="92" t="inlineStr">
         <is>
-          <t>원문 URL (멱등성 보장 키)</t>
+          <t>원문 발행 시각</t>
         </is>
       </c>
     </row>
@@ -3525,17 +3517,17 @@
       <c r="B16" s="91" t="n"/>
       <c r="C16" s="92" t="inlineStr">
         <is>
-          <t>published_at</t>
+          <t>collected_at</t>
         </is>
       </c>
       <c r="D16" s="92" t="inlineStr">
         <is>
-          <t>발행 시각</t>
+          <t>수집 시각</t>
         </is>
       </c>
       <c r="E16" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F16" s="92" t="inlineStr">
@@ -3546,10 +3538,14 @@
       <c r="G16" s="92" t="inlineStr"/>
       <c r="H16" s="92" t="inlineStr"/>
       <c r="I16" s="92" t="inlineStr"/>
-      <c r="J16" s="92" t="inlineStr"/>
+      <c r="J16" s="92" t="inlineStr">
+        <is>
+          <t>Default NOW()</t>
+        </is>
+      </c>
       <c r="K16" s="92" t="inlineStr">
         <is>
-          <t>원문 발행 시각</t>
+          <t>AXIS 가 수집한 시각</t>
         </is>
       </c>
     </row>
@@ -3558,12 +3554,12 @@
       <c r="B17" s="91" t="n"/>
       <c r="C17" s="92" t="inlineStr">
         <is>
-          <t>collected_at</t>
+          <t>credibility_score</t>
         </is>
       </c>
       <c r="D17" s="92" t="inlineStr">
         <is>
-          <t>수집 시각</t>
+          <t>신뢰도 점수</t>
         </is>
       </c>
       <c r="E17" s="92" t="inlineStr">
@@ -3573,7 +3569,7 @@
       </c>
       <c r="F17" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>FLOAT</t>
         </is>
       </c>
       <c r="G17" s="92" t="inlineStr"/>
@@ -3581,12 +3577,12 @@
       <c r="I17" s="92" t="inlineStr"/>
       <c r="J17" s="92" t="inlineStr">
         <is>
-          <t>Default NOW()</t>
+          <t>0.0~1.0</t>
         </is>
       </c>
       <c r="K17" s="92" t="inlineStr">
         <is>
-          <t>AXIS 가 수집한 시각</t>
+          <t>CredibilityAgent 가 계산한 출처 신뢰도</t>
         </is>
       </c>
     </row>
@@ -3595,12 +3591,12 @@
       <c r="B18" s="91" t="n"/>
       <c r="C18" s="92" t="inlineStr">
         <is>
-          <t>credibility_score</t>
+          <t>credibility_grade</t>
         </is>
       </c>
       <c r="D18" s="92" t="inlineStr">
         <is>
-          <t>신뢰도 점수</t>
+          <t>신뢰도 등급</t>
         </is>
       </c>
       <c r="E18" s="92" t="inlineStr">
@@ -3610,20 +3606,24 @@
       </c>
       <c r="F18" s="92" t="inlineStr">
         <is>
-          <t>FLOAT</t>
-        </is>
-      </c>
-      <c r="G18" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G18" s="92" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="H18" s="92" t="inlineStr"/>
       <c r="I18" s="92" t="inlineStr"/>
       <c r="J18" s="92" t="inlineStr">
         <is>
-          <t>0.0~1.0</t>
+          <t>High|Medium|Low|Unverified</t>
         </is>
       </c>
       <c r="K18" s="92" t="inlineStr">
         <is>
-          <t>CredibilityAgent 가 계산한 출처 신뢰도</t>
+          <t>score 의 등급화 결과</t>
         </is>
       </c>
     </row>
@@ -3632,12 +3632,12 @@
       <c r="B19" s="91" t="n"/>
       <c r="C19" s="92" t="inlineStr">
         <is>
-          <t>credibility_grade</t>
+          <t>cluster_id</t>
         </is>
       </c>
       <c r="D19" s="92" t="inlineStr">
         <is>
-          <t>신뢰도 등급</t>
+          <t>클러스터 ID</t>
         </is>
       </c>
       <c r="E19" s="92" t="inlineStr">
@@ -3647,24 +3647,16 @@
       </c>
       <c r="F19" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G19" s="92" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="G19" s="92" t="inlineStr"/>
       <c r="H19" s="92" t="inlineStr"/>
       <c r="I19" s="92" t="inlineStr"/>
-      <c r="J19" s="92" t="inlineStr">
-        <is>
-          <t>High|Medium|Low|Unverified</t>
-        </is>
-      </c>
+      <c r="J19" s="92" t="inlineStr"/>
       <c r="K19" s="92" t="inlineStr">
         <is>
-          <t>score 의 등급화 결과</t>
+          <t>DedupAgent 가 부여한 동일 이슈 묶음 ID</t>
         </is>
       </c>
     </row>
@@ -3673,12 +3665,12 @@
       <c r="B20" s="91" t="n"/>
       <c r="C20" s="92" t="inlineStr">
         <is>
-          <t>cluster_id</t>
+          <t>is_representative</t>
         </is>
       </c>
       <c r="D20" s="92" t="inlineStr">
         <is>
-          <t>클러스터 ID</t>
+          <t>대표 기사 여부</t>
         </is>
       </c>
       <c r="E20" s="92" t="inlineStr">
@@ -3688,16 +3680,20 @@
       </c>
       <c r="F20" s="92" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="G20" s="92" t="inlineStr"/>
       <c r="H20" s="92" t="inlineStr"/>
       <c r="I20" s="92" t="inlineStr"/>
-      <c r="J20" s="92" t="inlineStr"/>
+      <c r="J20" s="92" t="inlineStr">
+        <is>
+          <t>Default FALSE</t>
+        </is>
+      </c>
       <c r="K20" s="92" t="inlineStr">
         <is>
-          <t>DedupAgent 가 부여한 동일 이슈 묶음 ID</t>
+          <t>클러스터 내 대표 기사 1건 표시</t>
         </is>
       </c>
     </row>
@@ -3706,12 +3702,12 @@
       <c r="B21" s="91" t="n"/>
       <c r="C21" s="92" t="inlineStr">
         <is>
-          <t>is_representative</t>
+          <t>processing_status</t>
         </is>
       </c>
       <c r="D21" s="92" t="inlineStr">
         <is>
-          <t>대표 기사 여부</t>
+          <t>처리 상태</t>
         </is>
       </c>
       <c r="E21" s="92" t="inlineStr">
@@ -3721,20 +3717,24 @@
       </c>
       <c r="F21" s="92" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
-        </is>
-      </c>
-      <c r="G21" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G21" s="92" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="H21" s="92" t="inlineStr"/>
       <c r="I21" s="92" t="inlineStr"/>
       <c r="J21" s="92" t="inlineStr">
         <is>
-          <t>Default FALSE</t>
+          <t>Default 'RAW'</t>
         </is>
       </c>
       <c r="K21" s="92" t="inlineStr">
         <is>
-          <t>클러스터 내 대표 기사 1건 표시</t>
+          <t>RAW · CLUSTERED_REP/DUPE · CLASSIFIED · SKIPPED_QUALITY/CREDIBILITY/ERROR</t>
         </is>
       </c>
     </row>
@@ -3743,12 +3743,12 @@
       <c r="B22" s="91" t="n"/>
       <c r="C22" s="92" t="inlineStr">
         <is>
-          <t>processing_status</t>
+          <t>importance_score</t>
         </is>
       </c>
       <c r="D22" s="92" t="inlineStr">
         <is>
-          <t>처리 상태</t>
+          <t>중요도 점수</t>
         </is>
       </c>
       <c r="E22" s="92" t="inlineStr">
@@ -3758,24 +3758,20 @@
       </c>
       <c r="F22" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G22" s="92" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="G22" s="92" t="inlineStr"/>
       <c r="H22" s="92" t="inlineStr"/>
       <c r="I22" s="92" t="inlineStr"/>
       <c r="J22" s="92" t="inlineStr">
         <is>
-          <t>Default 'RAW'</t>
+          <t>0.0~1.0</t>
         </is>
       </c>
       <c r="K22" s="92" t="inlineStr">
         <is>
-          <t>RAW · CLUSTERED_REP/DUPE · CLASSIFIED · SKIPPED_QUALITY/CREDIBILITY/ERROR</t>
+          <t>v3 exposure_score (결정적 산식)</t>
         </is>
       </c>
     </row>
@@ -3784,12 +3780,12 @@
       <c r="B23" s="91" t="n"/>
       <c r="C23" s="92" t="inlineStr">
         <is>
-          <t>importance_score</t>
+          <t>metadata</t>
         </is>
       </c>
       <c r="D23" s="92" t="inlineStr">
         <is>
-          <t>중요도 점수</t>
+          <t>메타데이터</t>
         </is>
       </c>
       <c r="E23" s="92" t="inlineStr">
@@ -3799,7 +3795,7 @@
       </c>
       <c r="F23" s="92" t="inlineStr">
         <is>
-          <t>FLOAT</t>
+          <t>JSONB</t>
         </is>
       </c>
       <c r="G23" s="92" t="inlineStr"/>
@@ -3807,12 +3803,12 @@
       <c r="I23" s="92" t="inlineStr"/>
       <c r="J23" s="92" t="inlineStr">
         <is>
-          <t>0.0~1.0</t>
+          <t>Default '{}'</t>
         </is>
       </c>
       <c r="K23" s="92" t="inlineStr">
         <is>
-          <t>v3 exposure_score (결정적 산식)</t>
+          <t>url_hash · 크롤러별 부가 필드 · image_source_url 임시 보관</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3817,12 @@
       <c r="B24" s="91" t="n"/>
       <c r="C24" s="92" t="inlineStr">
         <is>
-          <t>metadata</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D24" s="92" t="inlineStr">
         <is>
-          <t>메타데이터</t>
+          <t>생성 시각</t>
         </is>
       </c>
       <c r="E24" s="92" t="inlineStr">
@@ -3836,7 +3832,7 @@
       </c>
       <c r="F24" s="92" t="inlineStr">
         <is>
-          <t>JSONB</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="G24" s="92" t="inlineStr"/>
@@ -3844,71 +3840,75 @@
       <c r="I24" s="92" t="inlineStr"/>
       <c r="J24" s="92" t="inlineStr">
         <is>
-          <t>Default '{}'</t>
+          <t>Default NOW()</t>
         </is>
       </c>
       <c r="K24" s="92" t="inlineStr">
         <is>
-          <t>url_hash · 크롤러별 부가 필드 · image_source_url 임시 보관</t>
+          <t>row 생성 시각</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="91" t="n"/>
-      <c r="B25" s="91" t="n"/>
+      <c r="A25" s="91" t="inlineStr">
+        <is>
+          <t>job_postings</t>
+        </is>
+      </c>
+      <c r="B25" s="91" t="inlineStr">
+        <is>
+          <t>채용공고 스냅샷</t>
+        </is>
+      </c>
       <c r="C25" s="92" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D25" s="92" t="inlineStr">
         <is>
-          <t>생성 시각</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E25" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F25" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>BIGSERIAL</t>
         </is>
       </c>
       <c r="G25" s="92" t="inlineStr"/>
-      <c r="H25" s="92" t="inlineStr"/>
+      <c r="H25" s="92" t="inlineStr">
+        <is>
+          <t>PK1</t>
+        </is>
+      </c>
       <c r="I25" s="92" t="inlineStr"/>
       <c r="J25" s="92" t="inlineStr">
         <is>
-          <t>Default NOW()</t>
+          <t>AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="K25" s="92" t="inlineStr">
         <is>
-          <t>row 생성 시각</t>
+          <t>row PK</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="91" t="inlineStr">
-        <is>
-          <t>job_postings</t>
-        </is>
-      </c>
-      <c r="B26" s="91" t="inlineStr">
-        <is>
-          <t>채용공고 스냅샷</t>
-        </is>
-      </c>
+      <c r="A26" s="91" t="n"/>
+      <c r="B26" s="91" t="n"/>
       <c r="C26" s="92" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>peer_id</t>
         </is>
       </c>
       <c r="D26" s="92" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Peer ID</t>
         </is>
       </c>
       <c r="E26" s="92" t="inlineStr">
@@ -3918,24 +3918,24 @@
       </c>
       <c r="F26" s="92" t="inlineStr">
         <is>
-          <t>BIGSERIAL</t>
-        </is>
-      </c>
-      <c r="G26" s="92" t="inlineStr"/>
-      <c r="H26" s="92" t="inlineStr">
-        <is>
-          <t>PK1</t>
-        </is>
-      </c>
-      <c r="I26" s="92" t="inlineStr"/>
-      <c r="J26" s="92" t="inlineStr">
-        <is>
-          <t>AUTO_INCREMENT</t>
-        </is>
-      </c>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G26" s="92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H26" s="92" t="inlineStr"/>
+      <c r="I26" s="92" t="inlineStr">
+        <is>
+          <t>peer_companies.id</t>
+        </is>
+      </c>
+      <c r="J26" s="92" t="inlineStr"/>
       <c r="K26" s="92" t="inlineStr">
         <is>
-          <t>row PK</t>
+          <t>채용공고가 속한 Peer 회사</t>
         </is>
       </c>
     </row>
@@ -3944,12 +3944,12 @@
       <c r="B27" s="91" t="n"/>
       <c r="C27" s="92" t="inlineStr">
         <is>
-          <t>peer_id</t>
+          <t>job_title</t>
         </is>
       </c>
       <c r="D27" s="92" t="inlineStr">
         <is>
-          <t>Peer ID</t>
+          <t>공고 제목</t>
         </is>
       </c>
       <c r="E27" s="92" t="inlineStr">
@@ -3959,24 +3959,16 @@
       </c>
       <c r="F27" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G27" s="92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="G27" s="92" t="inlineStr"/>
       <c r="H27" s="92" t="inlineStr"/>
-      <c r="I27" s="92" t="inlineStr">
-        <is>
-          <t>peer_companies.id</t>
-        </is>
-      </c>
+      <c r="I27" s="92" t="inlineStr"/>
       <c r="J27" s="92" t="inlineStr"/>
       <c r="K27" s="92" t="inlineStr">
         <is>
-          <t>채용공고가 속한 Peer 회사</t>
+          <t>채용공고 제목</t>
         </is>
       </c>
     </row>
@@ -3985,31 +3977,35 @@
       <c r="B28" s="91" t="n"/>
       <c r="C28" s="92" t="inlineStr">
         <is>
-          <t>job_title</t>
+          <t>department</t>
         </is>
       </c>
       <c r="D28" s="92" t="inlineStr">
         <is>
-          <t>공고 제목</t>
+          <t>부서</t>
         </is>
       </c>
       <c r="E28" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F28" s="92" t="inlineStr">
         <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="G28" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G28" s="92" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="H28" s="92" t="inlineStr"/>
       <c r="I28" s="92" t="inlineStr"/>
       <c r="J28" s="92" t="inlineStr"/>
       <c r="K28" s="92" t="inlineStr">
         <is>
-          <t>채용공고 제목</t>
+          <t>공고된 부서 (옵션)</t>
         </is>
       </c>
     </row>
@@ -4018,12 +4014,12 @@
       <c r="B29" s="91" t="n"/>
       <c r="C29" s="92" t="inlineStr">
         <is>
-          <t>department</t>
+          <t>tech_stack</t>
         </is>
       </c>
       <c r="D29" s="92" t="inlineStr">
         <is>
-          <t>부서</t>
+          <t>기술 스택</t>
         </is>
       </c>
       <c r="E29" s="92" t="inlineStr">
@@ -4033,20 +4029,20 @@
       </c>
       <c r="F29" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G29" s="92" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>TEXT[]</t>
+        </is>
+      </c>
+      <c r="G29" s="92" t="inlineStr"/>
       <c r="H29" s="92" t="inlineStr"/>
       <c r="I29" s="92" t="inlineStr"/>
-      <c r="J29" s="92" t="inlineStr"/>
+      <c r="J29" s="92" t="inlineStr">
+        <is>
+          <t>Default '{}'</t>
+        </is>
+      </c>
       <c r="K29" s="92" t="inlineStr">
         <is>
-          <t>공고된 부서 (옵션)</t>
+          <t>추출한 기술 키워드 배열</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4051,22 @@
       <c r="B30" s="91" t="n"/>
       <c r="C30" s="92" t="inlineStr">
         <is>
-          <t>tech_stack</t>
+          <t>snapshot_week</t>
         </is>
       </c>
       <c r="D30" s="92" t="inlineStr">
         <is>
-          <t>기술 스택</t>
+          <t>스냅샷 주</t>
         </is>
       </c>
       <c r="E30" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F30" s="92" t="inlineStr">
         <is>
-          <t>TEXT[]</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="G30" s="92" t="inlineStr"/>
@@ -4078,12 +4074,12 @@
       <c r="I30" s="92" t="inlineStr"/>
       <c r="J30" s="92" t="inlineStr">
         <is>
-          <t>Default '{}'</t>
+          <t>월요일 기준</t>
         </is>
       </c>
       <c r="K30" s="92" t="inlineStr">
         <is>
-          <t>추출한 기술 키워드 배열</t>
+          <t>주간 스냅샷 기준일 (월요일)</t>
         </is>
       </c>
     </row>
@@ -4092,22 +4088,22 @@
       <c r="B31" s="91" t="n"/>
       <c r="C31" s="92" t="inlineStr">
         <is>
-          <t>snapshot_week</t>
+          <t>is_new</t>
         </is>
       </c>
       <c r="D31" s="92" t="inlineStr">
         <is>
-          <t>스냅샷 주</t>
+          <t>신규 여부</t>
         </is>
       </c>
       <c r="E31" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F31" s="92" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="G31" s="92" t="inlineStr"/>
@@ -4115,12 +4111,12 @@
       <c r="I31" s="92" t="inlineStr"/>
       <c r="J31" s="92" t="inlineStr">
         <is>
-          <t>월요일 기준</t>
+          <t>Default TRUE</t>
         </is>
       </c>
       <c r="K31" s="92" t="inlineStr">
         <is>
-          <t>주간 스냅샷 기준일 (월요일)</t>
+          <t>이전 주 대비 신규 등장 여부</t>
         </is>
       </c>
     </row>
@@ -4129,12 +4125,12 @@
       <c r="B32" s="91" t="n"/>
       <c r="C32" s="92" t="inlineStr">
         <is>
-          <t>is_new</t>
+          <t>url</t>
         </is>
       </c>
       <c r="D32" s="92" t="inlineStr">
         <is>
-          <t>신규 여부</t>
+          <t>공고 URL</t>
         </is>
       </c>
       <c r="E32" s="92" t="inlineStr">
@@ -4144,20 +4140,16 @@
       </c>
       <c r="F32" s="92" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="G32" s="92" t="inlineStr"/>
       <c r="H32" s="92" t="inlineStr"/>
       <c r="I32" s="92" t="inlineStr"/>
-      <c r="J32" s="92" t="inlineStr">
-        <is>
-          <t>Default TRUE</t>
-        </is>
-      </c>
+      <c r="J32" s="92" t="inlineStr"/>
       <c r="K32" s="92" t="inlineStr">
         <is>
-          <t>이전 주 대비 신규 등장 여부</t>
+          <t>원본 URL</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4158,12 @@
       <c r="B33" s="91" t="n"/>
       <c r="C33" s="92" t="inlineStr">
         <is>
-          <t>url</t>
+          <t>collected_at</t>
         </is>
       </c>
       <c r="D33" s="92" t="inlineStr">
         <is>
-          <t>공고 URL</t>
+          <t>수집 시각</t>
         </is>
       </c>
       <c r="E33" s="92" t="inlineStr">
@@ -4181,75 +4173,83 @@
       </c>
       <c r="F33" s="92" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="G33" s="92" t="inlineStr"/>
       <c r="H33" s="92" t="inlineStr"/>
       <c r="I33" s="92" t="inlineStr"/>
-      <c r="J33" s="92" t="inlineStr"/>
+      <c r="J33" s="92" t="inlineStr">
+        <is>
+          <t>Default NOW()</t>
+        </is>
+      </c>
       <c r="K33" s="92" t="inlineStr">
         <is>
-          <t>원본 URL</t>
+          <t>수집 시각</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="91" t="n"/>
-      <c r="B34" s="91" t="n"/>
+      <c r="A34" s="91" t="inlineStr">
+        <is>
+          <t>peer_financials</t>
+        </is>
+      </c>
+      <c r="B34" s="91" t="inlineStr">
+        <is>
+          <t>Peer 분기·연간 재무</t>
+        </is>
+      </c>
       <c r="C34" s="92" t="inlineStr">
         <is>
-          <t>collected_at</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D34" s="92" t="inlineStr">
         <is>
-          <t>수집 시각</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E34" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F34" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>BIGSERIAL</t>
         </is>
       </c>
       <c r="G34" s="92" t="inlineStr"/>
-      <c r="H34" s="92" t="inlineStr"/>
+      <c r="H34" s="92" t="inlineStr">
+        <is>
+          <t>PK1</t>
+        </is>
+      </c>
       <c r="I34" s="92" t="inlineStr"/>
       <c r="J34" s="92" t="inlineStr">
         <is>
-          <t>Default NOW()</t>
+          <t>AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="K34" s="92" t="inlineStr">
         <is>
-          <t>수집 시각</t>
+          <t>row PK</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="91" t="inlineStr">
-        <is>
-          <t>peer_financials</t>
-        </is>
-      </c>
-      <c r="B35" s="91" t="inlineStr">
-        <is>
-          <t>Peer 분기·연간 재무</t>
-        </is>
-      </c>
+      <c r="A35" s="91" t="n"/>
+      <c r="B35" s="91" t="n"/>
       <c r="C35" s="92" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>peer_id</t>
         </is>
       </c>
       <c r="D35" s="92" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Peer ID</t>
         </is>
       </c>
       <c r="E35" s="92" t="inlineStr">
@@ -4259,24 +4259,28 @@
       </c>
       <c r="F35" s="92" t="inlineStr">
         <is>
-          <t>BIGSERIAL</t>
-        </is>
-      </c>
-      <c r="G35" s="92" t="inlineStr"/>
-      <c r="H35" s="92" t="inlineStr">
-        <is>
-          <t>PK1</t>
-        </is>
-      </c>
-      <c r="I35" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G35" s="92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H35" s="92" t="inlineStr"/>
+      <c r="I35" s="92" t="inlineStr">
+        <is>
+          <t>peer_companies.id</t>
+        </is>
+      </c>
       <c r="J35" s="92" t="inlineStr">
         <is>
-          <t>AUTO_INCREMENT</t>
+          <t>UNIQUE(peer_id, period)</t>
         </is>
       </c>
       <c r="K35" s="92" t="inlineStr">
         <is>
-          <t>row PK</t>
+          <t>재무 데이터 소속 Peer 회사</t>
         </is>
       </c>
     </row>
@@ -4285,12 +4289,12 @@
       <c r="B36" s="91" t="n"/>
       <c r="C36" s="92" t="inlineStr">
         <is>
-          <t>peer_id</t>
+          <t>period</t>
         </is>
       </c>
       <c r="D36" s="92" t="inlineStr">
         <is>
-          <t>Peer ID</t>
+          <t>보고 기간</t>
         </is>
       </c>
       <c r="E36" s="92" t="inlineStr">
@@ -4305,23 +4309,19 @@
       </c>
       <c r="G36" s="92" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H36" s="92" t="inlineStr"/>
-      <c r="I36" s="92" t="inlineStr">
-        <is>
-          <t>peer_companies.id</t>
-        </is>
-      </c>
+      <c r="I36" s="92" t="inlineStr"/>
       <c r="J36" s="92" t="inlineStr">
         <is>
-          <t>UNIQUE(peer_id, period)</t>
+          <t>예: '2026Q1'</t>
         </is>
       </c>
       <c r="K36" s="92" t="inlineStr">
         <is>
-          <t>재무 데이터 소속 Peer 회사</t>
+          <t>분기·연간 식별 (YYYYQn 또는 YYYY)</t>
         </is>
       </c>
     </row>
@@ -4330,39 +4330,31 @@
       <c r="B37" s="91" t="n"/>
       <c r="C37" s="92" t="inlineStr">
         <is>
-          <t>period</t>
+          <t>report_date</t>
         </is>
       </c>
       <c r="D37" s="92" t="inlineStr">
         <is>
-          <t>보고 기간</t>
+          <t>공시일</t>
         </is>
       </c>
       <c r="E37" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F37" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G37" s="92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="G37" s="92" t="inlineStr"/>
       <c r="H37" s="92" t="inlineStr"/>
       <c r="I37" s="92" t="inlineStr"/>
-      <c r="J37" s="92" t="inlineStr">
-        <is>
-          <t>예: '2026Q1'</t>
-        </is>
-      </c>
+      <c r="J37" s="92" t="inlineStr"/>
       <c r="K37" s="92" t="inlineStr">
         <is>
-          <t>분기·연간 식별 (YYYYQn 또는 YYYY)</t>
+          <t>DART 공시·발표일</t>
         </is>
       </c>
     </row>
@@ -4371,12 +4363,12 @@
       <c r="B38" s="91" t="n"/>
       <c r="C38" s="92" t="inlineStr">
         <is>
-          <t>report_date</t>
+          <t>dart_rcept_no</t>
         </is>
       </c>
       <c r="D38" s="92" t="inlineStr">
         <is>
-          <t>공시일</t>
+          <t>DART 공시번호</t>
         </is>
       </c>
       <c r="E38" s="92" t="inlineStr">
@@ -4386,16 +4378,20 @@
       </c>
       <c r="F38" s="92" t="inlineStr">
         <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="G38" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G38" s="92" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="H38" s="92" t="inlineStr"/>
       <c r="I38" s="92" t="inlineStr"/>
       <c r="J38" s="92" t="inlineStr"/>
       <c r="K38" s="92" t="inlineStr">
         <is>
-          <t>DART 공시·발표일</t>
+          <t>DART 접수번호 (검증 추적)</t>
         </is>
       </c>
     </row>
@@ -4404,12 +4400,12 @@
       <c r="B39" s="91" t="n"/>
       <c r="C39" s="92" t="inlineStr">
         <is>
-          <t>dart_rcept_no</t>
+          <t>ir_page</t>
         </is>
       </c>
       <c r="D39" s="92" t="inlineStr">
         <is>
-          <t>DART 공시번호</t>
+          <t>IR 페이지</t>
         </is>
       </c>
       <c r="E39" s="92" t="inlineStr">
@@ -4419,20 +4415,16 @@
       </c>
       <c r="F39" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G39" s="92" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="G39" s="92" t="inlineStr"/>
       <c r="H39" s="92" t="inlineStr"/>
       <c r="I39" s="92" t="inlineStr"/>
       <c r="J39" s="92" t="inlineStr"/>
       <c r="K39" s="92" t="inlineStr">
         <is>
-          <t>DART 접수번호 (검증 추적)</t>
+          <t>IR PDF 의 페이지 번호</t>
         </is>
       </c>
     </row>
@@ -4441,12 +4433,12 @@
       <c r="B40" s="91" t="n"/>
       <c r="C40" s="92" t="inlineStr">
         <is>
-          <t>ir_page</t>
+          <t>revenue_total_krwbn</t>
         </is>
       </c>
       <c r="D40" s="92" t="inlineStr">
         <is>
-          <t>IR 페이지</t>
+          <t>총 매출 (억원)</t>
         </is>
       </c>
       <c r="E40" s="92" t="inlineStr">
@@ -4456,16 +4448,20 @@
       </c>
       <c r="F40" s="92" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>FLOAT</t>
         </is>
       </c>
       <c r="G40" s="92" t="inlineStr"/>
       <c r="H40" s="92" t="inlineStr"/>
       <c r="I40" s="92" t="inlineStr"/>
-      <c r="J40" s="92" t="inlineStr"/>
+      <c r="J40" s="92" t="inlineStr">
+        <is>
+          <t>단위: 억원</t>
+        </is>
+      </c>
       <c r="K40" s="92" t="inlineStr">
         <is>
-          <t>IR PDF 의 페이지 번호</t>
+          <t>분기·연간 전체 매출</t>
         </is>
       </c>
     </row>
@@ -4474,12 +4470,12 @@
       <c r="B41" s="91" t="n"/>
       <c r="C41" s="92" t="inlineStr">
         <is>
-          <t>revenue_total_krwbn</t>
+          <t>operating_profit_krwbn</t>
         </is>
       </c>
       <c r="D41" s="92" t="inlineStr">
         <is>
-          <t>총 매출 (억원)</t>
+          <t>영업이익 (억원)</t>
         </is>
       </c>
       <c r="E41" s="92" t="inlineStr">
@@ -4502,7 +4498,7 @@
       </c>
       <c r="K41" s="92" t="inlineStr">
         <is>
-          <t>분기·연간 전체 매출</t>
+          <t>영업이익</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4507,12 @@
       <c r="B42" s="91" t="n"/>
       <c r="C42" s="92" t="inlineStr">
         <is>
-          <t>operating_profit_krwbn</t>
+          <t>segment_revenue</t>
         </is>
       </c>
       <c r="D42" s="92" t="inlineStr">
         <is>
-          <t>영업이익 (억원)</t>
+          <t>사업부 매출</t>
         </is>
       </c>
       <c r="E42" s="92" t="inlineStr">
@@ -4526,7 +4522,7 @@
       </c>
       <c r="F42" s="92" t="inlineStr">
         <is>
-          <t>FLOAT</t>
+          <t>JSONB</t>
         </is>
       </c>
       <c r="G42" s="92" t="inlineStr"/>
@@ -4534,12 +4530,12 @@
       <c r="I42" s="92" t="inlineStr"/>
       <c r="J42" s="92" t="inlineStr">
         <is>
-          <t>단위: 억원</t>
+          <t>Default '{}'</t>
         </is>
       </c>
       <c r="K42" s="92" t="inlineStr">
         <is>
-          <t>영업이익</t>
+          <t>{segment_id: 매출_억원}</t>
         </is>
       </c>
     </row>
@@ -4548,12 +4544,12 @@
       <c r="B43" s="91" t="n"/>
       <c r="C43" s="92" t="inlineStr">
         <is>
-          <t>segment_revenue</t>
+          <t>ai_revenue_share_pct</t>
         </is>
       </c>
       <c r="D43" s="92" t="inlineStr">
         <is>
-          <t>사업부 매출</t>
+          <t>AI 매출 비중 (%)</t>
         </is>
       </c>
       <c r="E43" s="92" t="inlineStr">
@@ -4563,7 +4559,7 @@
       </c>
       <c r="F43" s="92" t="inlineStr">
         <is>
-          <t>JSONB</t>
+          <t>FLOAT</t>
         </is>
       </c>
       <c r="G43" s="92" t="inlineStr"/>
@@ -4571,12 +4567,12 @@
       <c r="I43" s="92" t="inlineStr"/>
       <c r="J43" s="92" t="inlineStr">
         <is>
-          <t>Default '{}'</t>
+          <t>0~100</t>
         </is>
       </c>
       <c r="K43" s="92" t="inlineStr">
         <is>
-          <t>{segment_id: 매출_억원}</t>
+          <t>AI 사업 매출 비중</t>
         </is>
       </c>
     </row>
@@ -4585,12 +4581,12 @@
       <c r="B44" s="91" t="n"/>
       <c r="C44" s="92" t="inlineStr">
         <is>
-          <t>ai_revenue_share_pct</t>
+          <t>headcount</t>
         </is>
       </c>
       <c r="D44" s="92" t="inlineStr">
         <is>
-          <t>AI 매출 비중 (%)</t>
+          <t>인력 현황</t>
         </is>
       </c>
       <c r="E44" s="92" t="inlineStr">
@@ -4600,7 +4596,7 @@
       </c>
       <c r="F44" s="92" t="inlineStr">
         <is>
-          <t>FLOAT</t>
+          <t>JSONB</t>
         </is>
       </c>
       <c r="G44" s="92" t="inlineStr"/>
@@ -4608,12 +4604,12 @@
       <c r="I44" s="92" t="inlineStr"/>
       <c r="J44" s="92" t="inlineStr">
         <is>
-          <t>0~100</t>
+          <t>Default '{}'</t>
         </is>
       </c>
       <c r="K44" s="92" t="inlineStr">
         <is>
-          <t>AI 사업 매출 비중</t>
+          <t>{total, rd, ai_engineers_est}</t>
         </is>
       </c>
     </row>
@@ -4622,12 +4618,12 @@
       <c r="B45" s="91" t="n"/>
       <c r="C45" s="92" t="inlineStr">
         <is>
-          <t>headcount</t>
+          <t>raw_payload</t>
         </is>
       </c>
       <c r="D45" s="92" t="inlineStr">
         <is>
-          <t>인력 현황</t>
+          <t>원본 페이로드</t>
         </is>
       </c>
       <c r="E45" s="92" t="inlineStr">
@@ -4643,14 +4639,10 @@
       <c r="G45" s="92" t="inlineStr"/>
       <c r="H45" s="92" t="inlineStr"/>
       <c r="I45" s="92" t="inlineStr"/>
-      <c r="J45" s="92" t="inlineStr">
-        <is>
-          <t>Default '{}'</t>
-        </is>
-      </c>
+      <c r="J45" s="92" t="inlineStr"/>
       <c r="K45" s="92" t="inlineStr">
         <is>
-          <t>{total, rd, ai_engineers_est}</t>
+          <t>IRParserAgent 후처리 결과</t>
         </is>
       </c>
     </row>
@@ -4659,12 +4651,12 @@
       <c r="B46" s="91" t="n"/>
       <c r="C46" s="92" t="inlineStr">
         <is>
-          <t>raw_payload</t>
+          <t>source</t>
         </is>
       </c>
       <c r="D46" s="92" t="inlineStr">
         <is>
-          <t>원본 페이로드</t>
+          <t>데이터 출처</t>
         </is>
       </c>
       <c r="E46" s="92" t="inlineStr">
@@ -4674,16 +4666,24 @@
       </c>
       <c r="F46" s="92" t="inlineStr">
         <is>
-          <t>JSONB</t>
-        </is>
-      </c>
-      <c r="G46" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G46" s="92" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="H46" s="92" t="inlineStr"/>
       <c r="I46" s="92" t="inlineStr"/>
-      <c r="J46" s="92" t="inlineStr"/>
+      <c r="J46" s="92" t="inlineStr">
+        <is>
+          <t>Default 'stub_v0'</t>
+        </is>
+      </c>
       <c r="K46" s="92" t="inlineStr">
         <is>
-          <t>IRParserAgent 후처리 결과</t>
+          <t>stub_v0 | dart | ir_pdf | manual</t>
         </is>
       </c>
     </row>
@@ -4692,12 +4692,12 @@
       <c r="B47" s="91" t="n"/>
       <c r="C47" s="92" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D47" s="92" t="inlineStr">
         <is>
-          <t>데이터 출처</t>
+          <t>생성 시각</t>
         </is>
       </c>
       <c r="E47" s="92" t="inlineStr">
@@ -4707,83 +4707,83 @@
       </c>
       <c r="F47" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G47" s="92" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="G47" s="92" t="inlineStr"/>
       <c r="H47" s="92" t="inlineStr"/>
       <c r="I47" s="92" t="inlineStr"/>
       <c r="J47" s="92" t="inlineStr">
         <is>
-          <t>Default 'stub_v0'</t>
+          <t>Default NOW()</t>
         </is>
       </c>
       <c r="K47" s="92" t="inlineStr">
         <is>
-          <t>stub_v0 | dart | ir_pdf | manual</t>
+          <t>row 생성 시각</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="91" t="n"/>
-      <c r="B48" s="91" t="n"/>
+      <c r="A48" s="91" t="inlineStr">
+        <is>
+          <t>mbb_baseline</t>
+        </is>
+      </c>
+      <c r="B48" s="91" t="inlineStr">
+        <is>
+          <t>컨설팅 보고서 baseline</t>
+        </is>
+      </c>
       <c r="C48" s="92" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D48" s="92" t="inlineStr">
         <is>
-          <t>생성 시각</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E48" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F48" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>BIGSERIAL</t>
         </is>
       </c>
       <c r="G48" s="92" t="inlineStr"/>
-      <c r="H48" s="92" t="inlineStr"/>
+      <c r="H48" s="92" t="inlineStr">
+        <is>
+          <t>PK1</t>
+        </is>
+      </c>
       <c r="I48" s="92" t="inlineStr"/>
       <c r="J48" s="92" t="inlineStr">
         <is>
-          <t>Default NOW()</t>
+          <t>AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="K48" s="92" t="inlineStr">
         <is>
-          <t>row 생성 시각</t>
+          <t>row PK</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="91" t="inlineStr">
-        <is>
-          <t>mbb_baseline</t>
-        </is>
-      </c>
-      <c r="B49" s="91" t="inlineStr">
-        <is>
-          <t>컨설팅 보고서 baseline</t>
-        </is>
-      </c>
+      <c r="A49" s="91" t="n"/>
+      <c r="B49" s="91" t="n"/>
       <c r="C49" s="92" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>source</t>
         </is>
       </c>
       <c r="D49" s="92" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>발행처</t>
         </is>
       </c>
       <c r="E49" s="92" t="inlineStr">
@@ -4793,24 +4793,24 @@
       </c>
       <c r="F49" s="92" t="inlineStr">
         <is>
-          <t>BIGSERIAL</t>
-        </is>
-      </c>
-      <c r="G49" s="92" t="inlineStr"/>
-      <c r="H49" s="92" t="inlineStr">
-        <is>
-          <t>PK1</t>
-        </is>
-      </c>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G49" s="92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H49" s="92" t="inlineStr"/>
       <c r="I49" s="92" t="inlineStr"/>
       <c r="J49" s="92" t="inlineStr">
         <is>
-          <t>AUTO_INCREMENT</t>
+          <t>McKinsey|BCG|Bain|Kearney|...</t>
         </is>
       </c>
       <c r="K49" s="92" t="inlineStr">
         <is>
-          <t>row PK</t>
+          <t>컨설팅사 이름</t>
         </is>
       </c>
     </row>
@@ -4819,17 +4819,17 @@
       <c r="B50" s="91" t="n"/>
       <c r="C50" s="92" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>report_id</t>
         </is>
       </c>
       <c r="D50" s="92" t="inlineStr">
         <is>
-          <t>발행처</t>
+          <t>보고서 ID</t>
         </is>
       </c>
       <c r="E50" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F50" s="92" t="inlineStr">
@@ -4839,19 +4839,15 @@
       </c>
       <c r="G50" s="92" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H50" s="92" t="inlineStr"/>
       <c r="I50" s="92" t="inlineStr"/>
-      <c r="J50" s="92" t="inlineStr">
-        <is>
-          <t>McKinsey|BCG|Bain|Kearney|...</t>
-        </is>
-      </c>
+      <c r="J50" s="92" t="inlineStr"/>
       <c r="K50" s="92" t="inlineStr">
         <is>
-          <t>컨설팅사 이름</t>
+          <t>발행처 내부 식별자</t>
         </is>
       </c>
     </row>
@@ -4860,35 +4856,31 @@
       <c r="B51" s="91" t="n"/>
       <c r="C51" s="92" t="inlineStr">
         <is>
-          <t>report_id</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D51" s="92" t="inlineStr">
         <is>
-          <t>보고서 ID</t>
+          <t>제목</t>
         </is>
       </c>
       <c r="E51" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F51" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G51" s="92" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="G51" s="92" t="inlineStr"/>
       <c r="H51" s="92" t="inlineStr"/>
       <c r="I51" s="92" t="inlineStr"/>
       <c r="J51" s="92" t="inlineStr"/>
       <c r="K51" s="92" t="inlineStr">
         <is>
-          <t>발행처 내부 식별자</t>
+          <t>보고서 제목</t>
         </is>
       </c>
     </row>
@@ -4897,22 +4889,22 @@
       <c r="B52" s="91" t="n"/>
       <c r="C52" s="92" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>published_date</t>
         </is>
       </c>
       <c r="D52" s="92" t="inlineStr">
         <is>
-          <t>제목</t>
+          <t>발행일</t>
         </is>
       </c>
       <c r="E52" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F52" s="92" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="G52" s="92" t="inlineStr"/>
@@ -4921,7 +4913,7 @@
       <c r="J52" s="92" t="inlineStr"/>
       <c r="K52" s="92" t="inlineStr">
         <is>
-          <t>보고서 제목</t>
+          <t>원문 발행일</t>
         </is>
       </c>
     </row>
@@ -4930,12 +4922,12 @@
       <c r="B53" s="91" t="n"/>
       <c r="C53" s="92" t="inlineStr">
         <is>
-          <t>published_date</t>
+          <t>url</t>
         </is>
       </c>
       <c r="D53" s="92" t="inlineStr">
         <is>
-          <t>발행일</t>
+          <t>원문 URL</t>
         </is>
       </c>
       <c r="E53" s="92" t="inlineStr">
@@ -4945,7 +4937,7 @@
       </c>
       <c r="F53" s="92" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="G53" s="92" t="inlineStr"/>
@@ -4954,7 +4946,7 @@
       <c r="J53" s="92" t="inlineStr"/>
       <c r="K53" s="92" t="inlineStr">
         <is>
-          <t>원문 발행일</t>
+          <t>원문 URL (PDF · 웹 페이지)</t>
         </is>
       </c>
     </row>
@@ -4963,12 +4955,12 @@
       <c r="B54" s="91" t="n"/>
       <c r="C54" s="92" t="inlineStr">
         <is>
-          <t>url</t>
+          <t>summary</t>
         </is>
       </c>
       <c r="D54" s="92" t="inlineStr">
         <is>
-          <t>원문 URL</t>
+          <t>요약</t>
         </is>
       </c>
       <c r="E54" s="92" t="inlineStr">
@@ -4987,7 +4979,7 @@
       <c r="J54" s="92" t="inlineStr"/>
       <c r="K54" s="92" t="inlineStr">
         <is>
-          <t>원문 URL (PDF · 웹 페이지)</t>
+          <t>보고서 핵심 요약 (운영자 입력 또는 AI 생성)</t>
         </is>
       </c>
     </row>
@@ -4996,12 +4988,12 @@
       <c r="B55" s="91" t="n"/>
       <c r="C55" s="92" t="inlineStr">
         <is>
-          <t>summary</t>
+          <t>sectors</t>
         </is>
       </c>
       <c r="D55" s="92" t="inlineStr">
         <is>
-          <t>요약</t>
+          <t>섹터 배열</t>
         </is>
       </c>
       <c r="E55" s="92" t="inlineStr">
@@ -5011,16 +5003,20 @@
       </c>
       <c r="F55" s="92" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>TEXT[]</t>
         </is>
       </c>
       <c r="G55" s="92" t="inlineStr"/>
       <c r="H55" s="92" t="inlineStr"/>
       <c r="I55" s="92" t="inlineStr"/>
-      <c r="J55" s="92" t="inlineStr"/>
+      <c r="J55" s="92" t="inlineStr">
+        <is>
+          <t>Default '{}'</t>
+        </is>
+      </c>
       <c r="K55" s="92" t="inlineStr">
         <is>
-          <t>보고서 핵심 요약 (운영자 입력 또는 AI 생성)</t>
+          <t>['ai_tech', 'security'] 등</t>
         </is>
       </c>
     </row>
@@ -5029,12 +5025,12 @@
       <c r="B56" s="91" t="n"/>
       <c r="C56" s="92" t="inlineStr">
         <is>
-          <t>sectors</t>
+          <t>keywords</t>
         </is>
       </c>
       <c r="D56" s="92" t="inlineStr">
         <is>
-          <t>섹터 배열</t>
+          <t>키워드 배열</t>
         </is>
       </c>
       <c r="E56" s="92" t="inlineStr">
@@ -5057,7 +5053,7 @@
       </c>
       <c r="K56" s="92" t="inlineStr">
         <is>
-          <t>['ai_tech', 'security'] 등</t>
+          <t>EvidenceAgent 매칭용 키워드</t>
         </is>
       </c>
     </row>
@@ -5066,12 +5062,12 @@
       <c r="B57" s="91" t="n"/>
       <c r="C57" s="92" t="inlineStr">
         <is>
-          <t>keywords</t>
+          <t>raw_payload</t>
         </is>
       </c>
       <c r="D57" s="92" t="inlineStr">
         <is>
-          <t>키워드 배열</t>
+          <t>원본 페이로드</t>
         </is>
       </c>
       <c r="E57" s="92" t="inlineStr">
@@ -5081,7 +5077,7 @@
       </c>
       <c r="F57" s="92" t="inlineStr">
         <is>
-          <t>TEXT[]</t>
+          <t>JSONB</t>
         </is>
       </c>
       <c r="G57" s="92" t="inlineStr"/>
@@ -5094,7 +5090,7 @@
       </c>
       <c r="K57" s="92" t="inlineStr">
         <is>
-          <t>EvidenceAgent 매칭용 키워드</t>
+          <t>추가 메타 (저자 · 페이지 수 등)</t>
         </is>
       </c>
     </row>
@@ -5103,12 +5099,12 @@
       <c r="B58" s="91" t="n"/>
       <c r="C58" s="92" t="inlineStr">
         <is>
-          <t>raw_payload</t>
+          <t>is_active</t>
         </is>
       </c>
       <c r="D58" s="92" t="inlineStr">
         <is>
-          <t>원본 페이로드</t>
+          <t>활성 여부</t>
         </is>
       </c>
       <c r="E58" s="92" t="inlineStr">
@@ -5118,7 +5114,7 @@
       </c>
       <c r="F58" s="92" t="inlineStr">
         <is>
-          <t>JSONB</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="G58" s="92" t="inlineStr"/>
@@ -5126,12 +5122,12 @@
       <c r="I58" s="92" t="inlineStr"/>
       <c r="J58" s="92" t="inlineStr">
         <is>
-          <t>Default '{}'</t>
+          <t>Default TRUE</t>
         </is>
       </c>
       <c r="K58" s="92" t="inlineStr">
         <is>
-          <t>추가 메타 (저자 · 페이지 수 등)</t>
+          <t>현재 매칭 대상 여부</t>
         </is>
       </c>
     </row>
@@ -5140,12 +5136,12 @@
       <c r="B59" s="91" t="n"/>
       <c r="C59" s="92" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D59" s="92" t="inlineStr">
         <is>
-          <t>활성 여부</t>
+          <t>생성 시각</t>
         </is>
       </c>
       <c r="E59" s="92" t="inlineStr">
@@ -5155,7 +5151,7 @@
       </c>
       <c r="F59" s="92" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="G59" s="92" t="inlineStr"/>
@@ -5163,71 +5159,79 @@
       <c r="I59" s="92" t="inlineStr"/>
       <c r="J59" s="92" t="inlineStr">
         <is>
-          <t>Default TRUE</t>
+          <t>Default NOW()</t>
         </is>
       </c>
       <c r="K59" s="92" t="inlineStr">
         <is>
-          <t>현재 매칭 대상 여부</t>
+          <t>row 생성 시각</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="91" t="n"/>
-      <c r="B60" s="91" t="n"/>
+      <c r="A60" s="91" t="inlineStr">
+        <is>
+          <t>issue_cards</t>
+        </is>
+      </c>
+      <c r="B60" s="91" t="inlineStr">
+        <is>
+          <t>동향 카드</t>
+        </is>
+      </c>
       <c r="C60" s="92" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D60" s="92" t="inlineStr">
         <is>
-          <t>생성 시각</t>
+          <t>카드 ID</t>
         </is>
       </c>
       <c r="E60" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F60" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
-        </is>
-      </c>
-      <c r="G60" s="92" t="inlineStr"/>
-      <c r="H60" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G60" s="92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H60" s="92" t="inlineStr">
+        <is>
+          <t>PK1</t>
+        </is>
+      </c>
       <c r="I60" s="92" t="inlineStr"/>
       <c r="J60" s="92" t="inlineStr">
         <is>
-          <t>Default NOW()</t>
+          <t>IC-YYYYMMDD-NNN</t>
         </is>
       </c>
       <c r="K60" s="92" t="inlineStr">
         <is>
-          <t>row 생성 시각</t>
+          <t>카드 식별자 (날짜+순번)</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="91" t="inlineStr">
-        <is>
-          <t>issue_cards</t>
-        </is>
-      </c>
-      <c r="B61" s="91" t="inlineStr">
-        <is>
-          <t>동향 카드</t>
-        </is>
-      </c>
+      <c r="A61" s="91" t="n"/>
+      <c r="B61" s="91" t="n"/>
       <c r="C61" s="92" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>peer_id</t>
         </is>
       </c>
       <c r="D61" s="92" t="inlineStr">
         <is>
-          <t>카드 ID</t>
+          <t>Peer ID</t>
         </is>
       </c>
       <c r="E61" s="92" t="inlineStr">
@@ -5245,20 +5249,16 @@
           <t>50</t>
         </is>
       </c>
-      <c r="H61" s="92" t="inlineStr">
-        <is>
-          <t>PK1</t>
-        </is>
-      </c>
-      <c r="I61" s="92" t="inlineStr"/>
-      <c r="J61" s="92" t="inlineStr">
-        <is>
-          <t>IC-YYYYMMDD-NNN</t>
-        </is>
-      </c>
+      <c r="H61" s="92" t="inlineStr"/>
+      <c r="I61" s="92" t="inlineStr">
+        <is>
+          <t>peer_companies.id</t>
+        </is>
+      </c>
+      <c r="J61" s="92" t="inlineStr"/>
       <c r="K61" s="92" t="inlineStr">
         <is>
-          <t>카드 식별자 (날짜+순번)</t>
+          <t>카드가 속한 Peer 회사</t>
         </is>
       </c>
     </row>
@@ -5267,39 +5267,31 @@
       <c r="B62" s="91" t="n"/>
       <c r="C62" s="92" t="inlineStr">
         <is>
-          <t>peer_id</t>
+          <t>cluster_id</t>
         </is>
       </c>
       <c r="D62" s="92" t="inlineStr">
         <is>
-          <t>Peer ID</t>
+          <t>클러스터 ID</t>
         </is>
       </c>
       <c r="E62" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F62" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G62" s="92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="G62" s="92" t="inlineStr"/>
       <c r="H62" s="92" t="inlineStr"/>
-      <c r="I62" s="92" t="inlineStr">
-        <is>
-          <t>peer_companies.id</t>
-        </is>
-      </c>
+      <c r="I62" s="92" t="inlineStr"/>
       <c r="J62" s="92" t="inlineStr"/>
       <c r="K62" s="92" t="inlineStr">
         <is>
-          <t>카드가 속한 Peer 회사</t>
+          <t>raw_articles 의 cluster_id 와 매칭</t>
         </is>
       </c>
     </row>
@@ -5308,31 +5300,35 @@
       <c r="B63" s="91" t="n"/>
       <c r="C63" s="92" t="inlineStr">
         <is>
-          <t>cluster_id</t>
+          <t>title</t>
         </is>
       </c>
       <c r="D63" s="92" t="inlineStr">
         <is>
-          <t>클러스터 ID</t>
+          <t>카드 제목</t>
         </is>
       </c>
       <c r="E63" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F63" s="92" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="G63" s="92" t="inlineStr"/>
       <c r="H63" s="92" t="inlineStr"/>
       <c r="I63" s="92" t="inlineStr"/>
-      <c r="J63" s="92" t="inlineStr"/>
+      <c r="J63" s="92" t="inlineStr">
+        <is>
+          <t>≤500자</t>
+        </is>
+      </c>
       <c r="K63" s="92" t="inlineStr">
         <is>
-          <t>raw_articles 의 cluster_id 와 매칭</t>
+          <t>AI 가 생성한 카드 제목</t>
         </is>
       </c>
     </row>
@@ -5341,22 +5337,22 @@
       <c r="B64" s="91" t="n"/>
       <c r="C64" s="92" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>summary_lines</t>
         </is>
       </c>
       <c r="D64" s="92" t="inlineStr">
         <is>
-          <t>카드 제목</t>
+          <t>3줄 요약</t>
         </is>
       </c>
       <c r="E64" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F64" s="92" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>TEXT[]</t>
         </is>
       </c>
       <c r="G64" s="92" t="inlineStr"/>
@@ -5364,12 +5360,12 @@
       <c r="I64" s="92" t="inlineStr"/>
       <c r="J64" s="92" t="inlineStr">
         <is>
-          <t>≤500자</t>
+          <t>Default '{}', 정확히 3줄</t>
         </is>
       </c>
       <c r="K64" s="92" t="inlineStr">
         <is>
-          <t>AI 가 생성한 카드 제목</t>
+          <t>IssueCardAgent 가 생성한 3줄 요약 배열</t>
         </is>
       </c>
     </row>
@@ -5378,12 +5374,12 @@
       <c r="B65" s="91" t="n"/>
       <c r="C65" s="92" t="inlineStr">
         <is>
-          <t>summary_lines</t>
+          <t>event_type</t>
         </is>
       </c>
       <c r="D65" s="92" t="inlineStr">
         <is>
-          <t>3줄 요약</t>
+          <t>이벤트 타입</t>
         </is>
       </c>
       <c r="E65" s="92" t="inlineStr">
@@ -5393,20 +5389,24 @@
       </c>
       <c r="F65" s="92" t="inlineStr">
         <is>
-          <t>TEXT[]</t>
-        </is>
-      </c>
-      <c r="G65" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G65" s="92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="H65" s="92" t="inlineStr"/>
       <c r="I65" s="92" t="inlineStr"/>
       <c r="J65" s="92" t="inlineStr">
         <is>
-          <t>Default '{}', 정확히 3줄</t>
+          <t>partnership|ma|personnel|tech|regulation|new_biz</t>
         </is>
       </c>
       <c r="K65" s="92" t="inlineStr">
         <is>
-          <t>IssueCardAgent 가 생성한 3줄 요약 배열</t>
+          <t>v3 이벤트 6 분류</t>
         </is>
       </c>
     </row>
@@ -5415,12 +5415,12 @@
       <c r="B66" s="91" t="n"/>
       <c r="C66" s="92" t="inlineStr">
         <is>
-          <t>event_type</t>
+          <t>importance</t>
         </is>
       </c>
       <c r="D66" s="92" t="inlineStr">
         <is>
-          <t>이벤트 타입</t>
+          <t>중요도 (band)</t>
         </is>
       </c>
       <c r="E66" s="92" t="inlineStr">
@@ -5435,19 +5435,19 @@
       </c>
       <c r="G66" s="92" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H66" s="92" t="inlineStr"/>
       <c r="I66" s="92" t="inlineStr"/>
       <c r="J66" s="92" t="inlineStr">
         <is>
-          <t>partnership|ma|personnel|tech|regulation|new_biz</t>
+          <t>v3: high|medium|low</t>
         </is>
       </c>
       <c r="K66" s="92" t="inlineStr">
         <is>
-          <t>v3 이벤트 6 분류</t>
+          <t>v3 exposure_band (구 urgent/notable/reference)</t>
         </is>
       </c>
     </row>
@@ -5456,12 +5456,12 @@
       <c r="B67" s="91" t="n"/>
       <c r="C67" s="92" t="inlineStr">
         <is>
-          <t>importance</t>
+          <t>importance_score</t>
         </is>
       </c>
       <c r="D67" s="92" t="inlineStr">
         <is>
-          <t>중요도 (band)</t>
+          <t>중요도 점수</t>
         </is>
       </c>
       <c r="E67" s="92" t="inlineStr">
@@ -5471,24 +5471,20 @@
       </c>
       <c r="F67" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G67" s="92" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>FLOAT</t>
+        </is>
+      </c>
+      <c r="G67" s="92" t="inlineStr"/>
       <c r="H67" s="92" t="inlineStr"/>
       <c r="I67" s="92" t="inlineStr"/>
       <c r="J67" s="92" t="inlineStr">
         <is>
-          <t>v3: high|medium|low</t>
+          <t>0.0~1.0</t>
         </is>
       </c>
       <c r="K67" s="92" t="inlineStr">
         <is>
-          <t>v3 exposure_band (구 urgent/notable/reference)</t>
+          <t>v3 exposure_score (결정적 산식)</t>
         </is>
       </c>
     </row>
@@ -5497,12 +5493,12 @@
       <c r="B68" s="91" t="n"/>
       <c r="C68" s="92" t="inlineStr">
         <is>
-          <t>importance_score</t>
+          <t>implication</t>
         </is>
       </c>
       <c r="D68" s="92" t="inlineStr">
         <is>
-          <t>중요도 점수</t>
+          <t>시사점 + 통합 메타</t>
         </is>
       </c>
       <c r="E68" s="92" t="inlineStr">
@@ -5512,20 +5508,16 @@
       </c>
       <c r="F68" s="92" t="inlineStr">
         <is>
-          <t>FLOAT</t>
+          <t>JSONB</t>
         </is>
       </c>
       <c r="G68" s="92" t="inlineStr"/>
       <c r="H68" s="92" t="inlineStr"/>
       <c r="I68" s="92" t="inlineStr"/>
-      <c r="J68" s="92" t="inlineStr">
-        <is>
-          <t>0.0~1.0</t>
-        </is>
-      </c>
+      <c r="J68" s="92" t="inlineStr"/>
       <c r="K68" s="92" t="inlineStr">
         <is>
-          <t>v3 exposure_score (결정적 산식)</t>
+          <t>{sector, sectors, exposure_score, exposure_band, signals, evidence_chain}</t>
         </is>
       </c>
     </row>
@@ -5534,12 +5526,12 @@
       <c r="B69" s="91" t="n"/>
       <c r="C69" s="92" t="inlineStr">
         <is>
-          <t>implication</t>
+          <t>sources</t>
         </is>
       </c>
       <c r="D69" s="92" t="inlineStr">
         <is>
-          <t>시사점 + 통합 메타</t>
+          <t>출처 목록</t>
         </is>
       </c>
       <c r="E69" s="92" t="inlineStr">
@@ -5555,10 +5547,14 @@
       <c r="G69" s="92" t="inlineStr"/>
       <c r="H69" s="92" t="inlineStr"/>
       <c r="I69" s="92" t="inlineStr"/>
-      <c r="J69" s="92" t="inlineStr"/>
+      <c r="J69" s="92" t="inlineStr">
+        <is>
+          <t>JSONB array</t>
+        </is>
+      </c>
       <c r="K69" s="92" t="inlineStr">
         <is>
-          <t>{sector, sectors, exposure_score, exposure_band, signals, evidence_chain}</t>
+          <t>원문 출처 (제목 · URL · source_name · credibility_score)</t>
         </is>
       </c>
     </row>
@@ -5567,12 +5563,12 @@
       <c r="B70" s="91" t="n"/>
       <c r="C70" s="92" t="inlineStr">
         <is>
-          <t>sources</t>
+          <t>validation_pass</t>
         </is>
       </c>
       <c r="D70" s="92" t="inlineStr">
         <is>
-          <t>출처 목록</t>
+          <t>검증 통과 여부</t>
         </is>
       </c>
       <c r="E70" s="92" t="inlineStr">
@@ -5582,20 +5578,16 @@
       </c>
       <c r="F70" s="92" t="inlineStr">
         <is>
-          <t>JSONB</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="G70" s="92" t="inlineStr"/>
       <c r="H70" s="92" t="inlineStr"/>
       <c r="I70" s="92" t="inlineStr"/>
-      <c r="J70" s="92" t="inlineStr">
-        <is>
-          <t>JSONB array</t>
-        </is>
-      </c>
+      <c r="J70" s="92" t="inlineStr"/>
       <c r="K70" s="92" t="inlineStr">
         <is>
-          <t>원문 출처 (제목 · URL · source_name · credibility_score)</t>
+          <t>EvidenceAgent 의 4종 chain 첨부 통과 여부</t>
         </is>
       </c>
     </row>
@@ -5604,12 +5596,12 @@
       <c r="B71" s="91" t="n"/>
       <c r="C71" s="92" t="inlineStr">
         <is>
-          <t>validation_pass</t>
+          <t>validation_sc_score</t>
         </is>
       </c>
       <c r="D71" s="92" t="inlineStr">
         <is>
-          <t>검증 통과 여부</t>
+          <t>SC 점수</t>
         </is>
       </c>
       <c r="E71" s="92" t="inlineStr">
@@ -5619,16 +5611,20 @@
       </c>
       <c r="F71" s="92" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>FLOAT</t>
         </is>
       </c>
       <c r="G71" s="92" t="inlineStr"/>
       <c r="H71" s="92" t="inlineStr"/>
       <c r="I71" s="92" t="inlineStr"/>
-      <c r="J71" s="92" t="inlineStr"/>
+      <c r="J71" s="92" t="inlineStr">
+        <is>
+          <t>1.0(pass) | 0.0(fail)</t>
+        </is>
+      </c>
       <c r="K71" s="92" t="inlineStr">
         <is>
-          <t>EvidenceAgent 의 4종 chain 첨부 통과 여부</t>
+          <t>v3 에서 의미 축소 — pass 의 binary flag</t>
         </is>
       </c>
     </row>
@@ -5637,12 +5633,12 @@
       <c r="B72" s="91" t="n"/>
       <c r="C72" s="92" t="inlineStr">
         <is>
-          <t>validation_sc_score</t>
+          <t>is_human_reviewed</t>
         </is>
       </c>
       <c r="D72" s="92" t="inlineStr">
         <is>
-          <t>SC 점수</t>
+          <t>사람 검토 여부</t>
         </is>
       </c>
       <c r="E72" s="92" t="inlineStr">
@@ -5652,7 +5648,7 @@
       </c>
       <c r="F72" s="92" t="inlineStr">
         <is>
-          <t>FLOAT</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="G72" s="92" t="inlineStr"/>
@@ -5660,12 +5656,12 @@
       <c r="I72" s="92" t="inlineStr"/>
       <c r="J72" s="92" t="inlineStr">
         <is>
-          <t>1.0(pass) | 0.0(fail)</t>
+          <t>Default FALSE</t>
         </is>
       </c>
       <c r="K72" s="92" t="inlineStr">
         <is>
-          <t>v3 에서 의미 축소 — pass 의 binary flag</t>
+          <t>운영자 수동 검토 플래그</t>
         </is>
       </c>
     </row>
@@ -5674,12 +5670,12 @@
       <c r="B73" s="91" t="n"/>
       <c r="C73" s="92" t="inlineStr">
         <is>
-          <t>is_human_reviewed</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D73" s="92" t="inlineStr">
         <is>
-          <t>사람 검토 여부</t>
+          <t>생성 시각</t>
         </is>
       </c>
       <c r="E73" s="92" t="inlineStr">
@@ -5689,7 +5685,7 @@
       </c>
       <c r="F73" s="92" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="G73" s="92" t="inlineStr"/>
@@ -5697,71 +5693,75 @@
       <c r="I73" s="92" t="inlineStr"/>
       <c r="J73" s="92" t="inlineStr">
         <is>
-          <t>Default FALSE</t>
+          <t>Default NOW()</t>
         </is>
       </c>
       <c r="K73" s="92" t="inlineStr">
         <is>
-          <t>운영자 수동 검토 플래그</t>
+          <t>row 생성 시각</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="91" t="n"/>
-      <c r="B74" s="91" t="n"/>
+      <c r="A74" s="91" t="inlineStr">
+        <is>
+          <t>evidence_chain</t>
+        </is>
+      </c>
+      <c r="B74" s="91" t="inlineStr">
+        <is>
+          <t>검증 체인 4종</t>
+        </is>
+      </c>
       <c r="C74" s="92" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D74" s="92" t="inlineStr">
         <is>
-          <t>생성 시각</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E74" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F74" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>BIGSERIAL</t>
         </is>
       </c>
       <c r="G74" s="92" t="inlineStr"/>
-      <c r="H74" s="92" t="inlineStr"/>
+      <c r="H74" s="92" t="inlineStr">
+        <is>
+          <t>PK1</t>
+        </is>
+      </c>
       <c r="I74" s="92" t="inlineStr"/>
       <c r="J74" s="92" t="inlineStr">
         <is>
-          <t>Default NOW()</t>
+          <t>AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="K74" s="92" t="inlineStr">
         <is>
-          <t>row 생성 시각</t>
+          <t>row PK</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="91" t="inlineStr">
-        <is>
-          <t>evidence_chain</t>
-        </is>
-      </c>
-      <c r="B75" s="91" t="inlineStr">
-        <is>
-          <t>검증 체인 4종</t>
-        </is>
-      </c>
+      <c r="A75" s="91" t="n"/>
+      <c r="B75" s="91" t="n"/>
       <c r="C75" s="92" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>issue_card_id</t>
         </is>
       </c>
       <c r="D75" s="92" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>카드 ID</t>
         </is>
       </c>
       <c r="E75" s="92" t="inlineStr">
@@ -5771,24 +5771,28 @@
       </c>
       <c r="F75" s="92" t="inlineStr">
         <is>
-          <t>BIGSERIAL</t>
-        </is>
-      </c>
-      <c r="G75" s="92" t="inlineStr"/>
-      <c r="H75" s="92" t="inlineStr">
-        <is>
-          <t>PK1</t>
-        </is>
-      </c>
-      <c r="I75" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G75" s="92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H75" s="92" t="inlineStr"/>
+      <c r="I75" s="92" t="inlineStr">
+        <is>
+          <t>issue_cards.id</t>
+        </is>
+      </c>
       <c r="J75" s="92" t="inlineStr">
         <is>
-          <t>AUTO_INCREMENT</t>
+          <t>UNIQUE · ON DELETE CASCADE</t>
         </is>
       </c>
       <c r="K75" s="92" t="inlineStr">
         <is>
-          <t>row PK</t>
+          <t>1:1 매핑되는 동향 카드</t>
         </is>
       </c>
     </row>
@@ -5797,43 +5801,35 @@
       <c r="B76" s="91" t="n"/>
       <c r="C76" s="92" t="inlineStr">
         <is>
-          <t>issue_card_id</t>
+          <t>source_links</t>
         </is>
       </c>
       <c r="D76" s="92" t="inlineStr">
         <is>
-          <t>카드 ID</t>
+          <t>출처 링크</t>
         </is>
       </c>
       <c r="E76" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F76" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G76" s="92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>JSONB</t>
+        </is>
+      </c>
+      <c r="G76" s="92" t="inlineStr"/>
       <c r="H76" s="92" t="inlineStr"/>
-      <c r="I76" s="92" t="inlineStr">
-        <is>
-          <t>issue_cards.id</t>
-        </is>
-      </c>
+      <c r="I76" s="92" t="inlineStr"/>
       <c r="J76" s="92" t="inlineStr">
         <is>
-          <t>UNIQUE · ON DELETE CASCADE</t>
+          <t>Default '[]'</t>
         </is>
       </c>
       <c r="K76" s="92" t="inlineStr">
         <is>
-          <t>1:1 매핑되는 동향 카드</t>
+          <t>[{title, url, source_name, credibility_score}]</t>
         </is>
       </c>
     </row>
@@ -5842,12 +5838,12 @@
       <c r="B77" s="91" t="n"/>
       <c r="C77" s="92" t="inlineStr">
         <is>
-          <t>source_links</t>
+          <t>provenance</t>
         </is>
       </c>
       <c r="D77" s="92" t="inlineStr">
         <is>
-          <t>출처 링크</t>
+          <t>프로비넌스</t>
         </is>
       </c>
       <c r="E77" s="92" t="inlineStr">
@@ -5865,12 +5861,12 @@
       <c r="I77" s="92" t="inlineStr"/>
       <c r="J77" s="92" t="inlineStr">
         <is>
-          <t>Default '[]'</t>
+          <t>Default '{}'</t>
         </is>
       </c>
       <c r="K77" s="92" t="inlineStr">
         <is>
-          <t>[{title, url, source_name, credibility_score}]</t>
+          <t>{raw_article_ids, cluster_id, llm_model, prompt_version, evidence_version, run_at}</t>
         </is>
       </c>
     </row>
@@ -5879,12 +5875,12 @@
       <c r="B78" s="91" t="n"/>
       <c r="C78" s="92" t="inlineStr">
         <is>
-          <t>provenance</t>
+          <t>financial_refs</t>
         </is>
       </c>
       <c r="D78" s="92" t="inlineStr">
         <is>
-          <t>프로비넌스</t>
+          <t>재무 참조</t>
         </is>
       </c>
       <c r="E78" s="92" t="inlineStr">
@@ -5902,12 +5898,12 @@
       <c r="I78" s="92" t="inlineStr"/>
       <c r="J78" s="92" t="inlineStr">
         <is>
-          <t>Default '{}'</t>
+          <t>Default '[]'</t>
         </is>
       </c>
       <c r="K78" s="92" t="inlineStr">
         <is>
-          <t>{raw_article_ids, cluster_id, llm_model, prompt_version, evidence_version, run_at}</t>
+          <t>[{period, metric, value, delta_qoq, delta_yoy, dart_rcept_no, ir_page}]</t>
         </is>
       </c>
     </row>
@@ -5916,12 +5912,12 @@
       <c r="B79" s="91" t="n"/>
       <c r="C79" s="92" t="inlineStr">
         <is>
-          <t>financial_refs</t>
+          <t>mbb_refs</t>
         </is>
       </c>
       <c r="D79" s="92" t="inlineStr">
         <is>
-          <t>재무 참조</t>
+          <t>컨설팅 참조</t>
         </is>
       </c>
       <c r="E79" s="92" t="inlineStr">
@@ -5939,12 +5935,12 @@
       <c r="I79" s="92" t="inlineStr"/>
       <c r="J79" s="92" t="inlineStr">
         <is>
-          <t>Default '[]'</t>
+          <t>Default '[]', W5 활성</t>
         </is>
       </c>
       <c r="K79" s="92" t="inlineStr">
         <is>
-          <t>[{period, metric, value, delta_qoq, delta_yoy, dart_rcept_no, ir_page}]</t>
+          <t>MBB·커니 보고서 자동 매칭 결과</t>
         </is>
       </c>
     </row>
@@ -5953,12 +5949,12 @@
       <c r="B80" s="91" t="n"/>
       <c r="C80" s="92" t="inlineStr">
         <is>
-          <t>mbb_refs</t>
+          <t>financial_link</t>
         </is>
       </c>
       <c r="D80" s="92" t="inlineStr">
         <is>
-          <t>컨설팅 참조</t>
+          <t>재무 링크 정보</t>
         </is>
       </c>
       <c r="E80" s="92" t="inlineStr">
@@ -5974,14 +5970,10 @@
       <c r="G80" s="92" t="inlineStr"/>
       <c r="H80" s="92" t="inlineStr"/>
       <c r="I80" s="92" t="inlineStr"/>
-      <c r="J80" s="92" t="inlineStr">
-        <is>
-          <t>Default '[]', W5 활성</t>
-        </is>
-      </c>
+      <c r="J80" s="92" t="inlineStr"/>
       <c r="K80" s="92" t="inlineStr">
         <is>
-          <t>MBB·커니 보고서 자동 매칭 결과</t>
+          <t>{linked, segment, highlights, headcount_delta, reason}</t>
         </is>
       </c>
     </row>
@@ -5990,12 +5982,12 @@
       <c r="B81" s="91" t="n"/>
       <c r="C81" s="92" t="inlineStr">
         <is>
-          <t>financial_link</t>
+          <t>evidence_version</t>
         </is>
       </c>
       <c r="D81" s="92" t="inlineStr">
         <is>
-          <t>재무 링크 정보</t>
+          <t>버전</t>
         </is>
       </c>
       <c r="E81" s="92" t="inlineStr">
@@ -6005,16 +5997,24 @@
       </c>
       <c r="F81" s="92" t="inlineStr">
         <is>
-          <t>JSONB</t>
-        </is>
-      </c>
-      <c r="G81" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G81" s="92" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="H81" s="92" t="inlineStr"/>
       <c r="I81" s="92" t="inlineStr"/>
-      <c r="J81" s="92" t="inlineStr"/>
+      <c r="J81" s="92" t="inlineStr">
+        <is>
+          <t>Default 'v3.0'</t>
+        </is>
+      </c>
       <c r="K81" s="92" t="inlineStr">
         <is>
-          <t>{linked, segment, highlights, headcount_delta, reason}</t>
+          <t>Evidence chain 스키마 버전</t>
         </is>
       </c>
     </row>
@@ -6023,12 +6023,12 @@
       <c r="B82" s="91" t="n"/>
       <c r="C82" s="92" t="inlineStr">
         <is>
-          <t>evidence_version</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="D82" s="92" t="inlineStr">
         <is>
-          <t>버전</t>
+          <t>검증 통과</t>
         </is>
       </c>
       <c r="E82" s="92" t="inlineStr">
@@ -6038,24 +6038,20 @@
       </c>
       <c r="F82" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G82" s="92" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="G82" s="92" t="inlineStr"/>
       <c r="H82" s="92" t="inlineStr"/>
       <c r="I82" s="92" t="inlineStr"/>
       <c r="J82" s="92" t="inlineStr">
         <is>
-          <t>Default 'v3.0'</t>
+          <t>Default FALSE</t>
         </is>
       </c>
       <c r="K82" s="92" t="inlineStr">
         <is>
-          <t>Evidence chain 스키마 버전</t>
+          <t>4종 모두 첨부됐는지</t>
         </is>
       </c>
     </row>
@@ -6064,12 +6060,12 @@
       <c r="B83" s="91" t="n"/>
       <c r="C83" s="92" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>missing</t>
         </is>
       </c>
       <c r="D83" s="92" t="inlineStr">
         <is>
-          <t>검증 통과</t>
+          <t>누락 항목</t>
         </is>
       </c>
       <c r="E83" s="92" t="inlineStr">
@@ -6079,7 +6075,7 @@
       </c>
       <c r="F83" s="92" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>TEXT[]</t>
         </is>
       </c>
       <c r="G83" s="92" t="inlineStr"/>
@@ -6087,12 +6083,12 @@
       <c r="I83" s="92" t="inlineStr"/>
       <c r="J83" s="92" t="inlineStr">
         <is>
-          <t>Default FALSE</t>
+          <t>Default '{}'</t>
         </is>
       </c>
       <c r="K83" s="92" t="inlineStr">
         <is>
-          <t>4종 모두 첨부됐는지</t>
+          <t>pass=false 시 누락된 chain 종류</t>
         </is>
       </c>
     </row>
@@ -6101,12 +6097,12 @@
       <c r="B84" s="91" t="n"/>
       <c r="C84" s="92" t="inlineStr">
         <is>
-          <t>missing</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D84" s="92" t="inlineStr">
         <is>
-          <t>누락 항목</t>
+          <t>생성 시각</t>
         </is>
       </c>
       <c r="E84" s="92" t="inlineStr">
@@ -6116,7 +6112,7 @@
       </c>
       <c r="F84" s="92" t="inlineStr">
         <is>
-          <t>TEXT[]</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="G84" s="92" t="inlineStr"/>
@@ -6124,98 +6120,102 @@
       <c r="I84" s="92" t="inlineStr"/>
       <c r="J84" s="92" t="inlineStr">
         <is>
-          <t>Default '{}'</t>
+          <t>Default NOW()</t>
         </is>
       </c>
       <c r="K84" s="92" t="inlineStr">
         <is>
-          <t>pass=false 시 누락된 chain 종류</t>
+          <t>row 생성 시각</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="91" t="n"/>
-      <c r="B85" s="91" t="n"/>
+      <c r="A85" s="91" t="inlineStr">
+        <is>
+          <t>article_images</t>
+        </is>
+      </c>
+      <c r="B85" s="91" t="inlineStr">
+        <is>
+          <t>카드 뉴스 이미지 메타</t>
+        </is>
+      </c>
       <c r="C85" s="92" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D85" s="92" t="inlineStr">
         <is>
-          <t>생성 시각</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E85" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F85" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>BIGSERIAL</t>
         </is>
       </c>
       <c r="G85" s="92" t="inlineStr"/>
-      <c r="H85" s="92" t="inlineStr"/>
+      <c r="H85" s="92" t="inlineStr">
+        <is>
+          <t>PK1</t>
+        </is>
+      </c>
       <c r="I85" s="92" t="inlineStr"/>
       <c r="J85" s="92" t="inlineStr">
         <is>
-          <t>Default NOW()</t>
+          <t>AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="K85" s="92" t="inlineStr">
         <is>
-          <t>row 생성 시각</t>
+          <t>row PK</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="91" t="inlineStr">
-        <is>
-          <t>article_images</t>
-        </is>
-      </c>
-      <c r="B86" s="91" t="inlineStr">
-        <is>
-          <t>카드 뉴스 이미지 메타</t>
-        </is>
-      </c>
+      <c r="A86" s="91" t="n"/>
+      <c r="B86" s="91" t="n"/>
       <c r="C86" s="92" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>article_id</t>
         </is>
       </c>
       <c r="D86" s="92" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>기사 ID</t>
         </is>
       </c>
       <c r="E86" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F86" s="92" t="inlineStr">
         <is>
-          <t>BIGSERIAL</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="G86" s="92" t="inlineStr"/>
-      <c r="H86" s="92" t="inlineStr">
-        <is>
-          <t>PK1</t>
-        </is>
-      </c>
-      <c r="I86" s="92" t="inlineStr"/>
+      <c r="H86" s="92" t="inlineStr"/>
+      <c r="I86" s="92" t="inlineStr">
+        <is>
+          <t>raw_articles.id</t>
+        </is>
+      </c>
       <c r="J86" s="92" t="inlineStr">
         <is>
-          <t>AUTO_INCREMENT</t>
+          <t>ON DELETE SET NULL</t>
         </is>
       </c>
       <c r="K86" s="92" t="inlineStr">
         <is>
-          <t>row PK</t>
+          <t>원본 기사 (출처)</t>
         </is>
       </c>
     </row>
@@ -6224,12 +6224,12 @@
       <c r="B87" s="91" t="n"/>
       <c r="C87" s="92" t="inlineStr">
         <is>
-          <t>article_id</t>
+          <t>cluster_id</t>
         </is>
       </c>
       <c r="D87" s="92" t="inlineStr">
         <is>
-          <t>기사 ID</t>
+          <t>클러스터 ID</t>
         </is>
       </c>
       <c r="E87" s="92" t="inlineStr">
@@ -6244,19 +6244,11 @@
       </c>
       <c r="G87" s="92" t="inlineStr"/>
       <c r="H87" s="92" t="inlineStr"/>
-      <c r="I87" s="92" t="inlineStr">
-        <is>
-          <t>raw_articles.id</t>
-        </is>
-      </c>
-      <c r="J87" s="92" t="inlineStr">
-        <is>
-          <t>ON DELETE SET NULL</t>
-        </is>
-      </c>
+      <c r="I87" s="92" t="inlineStr"/>
+      <c r="J87" s="92" t="inlineStr"/>
       <c r="K87" s="92" t="inlineStr">
         <is>
-          <t>원본 기사 (출처)</t>
+          <t>이미지가 속한 클러스터</t>
         </is>
       </c>
     </row>
@@ -6265,12 +6257,12 @@
       <c r="B88" s="91" t="n"/>
       <c r="C88" s="92" t="inlineStr">
         <is>
-          <t>cluster_id</t>
+          <t>issue_card_id</t>
         </is>
       </c>
       <c r="D88" s="92" t="inlineStr">
         <is>
-          <t>클러스터 ID</t>
+          <t>카드 ID</t>
         </is>
       </c>
       <c r="E88" s="92" t="inlineStr">
@@ -6280,16 +6272,28 @@
       </c>
       <c r="F88" s="92" t="inlineStr">
         <is>
-          <t>BIGINT</t>
-        </is>
-      </c>
-      <c r="G88" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G88" s="92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="H88" s="92" t="inlineStr"/>
-      <c r="I88" s="92" t="inlineStr"/>
-      <c r="J88" s="92" t="inlineStr"/>
+      <c r="I88" s="92" t="inlineStr">
+        <is>
+          <t>issue_cards.id</t>
+        </is>
+      </c>
+      <c r="J88" s="92" t="inlineStr">
+        <is>
+          <t>ON DELETE SET NULL</t>
+        </is>
+      </c>
       <c r="K88" s="92" t="inlineStr">
         <is>
-          <t>이미지가 속한 클러스터</t>
+          <t>backend lookup 키 — 카드별 대표 이미지</t>
         </is>
       </c>
     </row>
@@ -6298,43 +6302,31 @@
       <c r="B89" s="91" t="n"/>
       <c r="C89" s="92" t="inlineStr">
         <is>
-          <t>issue_card_id</t>
+          <t>source_url</t>
         </is>
       </c>
       <c r="D89" s="92" t="inlineStr">
         <is>
-          <t>카드 ID</t>
+          <t>원본 URL</t>
         </is>
       </c>
       <c r="E89" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F89" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G89" s="92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="G89" s="92" t="inlineStr"/>
       <c r="H89" s="92" t="inlineStr"/>
-      <c r="I89" s="92" t="inlineStr">
-        <is>
-          <t>issue_cards.id</t>
-        </is>
-      </c>
-      <c r="J89" s="92" t="inlineStr">
-        <is>
-          <t>ON DELETE SET NULL</t>
-        </is>
-      </c>
+      <c r="I89" s="92" t="inlineStr"/>
+      <c r="J89" s="92" t="inlineStr"/>
       <c r="K89" s="92" t="inlineStr">
         <is>
-          <t>backend lookup 키 — 카드별 대표 이미지</t>
+          <t>og:image / twitter:image / 본문 첫 &lt;img&gt;</t>
         </is>
       </c>
     </row>
@@ -6343,12 +6335,12 @@
       <c r="B90" s="91" t="n"/>
       <c r="C90" s="92" t="inlineStr">
         <is>
-          <t>source_url</t>
+          <t>source_url_hash</t>
         </is>
       </c>
       <c r="D90" s="92" t="inlineStr">
         <is>
-          <t>원본 URL</t>
+          <t>URL 해시</t>
         </is>
       </c>
       <c r="E90" s="92" t="inlineStr">
@@ -6358,16 +6350,24 @@
       </c>
       <c r="F90" s="92" t="inlineStr">
         <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="G90" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G90" s="92" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="H90" s="92" t="inlineStr"/>
       <c r="I90" s="92" t="inlineStr"/>
-      <c r="J90" s="92" t="inlineStr"/>
+      <c r="J90" s="92" t="inlineStr">
+        <is>
+          <t>UNIQUE</t>
+        </is>
+      </c>
       <c r="K90" s="92" t="inlineStr">
         <is>
-          <t>og:image / twitter:image / 본문 첫 &lt;img&gt;</t>
+          <t>SHA-256(source_url) — 중복 다운로드 차단</t>
         </is>
       </c>
     </row>
@@ -6376,12 +6376,12 @@
       <c r="B91" s="91" t="n"/>
       <c r="C91" s="92" t="inlineStr">
         <is>
-          <t>source_url_hash</t>
+          <t>storage_path</t>
         </is>
       </c>
       <c r="D91" s="92" t="inlineStr">
         <is>
-          <t>URL 해시</t>
+          <t>저장 경로</t>
         </is>
       </c>
       <c r="E91" s="92" t="inlineStr">
@@ -6391,24 +6391,20 @@
       </c>
       <c r="F91" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G91" s="92" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="G91" s="92" t="inlineStr"/>
       <c r="H91" s="92" t="inlineStr"/>
       <c r="I91" s="92" t="inlineStr"/>
       <c r="J91" s="92" t="inlineStr">
         <is>
-          <t>UNIQUE</t>
+          <t>상대 경로</t>
         </is>
       </c>
       <c r="K91" s="92" t="inlineStr">
         <is>
-          <t>SHA-256(source_url) — 중복 다운로드 차단</t>
+          <t>IMAGE_STORAGE_PATH 기준 (예: lg_cns/2026-04/&lt;hash&gt;.jpg)</t>
         </is>
       </c>
     </row>
@@ -6417,35 +6413,39 @@
       <c r="B92" s="91" t="n"/>
       <c r="C92" s="92" t="inlineStr">
         <is>
-          <t>storage_path</t>
+          <t>content_type</t>
         </is>
       </c>
       <c r="D92" s="92" t="inlineStr">
         <is>
-          <t>저장 경로</t>
+          <t>MIME 타입</t>
         </is>
       </c>
       <c r="E92" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F92" s="92" t="inlineStr">
         <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="G92" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G92" s="92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="H92" s="92" t="inlineStr"/>
       <c r="I92" s="92" t="inlineStr"/>
       <c r="J92" s="92" t="inlineStr">
         <is>
-          <t>상대 경로</t>
+          <t>image/jpeg|png|webp</t>
         </is>
       </c>
       <c r="K92" s="92" t="inlineStr">
         <is>
-          <t>IMAGE_STORAGE_PATH 기준 (예: lg_cns/2026-04/&lt;hash&gt;.jpg)</t>
+          <t>이미지 MIME</t>
         </is>
       </c>
     </row>
@@ -6454,12 +6454,12 @@
       <c r="B93" s="91" t="n"/>
       <c r="C93" s="92" t="inlineStr">
         <is>
-          <t>content_type</t>
+          <t>width</t>
         </is>
       </c>
       <c r="D93" s="92" t="inlineStr">
         <is>
-          <t>MIME 타입</t>
+          <t>너비</t>
         </is>
       </c>
       <c r="E93" s="92" t="inlineStr">
@@ -6469,24 +6469,20 @@
       </c>
       <c r="F93" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G93" s="92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="G93" s="92" t="inlineStr"/>
       <c r="H93" s="92" t="inlineStr"/>
       <c r="I93" s="92" t="inlineStr"/>
       <c r="J93" s="92" t="inlineStr">
         <is>
-          <t>image/jpeg|png|webp</t>
+          <t>px</t>
         </is>
       </c>
       <c r="K93" s="92" t="inlineStr">
         <is>
-          <t>이미지 MIME</t>
+          <t>이미지 너비</t>
         </is>
       </c>
     </row>
@@ -6495,12 +6491,12 @@
       <c r="B94" s="91" t="n"/>
       <c r="C94" s="92" t="inlineStr">
         <is>
-          <t>width</t>
+          <t>height</t>
         </is>
       </c>
       <c r="D94" s="92" t="inlineStr">
         <is>
-          <t>너비</t>
+          <t>높이</t>
         </is>
       </c>
       <c r="E94" s="92" t="inlineStr">
@@ -6523,7 +6519,7 @@
       </c>
       <c r="K94" s="92" t="inlineStr">
         <is>
-          <t>이미지 너비</t>
+          <t>이미지 높이</t>
         </is>
       </c>
     </row>
@@ -6532,12 +6528,12 @@
       <c r="B95" s="91" t="n"/>
       <c r="C95" s="92" t="inlineStr">
         <is>
-          <t>height</t>
+          <t>file_size_bytes</t>
         </is>
       </c>
       <c r="D95" s="92" t="inlineStr">
         <is>
-          <t>높이</t>
+          <t>파일 크기</t>
         </is>
       </c>
       <c r="E95" s="92" t="inlineStr">
@@ -6555,12 +6551,12 @@
       <c r="I95" s="92" t="inlineStr"/>
       <c r="J95" s="92" t="inlineStr">
         <is>
-          <t>px</t>
+          <t>≤5MB</t>
         </is>
       </c>
       <c r="K95" s="92" t="inlineStr">
         <is>
-          <t>이미지 높이</t>
+          <t>파일 바이트 (5MB 상한)</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6565,12 @@
       <c r="B96" s="91" t="n"/>
       <c r="C96" s="92" t="inlineStr">
         <is>
-          <t>file_size_bytes</t>
+          <t>alt_text</t>
         </is>
       </c>
       <c r="D96" s="92" t="inlineStr">
         <is>
-          <t>파일 크기</t>
+          <t>alt 텍스트</t>
         </is>
       </c>
       <c r="E96" s="92" t="inlineStr">
@@ -6584,20 +6580,16 @@
       </c>
       <c r="F96" s="92" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="G96" s="92" t="inlineStr"/>
       <c r="H96" s="92" t="inlineStr"/>
       <c r="I96" s="92" t="inlineStr"/>
-      <c r="J96" s="92" t="inlineStr">
-        <is>
-          <t>≤5MB</t>
-        </is>
-      </c>
+      <c r="J96" s="92" t="inlineStr"/>
       <c r="K96" s="92" t="inlineStr">
         <is>
-          <t>파일 바이트 (5MB 상한)</t>
+          <t>접근성 + 이메일 차단 시 노출</t>
         </is>
       </c>
     </row>
@@ -6606,12 +6598,12 @@
       <c r="B97" s="91" t="n"/>
       <c r="C97" s="92" t="inlineStr">
         <is>
-          <t>alt_text</t>
+          <t>attribution</t>
         </is>
       </c>
       <c r="D97" s="92" t="inlineStr">
         <is>
-          <t>alt 텍스트</t>
+          <t>출처 표기</t>
         </is>
       </c>
       <c r="E97" s="92" t="inlineStr">
@@ -6630,7 +6622,7 @@
       <c r="J97" s="92" t="inlineStr"/>
       <c r="K97" s="92" t="inlineStr">
         <is>
-          <t>접근성 + 이메일 차단 시 노출</t>
+          <t>예: '제공: 한경'</t>
         </is>
       </c>
     </row>
@@ -6639,12 +6631,12 @@
       <c r="B98" s="91" t="n"/>
       <c r="C98" s="92" t="inlineStr">
         <is>
-          <t>attribution</t>
+          <t>fetched_at</t>
         </is>
       </c>
       <c r="D98" s="92" t="inlineStr">
         <is>
-          <t>출처 표기</t>
+          <t>다운로드 시각</t>
         </is>
       </c>
       <c r="E98" s="92" t="inlineStr">
@@ -6654,7 +6646,7 @@
       </c>
       <c r="F98" s="92" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="G98" s="92" t="inlineStr"/>
@@ -6663,7 +6655,7 @@
       <c r="J98" s="92" t="inlineStr"/>
       <c r="K98" s="92" t="inlineStr">
         <is>
-          <t>예: '제공: 한경'</t>
+          <t>이미지 다운로드 완료 시각</t>
         </is>
       </c>
     </row>
@@ -6672,12 +6664,12 @@
       <c r="B99" s="91" t="n"/>
       <c r="C99" s="92" t="inlineStr">
         <is>
-          <t>fetched_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D99" s="92" t="inlineStr">
         <is>
-          <t>다운로드 시각</t>
+          <t>생성 시각</t>
         </is>
       </c>
       <c r="E99" s="92" t="inlineStr">
@@ -6693,69 +6685,77 @@
       <c r="G99" s="92" t="inlineStr"/>
       <c r="H99" s="92" t="inlineStr"/>
       <c r="I99" s="92" t="inlineStr"/>
-      <c r="J99" s="92" t="inlineStr"/>
+      <c r="J99" s="92" t="inlineStr">
+        <is>
+          <t>Default NOW()</t>
+        </is>
+      </c>
       <c r="K99" s="92" t="inlineStr">
         <is>
-          <t>이미지 다운로드 완료 시각</t>
+          <t>row 생성 시각</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="91" t="n"/>
-      <c r="B100" s="91" t="n"/>
+      <c r="A100" s="91" t="inlineStr">
+        <is>
+          <t>recipients</t>
+        </is>
+      </c>
+      <c r="B100" s="91" t="inlineStr">
+        <is>
+          <t>메일 수신자</t>
+        </is>
+      </c>
       <c r="C100" s="92" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D100" s="92" t="inlineStr">
         <is>
-          <t>생성 시각</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E100" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F100" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>BIGSERIAL</t>
         </is>
       </c>
       <c r="G100" s="92" t="inlineStr"/>
-      <c r="H100" s="92" t="inlineStr"/>
+      <c r="H100" s="92" t="inlineStr">
+        <is>
+          <t>PK1</t>
+        </is>
+      </c>
       <c r="I100" s="92" t="inlineStr"/>
       <c r="J100" s="92" t="inlineStr">
         <is>
-          <t>Default NOW()</t>
+          <t>AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="K100" s="92" t="inlineStr">
         <is>
-          <t>row 생성 시각</t>
+          <t>row PK</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="91" t="inlineStr">
-        <is>
-          <t>recipients</t>
-        </is>
-      </c>
-      <c r="B101" s="91" t="inlineStr">
-        <is>
-          <t>메일 수신자</t>
-        </is>
-      </c>
+      <c r="A101" s="91" t="n"/>
+      <c r="B101" s="91" t="n"/>
       <c r="C101" s="92" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>email</t>
         </is>
       </c>
       <c r="D101" s="92" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>이메일</t>
         </is>
       </c>
       <c r="E101" s="92" t="inlineStr">
@@ -6765,24 +6765,24 @@
       </c>
       <c r="F101" s="92" t="inlineStr">
         <is>
-          <t>BIGSERIAL</t>
-        </is>
-      </c>
-      <c r="G101" s="92" t="inlineStr"/>
-      <c r="H101" s="92" t="inlineStr">
-        <is>
-          <t>PK1</t>
-        </is>
-      </c>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G101" s="92" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="H101" s="92" t="inlineStr"/>
       <c r="I101" s="92" t="inlineStr"/>
       <c r="J101" s="92" t="inlineStr">
         <is>
-          <t>AUTO_INCREMENT</t>
+          <t>UNIQUE</t>
         </is>
       </c>
       <c r="K101" s="92" t="inlineStr">
         <is>
-          <t>row PK</t>
+          <t>수신자 이메일 (중복 차단 키)</t>
         </is>
       </c>
     </row>
@@ -6791,17 +6791,17 @@
       <c r="B102" s="91" t="n"/>
       <c r="C102" s="92" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>name</t>
         </is>
       </c>
       <c r="D102" s="92" t="inlineStr">
         <is>
-          <t>이메일</t>
+          <t>이름</t>
         </is>
       </c>
       <c r="E102" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F102" s="92" t="inlineStr">
@@ -6811,19 +6811,15 @@
       </c>
       <c r="G102" s="92" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H102" s="92" t="inlineStr"/>
       <c r="I102" s="92" t="inlineStr"/>
-      <c r="J102" s="92" t="inlineStr">
-        <is>
-          <t>UNIQUE</t>
-        </is>
-      </c>
+      <c r="J102" s="92" t="inlineStr"/>
       <c r="K102" s="92" t="inlineStr">
         <is>
-          <t>수신자 이메일 (중복 차단 키)</t>
+          <t>수신자 이름</t>
         </is>
       </c>
     </row>
@@ -6832,17 +6828,17 @@
       <c r="B103" s="91" t="n"/>
       <c r="C103" s="92" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>role</t>
         </is>
       </c>
       <c r="D103" s="92" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>역할</t>
         </is>
       </c>
       <c r="E103" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F103" s="92" t="inlineStr">
@@ -6852,15 +6848,19 @@
       </c>
       <c r="G103" s="92" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H103" s="92" t="inlineStr"/>
       <c r="I103" s="92" t="inlineStr"/>
-      <c r="J103" s="92" t="inlineStr"/>
+      <c r="J103" s="92" t="inlineStr">
+        <is>
+          <t>pm|executive|admin</t>
+        </is>
+      </c>
       <c r="K103" s="92" t="inlineStr">
         <is>
-          <t>수신자 이름</t>
+          <t>PM=전체 / executive=핵심 / admin=관리자</t>
         </is>
       </c>
     </row>
@@ -6869,12 +6869,12 @@
       <c r="B104" s="91" t="n"/>
       <c r="C104" s="92" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>impact_threshold</t>
         </is>
       </c>
       <c r="D104" s="92" t="inlineStr">
         <is>
-          <t>역할</t>
+          <t>임팩트 임계치</t>
         </is>
       </c>
       <c r="E104" s="92" t="inlineStr">
@@ -6884,24 +6884,20 @@
       </c>
       <c r="F104" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G104" s="92" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>SMALLINT</t>
+        </is>
+      </c>
+      <c r="G104" s="92" t="inlineStr"/>
       <c r="H104" s="92" t="inlineStr"/>
       <c r="I104" s="92" t="inlineStr"/>
       <c r="J104" s="92" t="inlineStr">
         <is>
-          <t>pm|executive|admin</t>
+          <t>Default 3, 1~5</t>
         </is>
       </c>
       <c r="K104" s="92" t="inlineStr">
         <is>
-          <t>PM=전체 / executive=핵심 / admin=관리자</t>
+          <t>포함될 카드 최소 importance_score (PM=3, 임원=4)</t>
         </is>
       </c>
     </row>
@@ -6910,35 +6906,39 @@
       <c r="B105" s="91" t="n"/>
       <c r="C105" s="92" t="inlineStr">
         <is>
-          <t>impact_threshold</t>
+          <t>locale</t>
         </is>
       </c>
       <c r="D105" s="92" t="inlineStr">
         <is>
-          <t>임팩트 임계치</t>
+          <t>로케일</t>
         </is>
       </c>
       <c r="E105" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F105" s="92" t="inlineStr">
         <is>
-          <t>SMALLINT</t>
-        </is>
-      </c>
-      <c r="G105" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G105" s="92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="H105" s="92" t="inlineStr"/>
       <c r="I105" s="92" t="inlineStr"/>
       <c r="J105" s="92" t="inlineStr">
         <is>
-          <t>Default 3, 1~5</t>
+          <t>Default 'ko-KR'</t>
         </is>
       </c>
       <c r="K105" s="92" t="inlineStr">
         <is>
-          <t>포함될 카드 최소 importance_score (PM=3, 임원=4)</t>
+          <t>메일 언어 (ko-KR 등)</t>
         </is>
       </c>
     </row>
@@ -6947,12 +6947,12 @@
       <c r="B106" s="91" t="n"/>
       <c r="C106" s="92" t="inlineStr">
         <is>
-          <t>locale</t>
+          <t>is_active</t>
         </is>
       </c>
       <c r="D106" s="92" t="inlineStr">
         <is>
-          <t>로케일</t>
+          <t>활성 여부</t>
         </is>
       </c>
       <c r="E106" s="92" t="inlineStr">
@@ -6962,24 +6962,20 @@
       </c>
       <c r="F106" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G106" s="92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>BOOLEAN</t>
+        </is>
+      </c>
+      <c r="G106" s="92" t="inlineStr"/>
       <c r="H106" s="92" t="inlineStr"/>
       <c r="I106" s="92" t="inlineStr"/>
       <c r="J106" s="92" t="inlineStr">
         <is>
-          <t>Default 'ko-KR'</t>
+          <t>Default TRUE</t>
         </is>
       </c>
       <c r="K106" s="92" t="inlineStr">
         <is>
-          <t>메일 언어 (ko-KR 등)</t>
+          <t>현재 발송 대상 여부</t>
         </is>
       </c>
     </row>
@@ -6988,12 +6984,12 @@
       <c r="B107" s="91" t="n"/>
       <c r="C107" s="92" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D107" s="92" t="inlineStr">
         <is>
-          <t>활성 여부</t>
+          <t>생성 시각</t>
         </is>
       </c>
       <c r="E107" s="92" t="inlineStr">
@@ -7003,7 +6999,7 @@
       </c>
       <c r="F107" s="92" t="inlineStr">
         <is>
-          <t>BOOLEAN</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="G107" s="92" t="inlineStr"/>
@@ -7011,12 +7007,12 @@
       <c r="I107" s="92" t="inlineStr"/>
       <c r="J107" s="92" t="inlineStr">
         <is>
-          <t>Default TRUE</t>
+          <t>Default NOW()</t>
         </is>
       </c>
       <c r="K107" s="92" t="inlineStr">
         <is>
-          <t>현재 발송 대상 여부</t>
+          <t>row 생성 시각</t>
         </is>
       </c>
     </row>
@@ -7025,12 +7021,12 @@
       <c r="B108" s="91" t="n"/>
       <c r="C108" s="92" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>updated_at</t>
         </is>
       </c>
       <c r="D108" s="92" t="inlineStr">
         <is>
-          <t>생성 시각</t>
+          <t>수정 시각</t>
         </is>
       </c>
       <c r="E108" s="92" t="inlineStr">
@@ -7053,66 +7049,70 @@
       </c>
       <c r="K108" s="92" t="inlineStr">
         <is>
-          <t>row 생성 시각</t>
+          <t>row 수정 시각</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="91" t="n"/>
-      <c r="B109" s="91" t="n"/>
+      <c r="A109" s="91" t="inlineStr">
+        <is>
+          <t>briefing_history</t>
+        </is>
+      </c>
+      <c r="B109" s="91" t="inlineStr">
+        <is>
+          <t>메일 발송 이력</t>
+        </is>
+      </c>
       <c r="C109" s="92" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D109" s="92" t="inlineStr">
         <is>
-          <t>수정 시각</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E109" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F109" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>BIGSERIAL</t>
         </is>
       </c>
       <c r="G109" s="92" t="inlineStr"/>
-      <c r="H109" s="92" t="inlineStr"/>
+      <c r="H109" s="92" t="inlineStr">
+        <is>
+          <t>PK1</t>
+        </is>
+      </c>
       <c r="I109" s="92" t="inlineStr"/>
       <c r="J109" s="92" t="inlineStr">
         <is>
-          <t>Default NOW()</t>
+          <t>AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="K109" s="92" t="inlineStr">
         <is>
-          <t>row 수정 시각</t>
+          <t>row PK</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="91" t="inlineStr">
-        <is>
-          <t>briefing_history</t>
-        </is>
-      </c>
-      <c r="B110" s="91" t="inlineStr">
-        <is>
-          <t>메일 발송 이력</t>
-        </is>
-      </c>
+      <c r="A110" s="91" t="n"/>
+      <c r="B110" s="91" t="n"/>
       <c r="C110" s="92" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>recipient_id</t>
         </is>
       </c>
       <c r="D110" s="92" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>수신자 ID</t>
         </is>
       </c>
       <c r="E110" s="92" t="inlineStr">
@@ -7122,24 +7122,24 @@
       </c>
       <c r="F110" s="92" t="inlineStr">
         <is>
-          <t>BIGSERIAL</t>
+          <t>BIGINT</t>
         </is>
       </c>
       <c r="G110" s="92" t="inlineStr"/>
-      <c r="H110" s="92" t="inlineStr">
-        <is>
-          <t>PK1</t>
-        </is>
-      </c>
-      <c r="I110" s="92" t="inlineStr"/>
+      <c r="H110" s="92" t="inlineStr"/>
+      <c r="I110" s="92" t="inlineStr">
+        <is>
+          <t>recipients.id</t>
+        </is>
+      </c>
       <c r="J110" s="92" t="inlineStr">
         <is>
-          <t>AUTO_INCREMENT</t>
+          <t>ON DELETE RESTRICT</t>
         </is>
       </c>
       <c r="K110" s="92" t="inlineStr">
         <is>
-          <t>row PK</t>
+          <t>발송 대상 수신자</t>
         </is>
       </c>
     </row>
@@ -7148,12 +7148,12 @@
       <c r="B111" s="91" t="n"/>
       <c r="C111" s="92" t="inlineStr">
         <is>
-          <t>recipient_id</t>
+          <t>briefing_date</t>
         </is>
       </c>
       <c r="D111" s="92" t="inlineStr">
         <is>
-          <t>수신자 ID</t>
+          <t>브리핑 날짜</t>
         </is>
       </c>
       <c r="E111" s="92" t="inlineStr">
@@ -7163,24 +7163,16 @@
       </c>
       <c r="F111" s="92" t="inlineStr">
         <is>
-          <t>BIGINT</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="G111" s="92" t="inlineStr"/>
       <c r="H111" s="92" t="inlineStr"/>
-      <c r="I111" s="92" t="inlineStr">
-        <is>
-          <t>recipients.id</t>
-        </is>
-      </c>
-      <c r="J111" s="92" t="inlineStr">
-        <is>
-          <t>ON DELETE RESTRICT</t>
-        </is>
-      </c>
+      <c r="I111" s="92" t="inlineStr"/>
+      <c r="J111" s="92" t="inlineStr"/>
       <c r="K111" s="92" t="inlineStr">
         <is>
-          <t>발송 대상 수신자</t>
+          <t>어느 영업일의 브리핑인지</t>
         </is>
       </c>
     </row>
@@ -7189,31 +7181,35 @@
       <c r="B112" s="91" t="n"/>
       <c r="C112" s="92" t="inlineStr">
         <is>
-          <t>briefing_date</t>
+          <t>run_id</t>
         </is>
       </c>
       <c r="D112" s="92" t="inlineStr">
         <is>
-          <t>브리핑 날짜</t>
+          <t>실행 ID</t>
         </is>
       </c>
       <c r="E112" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F112" s="92" t="inlineStr">
         <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="G112" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G112" s="92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="H112" s="92" t="inlineStr"/>
       <c r="I112" s="92" t="inlineStr"/>
       <c r="J112" s="92" t="inlineStr"/>
       <c r="K112" s="92" t="inlineStr">
         <is>
-          <t>어느 영업일의 브리핑인지</t>
+          <t>한 cycle 식별자 (재시도 추적)</t>
         </is>
       </c>
     </row>
@@ -7222,35 +7218,35 @@
       <c r="B113" s="91" t="n"/>
       <c r="C113" s="92" t="inlineStr">
         <is>
-          <t>run_id</t>
+          <t>card_count</t>
         </is>
       </c>
       <c r="D113" s="92" t="inlineStr">
         <is>
-          <t>실행 ID</t>
+          <t>카드 수</t>
         </is>
       </c>
       <c r="E113" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F113" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G113" s="92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="G113" s="92" t="inlineStr"/>
       <c r="H113" s="92" t="inlineStr"/>
       <c r="I113" s="92" t="inlineStr"/>
-      <c r="J113" s="92" t="inlineStr"/>
+      <c r="J113" s="92" t="inlineStr">
+        <is>
+          <t>Default 0</t>
+        </is>
+      </c>
       <c r="K113" s="92" t="inlineStr">
         <is>
-          <t>한 cycle 식별자 (재시도 추적)</t>
+          <t>발송된 카드 개수</t>
         </is>
       </c>
     </row>
@@ -7259,22 +7255,22 @@
       <c r="B114" s="91" t="n"/>
       <c r="C114" s="92" t="inlineStr">
         <is>
-          <t>card_count</t>
+          <t>card_ids</t>
         </is>
       </c>
       <c r="D114" s="92" t="inlineStr">
         <is>
-          <t>카드 수</t>
+          <t>카드 ID 배열</t>
         </is>
       </c>
       <c r="E114" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F114" s="92" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>TEXT[]</t>
         </is>
       </c>
       <c r="G114" s="92" t="inlineStr"/>
@@ -7282,12 +7278,12 @@
       <c r="I114" s="92" t="inlineStr"/>
       <c r="J114" s="92" t="inlineStr">
         <is>
-          <t>Default 0</t>
+          <t>Default '{}'</t>
         </is>
       </c>
       <c r="K114" s="92" t="inlineStr">
         <is>
-          <t>발송된 카드 개수</t>
+          <t>포함된 issue_cards.id 배열</t>
         </is>
       </c>
     </row>
@@ -7296,12 +7292,12 @@
       <c r="B115" s="91" t="n"/>
       <c r="C115" s="92" t="inlineStr">
         <is>
-          <t>card_ids</t>
+          <t>subject</t>
         </is>
       </c>
       <c r="D115" s="92" t="inlineStr">
         <is>
-          <t>카드 ID 배열</t>
+          <t>메일 제목</t>
         </is>
       </c>
       <c r="E115" s="92" t="inlineStr">
@@ -7311,20 +7307,16 @@
       </c>
       <c r="F115" s="92" t="inlineStr">
         <is>
-          <t>TEXT[]</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="G115" s="92" t="inlineStr"/>
       <c r="H115" s="92" t="inlineStr"/>
       <c r="I115" s="92" t="inlineStr"/>
-      <c r="J115" s="92" t="inlineStr">
-        <is>
-          <t>Default '{}'</t>
-        </is>
-      </c>
+      <c r="J115" s="92" t="inlineStr"/>
       <c r="K115" s="92" t="inlineStr">
         <is>
-          <t>포함된 issue_cards.id 배열</t>
+          <t>메일 제목 (저장 옵션)</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7325,12 @@
       <c r="B116" s="91" t="n"/>
       <c r="C116" s="92" t="inlineStr">
         <is>
-          <t>subject</t>
+          <t>body_preview</t>
         </is>
       </c>
       <c r="D116" s="92" t="inlineStr">
         <is>
-          <t>메일 제목</t>
+          <t>본문 미리보기</t>
         </is>
       </c>
       <c r="E116" s="92" t="inlineStr">
@@ -7354,10 +7346,14 @@
       <c r="G116" s="92" t="inlineStr"/>
       <c r="H116" s="92" t="inlineStr"/>
       <c r="I116" s="92" t="inlineStr"/>
-      <c r="J116" s="92" t="inlineStr"/>
+      <c r="J116" s="92" t="inlineStr">
+        <is>
+          <t>첫 200자</t>
+        </is>
+      </c>
       <c r="K116" s="92" t="inlineStr">
         <is>
-          <t>메일 제목 (저장 옵션)</t>
+          <t>본문 첫 200자 (감사 + 디버깅)</t>
         </is>
       </c>
     </row>
@@ -7366,35 +7362,39 @@
       <c r="B117" s="91" t="n"/>
       <c r="C117" s="92" t="inlineStr">
         <is>
-          <t>body_preview</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D117" s="92" t="inlineStr">
         <is>
-          <t>본문 미리보기</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="E117" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F117" s="92" t="inlineStr">
         <is>
-          <t>TEXT</t>
-        </is>
-      </c>
-      <c r="G117" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G117" s="92" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="H117" s="92" t="inlineStr"/>
       <c r="I117" s="92" t="inlineStr"/>
       <c r="J117" s="92" t="inlineStr">
         <is>
-          <t>첫 200자</t>
+          <t>sent|failed|skipped</t>
         </is>
       </c>
       <c r="K117" s="92" t="inlineStr">
         <is>
-          <t>본문 첫 200자 (감사 + 디버깅)</t>
+          <t>발송 결과</t>
         </is>
       </c>
     </row>
@@ -7403,39 +7403,31 @@
       <c r="B118" s="91" t="n"/>
       <c r="C118" s="92" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>smtp_response</t>
         </is>
       </c>
       <c r="D118" s="92" t="inlineStr">
         <is>
-          <t>상태</t>
+          <t>SMTP 응답</t>
         </is>
       </c>
       <c r="E118" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F118" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G118" s="92" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="G118" s="92" t="inlineStr"/>
       <c r="H118" s="92" t="inlineStr"/>
       <c r="I118" s="92" t="inlineStr"/>
-      <c r="J118" s="92" t="inlineStr">
-        <is>
-          <t>sent|failed|skipped</t>
-        </is>
-      </c>
+      <c r="J118" s="92" t="inlineStr"/>
       <c r="K118" s="92" t="inlineStr">
         <is>
-          <t>발송 결과</t>
+          <t>SendGrid/SMTP 응답 코드 + 메시지</t>
         </is>
       </c>
     </row>
@@ -7444,12 +7436,12 @@
       <c r="B119" s="91" t="n"/>
       <c r="C119" s="92" t="inlineStr">
         <is>
-          <t>smtp_response</t>
+          <t>error_msg</t>
         </is>
       </c>
       <c r="D119" s="92" t="inlineStr">
         <is>
-          <t>SMTP 응답</t>
+          <t>에러 메시지</t>
         </is>
       </c>
       <c r="E119" s="92" t="inlineStr">
@@ -7468,7 +7460,7 @@
       <c r="J119" s="92" t="inlineStr"/>
       <c r="K119" s="92" t="inlineStr">
         <is>
-          <t>SendGrid/SMTP 응답 코드 + 메시지</t>
+          <t>status=failed 시 상세</t>
         </is>
       </c>
     </row>
@@ -7477,12 +7469,12 @@
       <c r="B120" s="91" t="n"/>
       <c r="C120" s="92" t="inlineStr">
         <is>
-          <t>error_msg</t>
+          <t>retry_count</t>
         </is>
       </c>
       <c r="D120" s="92" t="inlineStr">
         <is>
-          <t>에러 메시지</t>
+          <t>재시도 횟수</t>
         </is>
       </c>
       <c r="E120" s="92" t="inlineStr">
@@ -7492,16 +7484,20 @@
       </c>
       <c r="F120" s="92" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>SMALLINT</t>
         </is>
       </c>
       <c r="G120" s="92" t="inlineStr"/>
       <c r="H120" s="92" t="inlineStr"/>
       <c r="I120" s="92" t="inlineStr"/>
-      <c r="J120" s="92" t="inlineStr"/>
+      <c r="J120" s="92" t="inlineStr">
+        <is>
+          <t>Default 0</t>
+        </is>
+      </c>
       <c r="K120" s="92" t="inlineStr">
         <is>
-          <t>status=failed 시 상세</t>
+          <t>EmailAgent retry ×3 횟수</t>
         </is>
       </c>
     </row>
@@ -7510,12 +7506,12 @@
       <c r="B121" s="91" t="n"/>
       <c r="C121" s="92" t="inlineStr">
         <is>
-          <t>retry_count</t>
+          <t>sent_at</t>
         </is>
       </c>
       <c r="D121" s="92" t="inlineStr">
         <is>
-          <t>재시도 횟수</t>
+          <t>발송 시각</t>
         </is>
       </c>
       <c r="E121" s="92" t="inlineStr">
@@ -7525,7 +7521,7 @@
       </c>
       <c r="F121" s="92" t="inlineStr">
         <is>
-          <t>SMALLINT</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="G121" s="92" t="inlineStr"/>
@@ -7533,12 +7529,12 @@
       <c r="I121" s="92" t="inlineStr"/>
       <c r="J121" s="92" t="inlineStr">
         <is>
-          <t>Default 0</t>
+          <t>Default NOW()</t>
         </is>
       </c>
       <c r="K121" s="92" t="inlineStr">
         <is>
-          <t>EmailAgent retry ×3 횟수</t>
+          <t>메일 발송 완료 시각</t>
         </is>
       </c>
     </row>
@@ -7547,12 +7543,12 @@
       <c r="B122" s="91" t="n"/>
       <c r="C122" s="92" t="inlineStr">
         <is>
-          <t>sent_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D122" s="92" t="inlineStr">
         <is>
-          <t>발송 시각</t>
+          <t>생성 시각</t>
         </is>
       </c>
       <c r="E122" s="92" t="inlineStr">
@@ -7575,66 +7571,70 @@
       </c>
       <c r="K122" s="92" t="inlineStr">
         <is>
-          <t>메일 발송 완료 시각</t>
+          <t>row 생성 시각</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="91" t="n"/>
-      <c r="B123" s="91" t="n"/>
+      <c r="A123" s="91" t="inlineStr">
+        <is>
+          <t>pipeline_logs</t>
+        </is>
+      </c>
+      <c r="B123" s="91" t="inlineStr">
+        <is>
+          <t>파이프라인 실행 로그</t>
+        </is>
+      </c>
       <c r="C123" s="92" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D123" s="92" t="inlineStr">
         <is>
-          <t>생성 시각</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E123" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F123" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>BIGSERIAL</t>
         </is>
       </c>
       <c r="G123" s="92" t="inlineStr"/>
-      <c r="H123" s="92" t="inlineStr"/>
+      <c r="H123" s="92" t="inlineStr">
+        <is>
+          <t>PK1</t>
+        </is>
+      </c>
       <c r="I123" s="92" t="inlineStr"/>
       <c r="J123" s="92" t="inlineStr">
         <is>
-          <t>Default NOW()</t>
+          <t>AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="K123" s="92" t="inlineStr">
         <is>
-          <t>row 생성 시각</t>
+          <t>row PK</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="91" t="inlineStr">
-        <is>
-          <t>pipeline_logs</t>
-        </is>
-      </c>
-      <c r="B124" s="91" t="inlineStr">
-        <is>
-          <t>파이프라인 실행 로그</t>
-        </is>
-      </c>
+      <c r="A124" s="91" t="n"/>
+      <c r="B124" s="91" t="n"/>
       <c r="C124" s="92" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>pipeline_step</t>
         </is>
       </c>
       <c r="D124" s="92" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>파이프라인 단계</t>
         </is>
       </c>
       <c r="E124" s="92" t="inlineStr">
@@ -7644,24 +7644,20 @@
       </c>
       <c r="F124" s="92" t="inlineStr">
         <is>
-          <t>BIGSERIAL</t>
-        </is>
-      </c>
-      <c r="G124" s="92" t="inlineStr"/>
-      <c r="H124" s="92" t="inlineStr">
-        <is>
-          <t>PK1</t>
-        </is>
-      </c>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G124" s="92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H124" s="92" t="inlineStr"/>
       <c r="I124" s="92" t="inlineStr"/>
-      <c r="J124" s="92" t="inlineStr">
-        <is>
-          <t>AUTO_INCREMENT</t>
-        </is>
-      </c>
+      <c r="J124" s="92" t="inlineStr"/>
       <c r="K124" s="92" t="inlineStr">
         <is>
-          <t>row PK</t>
+          <t>단계 식별자 (crawl · credibility · dedup 등)</t>
         </is>
       </c>
     </row>
@@ -7670,17 +7666,17 @@
       <c r="B125" s="91" t="n"/>
       <c r="C125" s="92" t="inlineStr">
         <is>
-          <t>pipeline_step</t>
+          <t>peer_id</t>
         </is>
       </c>
       <c r="D125" s="92" t="inlineStr">
         <is>
-          <t>파이프라인 단계</t>
+          <t>Peer ID</t>
         </is>
       </c>
       <c r="E125" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F125" s="92" t="inlineStr">
@@ -7698,7 +7694,7 @@
       <c r="J125" s="92" t="inlineStr"/>
       <c r="K125" s="92" t="inlineStr">
         <is>
-          <t>단계 식별자 (crawl · credibility · dedup 등)</t>
+          <t>처리한 Peer (전체 단계면 NULL)</t>
         </is>
       </c>
     </row>
@@ -7707,12 +7703,12 @@
       <c r="B126" s="91" t="n"/>
       <c r="C126" s="92" t="inlineStr">
         <is>
-          <t>peer_id</t>
+          <t>input_count</t>
         </is>
       </c>
       <c r="D126" s="92" t="inlineStr">
         <is>
-          <t>Peer ID</t>
+          <t>입력 건수</t>
         </is>
       </c>
       <c r="E126" s="92" t="inlineStr">
@@ -7722,20 +7718,16 @@
       </c>
       <c r="F126" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G126" s="92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="G126" s="92" t="inlineStr"/>
       <c r="H126" s="92" t="inlineStr"/>
       <c r="I126" s="92" t="inlineStr"/>
       <c r="J126" s="92" t="inlineStr"/>
       <c r="K126" s="92" t="inlineStr">
         <is>
-          <t>처리한 Peer (전체 단계면 NULL)</t>
+          <t>단계 입력 article 또는 cluster 수</t>
         </is>
       </c>
     </row>
@@ -7744,12 +7736,12 @@
       <c r="B127" s="91" t="n"/>
       <c r="C127" s="92" t="inlineStr">
         <is>
-          <t>input_count</t>
+          <t>output_count</t>
         </is>
       </c>
       <c r="D127" s="92" t="inlineStr">
         <is>
-          <t>입력 건수</t>
+          <t>출력 건수</t>
         </is>
       </c>
       <c r="E127" s="92" t="inlineStr">
@@ -7768,7 +7760,7 @@
       <c r="J127" s="92" t="inlineStr"/>
       <c r="K127" s="92" t="inlineStr">
         <is>
-          <t>단계 입력 article 또는 cluster 수</t>
+          <t>단계 출력 건수</t>
         </is>
       </c>
     </row>
@@ -7777,12 +7769,12 @@
       <c r="B128" s="91" t="n"/>
       <c r="C128" s="92" t="inlineStr">
         <is>
-          <t>output_count</t>
+          <t>elapsed_ms</t>
         </is>
       </c>
       <c r="D128" s="92" t="inlineStr">
         <is>
-          <t>출력 건수</t>
+          <t>소요 시간</t>
         </is>
       </c>
       <c r="E128" s="92" t="inlineStr">
@@ -7798,10 +7790,14 @@
       <c r="G128" s="92" t="inlineStr"/>
       <c r="H128" s="92" t="inlineStr"/>
       <c r="I128" s="92" t="inlineStr"/>
-      <c r="J128" s="92" t="inlineStr"/>
+      <c r="J128" s="92" t="inlineStr">
+        <is>
+          <t>단위: ms</t>
+        </is>
+      </c>
       <c r="K128" s="92" t="inlineStr">
         <is>
-          <t>단계 출력 건수</t>
+          <t>단계 실행 소요 ms</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7806,12 @@
       <c r="B129" s="91" t="n"/>
       <c r="C129" s="92" t="inlineStr">
         <is>
-          <t>elapsed_ms</t>
+          <t>llm_tokens_used</t>
         </is>
       </c>
       <c r="D129" s="92" t="inlineStr">
         <is>
-          <t>소요 시간</t>
+          <t>LLM 토큰</t>
         </is>
       </c>
       <c r="E129" s="92" t="inlineStr">
@@ -7830,15 +7826,19 @@
       </c>
       <c r="G129" s="92" t="inlineStr"/>
       <c r="H129" s="92" t="inlineStr"/>
-      <c r="I129" s="92" t="inlineStr"/>
+      <c r="I129" s="92" t="inlineStr">
+        <is>
+          <t>Default 0</t>
+        </is>
+      </c>
       <c r="J129" s="92" t="inlineStr">
         <is>
-          <t>단위: ms</t>
+          <t>단계 별 OpenAI 토큰 사용량 합계</t>
         </is>
       </c>
       <c r="K129" s="92" t="inlineStr">
         <is>
-          <t>단계 실행 소요 ms</t>
+          <t>비용 추적</t>
         </is>
       </c>
     </row>
@@ -7847,12 +7847,12 @@
       <c r="B130" s="91" t="n"/>
       <c r="C130" s="92" t="inlineStr">
         <is>
-          <t>llm_tokens_used</t>
+          <t>error_msg</t>
         </is>
       </c>
       <c r="D130" s="92" t="inlineStr">
         <is>
-          <t>LLM 토큰</t>
+          <t>에러 메시지</t>
         </is>
       </c>
       <c r="E130" s="92" t="inlineStr">
@@ -7862,24 +7862,16 @@
       </c>
       <c r="F130" s="92" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="G130" s="92" t="inlineStr"/>
       <c r="H130" s="92" t="inlineStr"/>
-      <c r="I130" s="92" t="inlineStr">
-        <is>
-          <t>Default 0</t>
-        </is>
-      </c>
-      <c r="J130" s="92" t="inlineStr">
-        <is>
-          <t>단계 별 OpenAI 토큰 사용량 합계</t>
-        </is>
-      </c>
+      <c r="I130" s="92" t="inlineStr"/>
+      <c r="J130" s="92" t="inlineStr"/>
       <c r="K130" s="92" t="inlineStr">
         <is>
-          <t>비용 추적</t>
+          <t>에러 시 메시지 (정상 시 NULL)</t>
         </is>
       </c>
     </row>
@@ -7888,12 +7880,12 @@
       <c r="B131" s="91" t="n"/>
       <c r="C131" s="92" t="inlineStr">
         <is>
-          <t>error_msg</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D131" s="92" t="inlineStr">
         <is>
-          <t>에러 메시지</t>
+          <t>기록 시각</t>
         </is>
       </c>
       <c r="E131" s="92" t="inlineStr">
@@ -7903,75 +7895,83 @@
       </c>
       <c r="F131" s="92" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="G131" s="92" t="inlineStr"/>
       <c r="H131" s="92" t="inlineStr"/>
       <c r="I131" s="92" t="inlineStr"/>
-      <c r="J131" s="92" t="inlineStr"/>
+      <c r="J131" s="92" t="inlineStr">
+        <is>
+          <t>Default NOW()</t>
+        </is>
+      </c>
       <c r="K131" s="92" t="inlineStr">
         <is>
-          <t>에러 시 메시지 (정상 시 NULL)</t>
+          <t>로그 기록 시각</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="91" t="n"/>
-      <c r="B132" s="91" t="n"/>
+      <c r="A132" s="91" t="inlineStr">
+        <is>
+          <t>crawl_logs</t>
+        </is>
+      </c>
+      <c r="B132" s="91" t="inlineStr">
+        <is>
+          <t>크롤러 실행 로그</t>
+        </is>
+      </c>
       <c r="C132" s="92" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D132" s="92" t="inlineStr">
         <is>
-          <t>기록 시각</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E132" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F132" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>BIGSERIAL</t>
         </is>
       </c>
       <c r="G132" s="92" t="inlineStr"/>
-      <c r="H132" s="92" t="inlineStr"/>
+      <c r="H132" s="92" t="inlineStr">
+        <is>
+          <t>PK1</t>
+        </is>
+      </c>
       <c r="I132" s="92" t="inlineStr"/>
       <c r="J132" s="92" t="inlineStr">
         <is>
-          <t>Default NOW()</t>
+          <t>AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="K132" s="92" t="inlineStr">
         <is>
-          <t>로그 기록 시각</t>
+          <t>row PK</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="91" t="inlineStr">
-        <is>
-          <t>crawl_logs</t>
-        </is>
-      </c>
-      <c r="B133" s="91" t="inlineStr">
-        <is>
-          <t>크롤러 실행 로그</t>
-        </is>
-      </c>
+      <c r="A133" s="91" t="n"/>
+      <c r="B133" s="91" t="n"/>
       <c r="C133" s="92" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>peer_id</t>
         </is>
       </c>
       <c r="D133" s="92" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Peer ID</t>
         </is>
       </c>
       <c r="E133" s="92" t="inlineStr">
@@ -7981,24 +7981,20 @@
       </c>
       <c r="F133" s="92" t="inlineStr">
         <is>
-          <t>BIGSERIAL</t>
-        </is>
-      </c>
-      <c r="G133" s="92" t="inlineStr"/>
-      <c r="H133" s="92" t="inlineStr">
-        <is>
-          <t>PK1</t>
-        </is>
-      </c>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G133" s="92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H133" s="92" t="inlineStr"/>
       <c r="I133" s="92" t="inlineStr"/>
-      <c r="J133" s="92" t="inlineStr">
-        <is>
-          <t>AUTO_INCREMENT</t>
-        </is>
-      </c>
+      <c r="J133" s="92" t="inlineStr"/>
       <c r="K133" s="92" t="inlineStr">
         <is>
-          <t>row PK</t>
+          <t>크롤링 대상 Peer</t>
         </is>
       </c>
     </row>
@@ -8007,12 +8003,12 @@
       <c r="B134" s="91" t="n"/>
       <c r="C134" s="92" t="inlineStr">
         <is>
-          <t>peer_id</t>
+          <t>source_name</t>
         </is>
       </c>
       <c r="D134" s="92" t="inlineStr">
         <is>
-          <t>Peer ID</t>
+          <t>출처 이름</t>
         </is>
       </c>
       <c r="E134" s="92" t="inlineStr">
@@ -8027,7 +8023,7 @@
       </c>
       <c r="G134" s="92" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H134" s="92" t="inlineStr"/>
@@ -8035,7 +8031,7 @@
       <c r="J134" s="92" t="inlineStr"/>
       <c r="K134" s="92" t="inlineStr">
         <is>
-          <t>크롤링 대상 Peer</t>
+          <t>크롤링 소스 (DART · 한경 등)</t>
         </is>
       </c>
     </row>
@@ -8044,12 +8040,12 @@
       <c r="B135" s="91" t="n"/>
       <c r="C135" s="92" t="inlineStr">
         <is>
-          <t>source_name</t>
+          <t>started_at</t>
         </is>
       </c>
       <c r="D135" s="92" t="inlineStr">
         <is>
-          <t>출처 이름</t>
+          <t>시작 시각</t>
         </is>
       </c>
       <c r="E135" s="92" t="inlineStr">
@@ -8059,20 +8055,16 @@
       </c>
       <c r="F135" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G135" s="92" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="G135" s="92" t="inlineStr"/>
       <c r="H135" s="92" t="inlineStr"/>
       <c r="I135" s="92" t="inlineStr"/>
       <c r="J135" s="92" t="inlineStr"/>
       <c r="K135" s="92" t="inlineStr">
         <is>
-          <t>크롤링 소스 (DART · 한경 등)</t>
+          <t>크롤링 시작 시각</t>
         </is>
       </c>
     </row>
@@ -8081,17 +8073,17 @@
       <c r="B136" s="91" t="n"/>
       <c r="C136" s="92" t="inlineStr">
         <is>
-          <t>started_at</t>
+          <t>finished_at</t>
         </is>
       </c>
       <c r="D136" s="92" t="inlineStr">
         <is>
-          <t>시작 시각</t>
+          <t>완료 시각</t>
         </is>
       </c>
       <c r="E136" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F136" s="92" t="inlineStr">
@@ -8105,7 +8097,7 @@
       <c r="J136" s="92" t="inlineStr"/>
       <c r="K136" s="92" t="inlineStr">
         <is>
-          <t>크롤링 시작 시각</t>
+          <t>크롤링 완료 시각 (실패 시 NULL)</t>
         </is>
       </c>
     </row>
@@ -8114,12 +8106,12 @@
       <c r="B137" s="91" t="n"/>
       <c r="C137" s="92" t="inlineStr">
         <is>
-          <t>finished_at</t>
+          <t>total_count</t>
         </is>
       </c>
       <c r="D137" s="92" t="inlineStr">
         <is>
-          <t>완료 시각</t>
+          <t>전체 건수</t>
         </is>
       </c>
       <c r="E137" s="92" t="inlineStr">
@@ -8129,16 +8121,20 @@
       </c>
       <c r="F137" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="G137" s="92" t="inlineStr"/>
       <c r="H137" s="92" t="inlineStr"/>
       <c r="I137" s="92" t="inlineStr"/>
-      <c r="J137" s="92" t="inlineStr"/>
+      <c r="J137" s="92" t="inlineStr">
+        <is>
+          <t>Default 0</t>
+        </is>
+      </c>
       <c r="K137" s="92" t="inlineStr">
         <is>
-          <t>크롤링 완료 시각 (실패 시 NULL)</t>
+          <t>수집 시도 총 건수</t>
         </is>
       </c>
     </row>
@@ -8147,12 +8143,12 @@
       <c r="B138" s="91" t="n"/>
       <c r="C138" s="92" t="inlineStr">
         <is>
-          <t>total_count</t>
+          <t>success_count</t>
         </is>
       </c>
       <c r="D138" s="92" t="inlineStr">
         <is>
-          <t>전체 건수</t>
+          <t>성공 건수</t>
         </is>
       </c>
       <c r="E138" s="92" t="inlineStr">
@@ -8175,7 +8171,7 @@
       </c>
       <c r="K138" s="92" t="inlineStr">
         <is>
-          <t>수집 시도 총 건수</t>
+          <t>INSERT 성공 건수</t>
         </is>
       </c>
     </row>
@@ -8184,12 +8180,12 @@
       <c r="B139" s="91" t="n"/>
       <c r="C139" s="92" t="inlineStr">
         <is>
-          <t>success_count</t>
+          <t>skipped_count</t>
         </is>
       </c>
       <c r="D139" s="92" t="inlineStr">
         <is>
-          <t>성공 건수</t>
+          <t>스킵 건수</t>
         </is>
       </c>
       <c r="E139" s="92" t="inlineStr">
@@ -8212,7 +8208,7 @@
       </c>
       <c r="K139" s="92" t="inlineStr">
         <is>
-          <t>INSERT 성공 건수</t>
+          <t>중복/품질 미달로 스킵된 건수</t>
         </is>
       </c>
     </row>
@@ -8221,12 +8217,12 @@
       <c r="B140" s="91" t="n"/>
       <c r="C140" s="92" t="inlineStr">
         <is>
-          <t>skipped_count</t>
+          <t>error_msg</t>
         </is>
       </c>
       <c r="D140" s="92" t="inlineStr">
         <is>
-          <t>스킵 건수</t>
+          <t>에러 메시지</t>
         </is>
       </c>
       <c r="E140" s="92" t="inlineStr">
@@ -8236,20 +8232,16 @@
       </c>
       <c r="F140" s="92" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="G140" s="92" t="inlineStr"/>
       <c r="H140" s="92" t="inlineStr"/>
       <c r="I140" s="92" t="inlineStr"/>
-      <c r="J140" s="92" t="inlineStr">
-        <is>
-          <t>Default 0</t>
-        </is>
-      </c>
+      <c r="J140" s="92" t="inlineStr"/>
       <c r="K140" s="92" t="inlineStr">
         <is>
-          <t>중복/품질 미달로 스킵된 건수</t>
+          <t>전체 작업 실패 시 에러</t>
         </is>
       </c>
     </row>
@@ -8258,12 +8250,12 @@
       <c r="B141" s="91" t="n"/>
       <c r="C141" s="92" t="inlineStr">
         <is>
-          <t>error_msg</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D141" s="92" t="inlineStr">
         <is>
-          <t>에러 메시지</t>
+          <t>기록 시각</t>
         </is>
       </c>
       <c r="E141" s="92" t="inlineStr">
@@ -8273,75 +8265,83 @@
       </c>
       <c r="F141" s="92" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>TIMESTAMPTZ</t>
         </is>
       </c>
       <c r="G141" s="92" t="inlineStr"/>
       <c r="H141" s="92" t="inlineStr"/>
       <c r="I141" s="92" t="inlineStr"/>
-      <c r="J141" s="92" t="inlineStr"/>
+      <c r="J141" s="92" t="inlineStr">
+        <is>
+          <t>Default NOW()</t>
+        </is>
+      </c>
       <c r="K141" s="92" t="inlineStr">
         <is>
-          <t>전체 작업 실패 시 에러</t>
+          <t>로그 기록 시각</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="91" t="n"/>
-      <c r="B142" s="91" t="n"/>
+      <c r="A142" s="91" t="inlineStr">
+        <is>
+          <t>golden_set</t>
+        </is>
+      </c>
+      <c r="B142" s="91" t="inlineStr">
+        <is>
+          <t>RAG 평가용 골든셋</t>
+        </is>
+      </c>
       <c r="C142" s="92" t="inlineStr">
         <is>
-          <t>created_at</t>
+          <t>id</t>
         </is>
       </c>
       <c r="D142" s="92" t="inlineStr">
         <is>
-          <t>기록 시각</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E142" s="92" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F142" s="92" t="inlineStr">
         <is>
-          <t>TIMESTAMPTZ</t>
+          <t>BIGSERIAL</t>
         </is>
       </c>
       <c r="G142" s="92" t="inlineStr"/>
-      <c r="H142" s="92" t="inlineStr"/>
+      <c r="H142" s="92" t="inlineStr">
+        <is>
+          <t>PK1</t>
+        </is>
+      </c>
       <c r="I142" s="92" t="inlineStr"/>
       <c r="J142" s="92" t="inlineStr">
         <is>
-          <t>Default NOW()</t>
+          <t>AUTO_INCREMENT</t>
         </is>
       </c>
       <c r="K142" s="92" t="inlineStr">
         <is>
-          <t>로그 기록 시각</t>
+          <t>row PK</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="91" t="inlineStr">
-        <is>
-          <t>golden_set</t>
-        </is>
-      </c>
-      <c r="B143" s="91" t="inlineStr">
-        <is>
-          <t>RAG 평가용 골든셋</t>
-        </is>
-      </c>
+      <c r="A143" s="91" t="n"/>
+      <c r="B143" s="91" t="n"/>
       <c r="C143" s="92" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>query</t>
         </is>
       </c>
       <c r="D143" s="92" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>쿼리</t>
         </is>
       </c>
       <c r="E143" s="92" t="inlineStr">
@@ -8351,24 +8351,16 @@
       </c>
       <c r="F143" s="92" t="inlineStr">
         <is>
-          <t>BIGSERIAL</t>
+          <t>TEXT</t>
         </is>
       </c>
       <c r="G143" s="92" t="inlineStr"/>
-      <c r="H143" s="92" t="inlineStr">
-        <is>
-          <t>PK1</t>
-        </is>
-      </c>
+      <c r="H143" s="92" t="inlineStr"/>
       <c r="I143" s="92" t="inlineStr"/>
-      <c r="J143" s="92" t="inlineStr">
-        <is>
-          <t>AUTO_INCREMENT</t>
-        </is>
-      </c>
+      <c r="J143" s="92" t="inlineStr"/>
       <c r="K143" s="92" t="inlineStr">
         <is>
-          <t>row PK</t>
+          <t>RAG 평가용 자연어 query</t>
         </is>
       </c>
     </row>
@@ -8377,31 +8369,35 @@
       <c r="B144" s="91" t="n"/>
       <c r="C144" s="92" t="inlineStr">
         <is>
-          <t>query</t>
+          <t>expected_card_ids</t>
         </is>
       </c>
       <c r="D144" s="92" t="inlineStr">
         <is>
-          <t>쿼리</t>
+          <t>기대 카드 ID</t>
         </is>
       </c>
       <c r="E144" s="92" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="F144" s="92" t="inlineStr">
         <is>
-          <t>TEXT</t>
+          <t>TEXT[]</t>
         </is>
       </c>
       <c r="G144" s="92" t="inlineStr"/>
       <c r="H144" s="92" t="inlineStr"/>
       <c r="I144" s="92" t="inlineStr"/>
-      <c r="J144" s="92" t="inlineStr"/>
+      <c r="J144" s="92" t="inlineStr">
+        <is>
+          <t>Default '{}'</t>
+        </is>
+      </c>
       <c r="K144" s="92" t="inlineStr">
         <is>
-          <t>RAG 평가용 자연어 query</t>
+          <t>정답 카드 ID 배열</t>
         </is>
       </c>
     </row>
@@ -8410,12 +8406,12 @@
       <c r="B145" s="91" t="n"/>
       <c r="C145" s="92" t="inlineStr">
         <is>
-          <t>expected_card_ids</t>
+          <t>annotator</t>
         </is>
       </c>
       <c r="D145" s="92" t="inlineStr">
         <is>
-          <t>기대 카드 ID</t>
+          <t>라벨러</t>
         </is>
       </c>
       <c r="E145" s="92" t="inlineStr">
@@ -8425,20 +8421,20 @@
       </c>
       <c r="F145" s="92" t="inlineStr">
         <is>
-          <t>TEXT[]</t>
-        </is>
-      </c>
-      <c r="G145" s="92" t="inlineStr"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="G145" s="92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="H145" s="92" t="inlineStr"/>
       <c r="I145" s="92" t="inlineStr"/>
-      <c r="J145" s="92" t="inlineStr">
-        <is>
-          <t>Default '{}'</t>
-        </is>
-      </c>
+      <c r="J145" s="92" t="inlineStr"/>
       <c r="K145" s="92" t="inlineStr">
         <is>
-          <t>정답 카드 ID 배열</t>
+          <t>라벨링 담당자 이름</t>
         </is>
       </c>
     </row>
@@ -8447,12 +8443,12 @@
       <c r="B146" s="91" t="n"/>
       <c r="C146" s="92" t="inlineStr">
         <is>
-          <t>annotator</t>
+          <t>difficulty</t>
         </is>
       </c>
       <c r="D146" s="92" t="inlineStr">
         <is>
-          <t>라벨러</t>
+          <t>난이도</t>
         </is>
       </c>
       <c r="E146" s="92" t="inlineStr">
@@ -8467,15 +8463,19 @@
       </c>
       <c r="G146" s="92" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H146" s="92" t="inlineStr"/>
       <c r="I146" s="92" t="inlineStr"/>
-      <c r="J146" s="92" t="inlineStr"/>
+      <c r="J146" s="92" t="inlineStr">
+        <is>
+          <t>easy | hard</t>
+        </is>
+      </c>
       <c r="K146" s="92" t="inlineStr">
         <is>
-          <t>라벨링 담당자 이름</t>
+          <t>평가 난이도 분류</t>
         </is>
       </c>
     </row>
@@ -8484,12 +8484,12 @@
       <c r="B147" s="91" t="n"/>
       <c r="C147" s="92" t="inlineStr">
         <is>
-          <t>difficulty</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="D147" s="92" t="inlineStr">
         <is>
-          <t>난이도</t>
+          <t>생성 시각</t>
         </is>
       </c>
       <c r="E147" s="92" t="inlineStr">
@@ -8499,59 +8499,18 @@
       </c>
       <c r="F147" s="92" t="inlineStr">
         <is>
-          <t>VARCHAR</t>
-        </is>
-      </c>
-      <c r="G147" s="92" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>TIMESTAMPTZ</t>
+        </is>
+      </c>
+      <c r="G147" s="92" t="inlineStr"/>
       <c r="H147" s="92" t="inlineStr"/>
       <c r="I147" s="92" t="inlineStr"/>
       <c r="J147" s="92" t="inlineStr">
         <is>
-          <t>easy | hard</t>
+          <t>Default NOW()</t>
         </is>
       </c>
       <c r="K147" s="92" t="inlineStr">
-        <is>
-          <t>평가 난이도 분류</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="91" t="n"/>
-      <c r="B148" s="91" t="n"/>
-      <c r="C148" s="92" t="inlineStr">
-        <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="D148" s="92" t="inlineStr">
-        <is>
-          <t>생성 시각</t>
-        </is>
-      </c>
-      <c r="E148" s="92" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F148" s="92" t="inlineStr">
-        <is>
-          <t>TIMESTAMPTZ</t>
-        </is>
-      </c>
-      <c r="G148" s="92" t="inlineStr"/>
-      <c r="H148" s="92" t="inlineStr"/>
-      <c r="I148" s="92" t="inlineStr"/>
-      <c r="J148" s="92" t="inlineStr">
-        <is>
-          <t>Default NOW()</t>
-        </is>
-      </c>
-      <c r="K148" s="92" t="inlineStr">
         <is>
           <t>row 생성 시각</t>
         </is>
